--- a/VRTX.xlsx
+++ b/VRTX.xlsx
@@ -1,34 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE9B7D9A-E9FB-4944-B830-ADFB13126A5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E55A28FE-5124-4414-97C5-E2B181B238D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="42170" yWindow="2090" windowWidth="31080" windowHeight="16810" xr2:uid="{79B82797-CA5A-45D2-8A30-BD70659F48DF}"/>
+    <workbookView xWindow="9870" yWindow="1650" windowWidth="22360" windowHeight="16580" activeTab="2" xr2:uid="{79B82797-CA5A-45D2-8A30-BD70659F48DF}"/>
   </bookViews>
   <sheets>
-    <sheet name="Main" sheetId="1" r:id="rId1"/>
-    <sheet name="Model" sheetId="3" r:id="rId2"/>
-    <sheet name="Trikafta" sheetId="9" r:id="rId3"/>
-    <sheet name="Orkambi" sheetId="11" r:id="rId4"/>
-    <sheet name="Symdeko" sheetId="6" r:id="rId5"/>
-    <sheet name="Kalydeco" sheetId="2" r:id="rId6"/>
-    <sheet name="Casgevy" sheetId="8" r:id="rId7"/>
-    <sheet name="VX-880" sheetId="7" r:id="rId8"/>
-    <sheet name="povetacicept" sheetId="16" r:id="rId9"/>
-    <sheet name="Alyftrek" sheetId="12" r:id="rId10"/>
-    <sheet name="VX-548" sheetId="13" r:id="rId11"/>
-    <sheet name="VX-522" sheetId="15" r:id="rId12"/>
-    <sheet name="inaxaplin" sheetId="10" r:id="rId13"/>
-    <sheet name="VX-634" sheetId="14" r:id="rId14"/>
-    <sheet name="IP" sheetId="4" r:id="rId15"/>
-    <sheet name="Compounds" sheetId="5" r:id="rId16"/>
+    <sheet name="Master" sheetId="17" r:id="rId1"/>
+    <sheet name="Main" sheetId="1" r:id="rId2"/>
+    <sheet name="Model" sheetId="3" r:id="rId3"/>
+    <sheet name="Trikafta" sheetId="9" r:id="rId4"/>
+    <sheet name="Orkambi" sheetId="11" r:id="rId5"/>
+    <sheet name="Symdeko" sheetId="6" r:id="rId6"/>
+    <sheet name="Kalydeco" sheetId="2" r:id="rId7"/>
+    <sheet name="Casgevy" sheetId="8" r:id="rId8"/>
+    <sheet name="VX-880" sheetId="7" r:id="rId9"/>
+    <sheet name="povetacicept" sheetId="16" r:id="rId10"/>
+    <sheet name="Alyftrek" sheetId="12" r:id="rId11"/>
+    <sheet name="VX-548" sheetId="13" r:id="rId12"/>
+    <sheet name="VX-522" sheetId="15" r:id="rId13"/>
+    <sheet name="inaxaplin" sheetId="10" r:id="rId14"/>
+    <sheet name="VX-634" sheetId="14" r:id="rId15"/>
+    <sheet name="IP" sheetId="4" r:id="rId16"/>
+    <sheet name="Compounds" sheetId="5" r:id="rId17"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -109,7 +110,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="417">
   <si>
     <t>Price</t>
   </si>
@@ -1233,9 +1234,6 @@
     <t>expires 2037</t>
   </si>
   <si>
-    <t>1H26 filing for povetacicept</t>
-  </si>
-  <si>
     <t>VX-828</t>
   </si>
   <si>
@@ -1245,9 +1243,6 @@
     <t>VX-973</t>
   </si>
   <si>
-    <t>VX-993 2H25 results</t>
-  </si>
-  <si>
     <t>zimislecel</t>
   </si>
   <si>
@@ -1342,6 +1337,30 @@
   </si>
   <si>
     <t>Phase II/III "OLYMPUS" MN</t>
+  </si>
+  <si>
+    <t>corrector 3.0</t>
+  </si>
+  <si>
+    <t>2H26: VX-828 results</t>
+  </si>
+  <si>
+    <t>VX-581</t>
+  </si>
+  <si>
+    <t>VX-272</t>
+  </si>
+  <si>
+    <t>abandoned</t>
+  </si>
+  <si>
+    <t>2H26: complete enrollment in DPN Phase III studies</t>
+  </si>
+  <si>
+    <t>Nav1.7</t>
+  </si>
+  <si>
+    <t>Early 2027: AMPLITUDE interim analysis</t>
   </si>
 </sst>
 </file>
@@ -1580,14 +1599,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>31</xdr:col>
-      <xdr:colOff>61778</xdr:colOff>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>83548</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>31</xdr:col>
-      <xdr:colOff>61778</xdr:colOff>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>83548</xdr:colOff>
       <xdr:row>88</xdr:row>
       <xdr:rowOff>140368</xdr:rowOff>
     </xdr:to>
@@ -1604,7 +1623,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="19438349" y="0"/>
+          <a:off x="20559577" y="0"/>
           <a:ext cx="0" cy="14204711"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1630,16 +1649,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>48</xdr:col>
-      <xdr:colOff>8666</xdr:colOff>
+      <xdr:col>49</xdr:col>
+      <xdr:colOff>84866</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>10456</xdr:rowOff>
+      <xdr:rowOff>79399</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>48</xdr:col>
-      <xdr:colOff>8666</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>145166</xdr:rowOff>
+      <xdr:col>49</xdr:col>
+      <xdr:colOff>84866</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>54452</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1654,8 +1673,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="26733095" y="10456"/>
-          <a:ext cx="0" cy="8952139"/>
+          <a:off x="30256437" y="79399"/>
+          <a:ext cx="0" cy="9090024"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -2399,8 +2418,1413 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE8CB29E-6F91-4168-8EDB-015B16A97FEA}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>305</v>
+      </c>
+      <c r="C2" t="s">
+        <v>375</v>
+      </c>
+      <c r="D2" t="s">
+        <v>394</v>
+      </c>
+      <c r="E2" t="s">
+        <v>413</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8C3D72A-F23C-49FA-B015-8CB9FAFD237F}">
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+      <c r="C6" s="18" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+      <c r="C10" s="18" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D12" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C13" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+      <c r="C16" s="18" t="s">
+        <v>408</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{22B1C448-9C83-4D95-99CC-9F72F9CD7C85}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF238714-88C7-42B3-B2FD-3531313A58EB}">
+  <dimension ref="A1:N14"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.81640625" customWidth="1"/>
+    <col min="3" max="3" width="12.26953125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>359</v>
+      </c>
+      <c r="H2" s="20"/>
+      <c r="N2" s="8"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C5" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="13" x14ac:dyDescent="0.3">
+      <c r="C7" s="18" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="13" x14ac:dyDescent="0.3">
+      <c r="C10" s="18" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="13" x14ac:dyDescent="0.3">
+      <c r="C14" s="18" t="s">
+        <v>317</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{D27BB88E-1A8F-41E5-B99C-BA493095DC2C}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11AB47AF-768E-4B06-9E84-BC4ABCFB8ABD}">
+  <dimension ref="A1:E40"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.26953125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>230</v>
+      </c>
+      <c r="C6" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>337</v>
+      </c>
+      <c r="C7" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>385</v>
+      </c>
+      <c r="C8" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+      <c r="C10" s="18" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+      <c r="C13" s="18" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="17" spans="3:5" ht="13" x14ac:dyDescent="0.3">
+      <c r="C17" s="18" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="18" spans="3:5" ht="13" x14ac:dyDescent="0.3">
+      <c r="C18" s="18"/>
+      <c r="D18" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="19" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C19" t="s">
+        <v>231</v>
+      </c>
+      <c r="D19" s="22">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="20" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C20" t="s">
+        <v>233</v>
+      </c>
+      <c r="D20" s="22">
+        <v>137.80000000000001</v>
+      </c>
+      <c r="E20" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="21" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C21" t="s">
+        <v>235</v>
+      </c>
+      <c r="D21" s="22">
+        <v>86.9</v>
+      </c>
+      <c r="E21" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="22" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C22" t="s">
+        <v>236</v>
+      </c>
+      <c r="D22" s="22">
+        <v>112.9</v>
+      </c>
+      <c r="E22" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="23" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C23" t="s">
+        <v>237</v>
+      </c>
+      <c r="D23" s="22">
+        <v>115.6</v>
+      </c>
+      <c r="E23" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="24" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D24" s="22"/>
+    </row>
+    <row r="25" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D25" s="22"/>
+    </row>
+    <row r="26" spans="3:5" ht="13" x14ac:dyDescent="0.3">
+      <c r="C26" s="18" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="27" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D27" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="28" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C28" t="s">
+        <v>231</v>
+      </c>
+      <c r="D28">
+        <v>72.7</v>
+      </c>
+    </row>
+    <row r="29" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C29" t="s">
+        <v>233</v>
+      </c>
+      <c r="D29">
+        <v>110.5</v>
+      </c>
+      <c r="E29" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="30" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C30" t="s">
+        <v>235</v>
+      </c>
+      <c r="D30">
+        <v>95.1</v>
+      </c>
+      <c r="E30" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="31" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C31" t="s">
+        <v>237</v>
+      </c>
+      <c r="D31">
+        <v>85.2</v>
+      </c>
+      <c r="E31" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="33" spans="3:3" ht="13" x14ac:dyDescent="0.3">
+      <c r="C33" s="18" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="35" spans="3:3" ht="13" x14ac:dyDescent="0.3">
+      <c r="C35" s="18" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="38" spans="3:3" ht="13" x14ac:dyDescent="0.3">
+      <c r="C38" s="18" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="39" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C39" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="40" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C40" t="s">
+        <v>336</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{9F1444FB-1FC7-4AF6-9D19-F860F1DDD4D6}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CA6AB23-686C-478E-AA6A-03F37C9331A3}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C4" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+      <c r="C6" s="18" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
+        <v>321</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{C0D50ABE-2133-4DD7-AC00-5588FBC472DA}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3500169-374E-454F-AD84-2EA69EF52EB1}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+      <c r="C7" s="18" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C8" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C9" t="s">
+        <v>325</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{8E17983A-F281-41DE-94AE-3C971B03D303}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECE9D23D-12F6-4A5D-93D1-1862668A41BC}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C4" t="s">
+        <v>294</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{0A34DDFA-7AD8-4524-8897-4C2FF35B4CE5}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEF0003B-178C-466F-BE10-E90BCC8A1B78}">
+  <dimension ref="A1:I24"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.81640625" customWidth="1"/>
+    <col min="7" max="8" width="10.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H2" t="s">
+        <v>72</v>
+      </c>
+      <c r="I2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B3">
+        <v>11390600</v>
+      </c>
+      <c r="C3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3" s="15">
+        <v>44019</v>
+      </c>
+      <c r="H3" s="15">
+        <v>44761</v>
+      </c>
+      <c r="I3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B4">
+        <v>11370798</v>
+      </c>
+      <c r="C4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E4" t="s">
+        <v>74</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="G4" s="15">
+        <v>44074</v>
+      </c>
+      <c r="H4" s="15">
+        <v>44740</v>
+      </c>
+      <c r="I4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B5">
+        <v>11369692</v>
+      </c>
+      <c r="C5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F5">
+        <v>5</v>
+      </c>
+      <c r="G5" s="15">
+        <v>42671</v>
+      </c>
+      <c r="H5" s="15">
+        <v>44740</v>
+      </c>
+      <c r="I5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B6">
+        <v>11358977</v>
+      </c>
+      <c r="C6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D6" t="s">
+        <v>73</v>
+      </c>
+      <c r="E6" t="s">
+        <v>82</v>
+      </c>
+      <c r="F6">
+        <v>8</v>
+      </c>
+      <c r="G6" s="15">
+        <v>43236</v>
+      </c>
+      <c r="H6" s="15">
+        <v>44726</v>
+      </c>
+      <c r="I6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B7">
+        <v>11345700</v>
+      </c>
+      <c r="C7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E7" t="s">
+        <v>83</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7" s="15">
+        <v>43899</v>
+      </c>
+      <c r="H7" s="15">
+        <v>44712</v>
+      </c>
+      <c r="I7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B8">
+        <v>11291662</v>
+      </c>
+      <c r="C8" t="s">
+        <v>86</v>
+      </c>
+      <c r="D8" t="s">
+        <v>73</v>
+      </c>
+      <c r="E8" t="s">
+        <v>87</v>
+      </c>
+      <c r="F8">
+        <v>3</v>
+      </c>
+      <c r="G8" s="15">
+        <v>43804</v>
+      </c>
+      <c r="H8" s="15">
+        <v>44656</v>
+      </c>
+      <c r="I8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B9">
+        <v>11268077</v>
+      </c>
+      <c r="C9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D9" t="s">
+        <v>73</v>
+      </c>
+      <c r="E9" t="s">
+        <v>91</v>
+      </c>
+      <c r="F9">
+        <v>5</v>
+      </c>
+      <c r="G9" s="15">
+        <v>43501</v>
+      </c>
+      <c r="H9" s="15">
+        <v>44628</v>
+      </c>
+      <c r="I9" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B10">
+        <v>11253509</v>
+      </c>
+      <c r="C10" t="s">
+        <v>93</v>
+      </c>
+      <c r="D10" t="s">
+        <v>73</v>
+      </c>
+      <c r="E10" t="s">
+        <v>94</v>
+      </c>
+      <c r="F10">
+        <v>2</v>
+      </c>
+      <c r="G10" s="15">
+        <v>43259</v>
+      </c>
+      <c r="H10" s="15">
+        <v>44614</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B11">
+        <v>11203571</v>
+      </c>
+      <c r="C11" t="s">
+        <v>195</v>
+      </c>
+      <c r="D11" t="s">
+        <v>73</v>
+      </c>
+      <c r="E11" t="s">
+        <v>196</v>
+      </c>
+      <c r="F11">
+        <v>8</v>
+      </c>
+      <c r="G11" s="15">
+        <v>41835</v>
+      </c>
+      <c r="H11" s="15">
+        <v>44551</v>
+      </c>
+      <c r="I11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B12">
+        <v>11186566</v>
+      </c>
+      <c r="C12" t="s">
+        <v>197</v>
+      </c>
+      <c r="D12" t="s">
+        <v>73</v>
+      </c>
+      <c r="E12" t="s">
+        <v>198</v>
+      </c>
+      <c r="F12">
+        <v>6</v>
+      </c>
+      <c r="G12" s="15">
+        <v>43803</v>
+      </c>
+      <c r="H12" s="15">
+        <v>44530</v>
+      </c>
+      <c r="I12" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B13">
+        <v>11179394</v>
+      </c>
+      <c r="C13" t="s">
+        <v>200</v>
+      </c>
+      <c r="D13" t="s">
+        <v>73</v>
+      </c>
+      <c r="E13" t="s">
+        <v>201</v>
+      </c>
+      <c r="F13">
+        <v>3</v>
+      </c>
+      <c r="G13" s="15">
+        <v>42172</v>
+      </c>
+      <c r="H13" s="15">
+        <v>44523</v>
+      </c>
+      <c r="I13" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B14">
+        <v>11179367</v>
+      </c>
+      <c r="C14" t="s">
+        <v>203</v>
+      </c>
+      <c r="D14" t="s">
+        <v>73</v>
+      </c>
+      <c r="E14" t="s">
+        <v>204</v>
+      </c>
+      <c r="F14">
+        <v>2</v>
+      </c>
+      <c r="G14" s="15">
+        <v>43500</v>
+      </c>
+      <c r="H14" s="15">
+        <v>44523</v>
+      </c>
+      <c r="I14" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B15">
+        <v>11155533</v>
+      </c>
+      <c r="C15" t="s">
+        <v>206</v>
+      </c>
+      <c r="D15" t="s">
+        <v>73</v>
+      </c>
+      <c r="E15" t="s">
+        <v>207</v>
+      </c>
+      <c r="F15">
+        <v>2</v>
+      </c>
+      <c r="G15" s="15">
+        <v>43915</v>
+      </c>
+      <c r="H15" s="15">
+        <v>44495</v>
+      </c>
+      <c r="I15" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <v>11147770</v>
+      </c>
+      <c r="C16" t="s">
+        <v>209</v>
+      </c>
+      <c r="D16" t="s">
+        <v>73</v>
+      </c>
+      <c r="E16" t="s">
+        <v>210</v>
+      </c>
+      <c r="F16">
+        <v>2</v>
+      </c>
+      <c r="G16" s="15">
+        <v>43536</v>
+      </c>
+      <c r="H16" s="15">
+        <v>44488</v>
+      </c>
+      <c r="I16" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <v>11124805</v>
+      </c>
+      <c r="C17" t="s">
+        <v>211</v>
+      </c>
+      <c r="D17" t="s">
+        <v>73</v>
+      </c>
+      <c r="E17" t="s">
+        <v>212</v>
+      </c>
+      <c r="F17">
+        <v>7</v>
+      </c>
+      <c r="G17" s="15">
+        <v>42929</v>
+      </c>
+      <c r="H17" s="15">
+        <v>44460</v>
+      </c>
+      <c r="I17" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B18">
+        <v>11117900</v>
+      </c>
+      <c r="C18" t="s">
+        <v>70</v>
+      </c>
+      <c r="D18" t="s">
+        <v>73</v>
+      </c>
+      <c r="E18" t="s">
+        <v>74</v>
+      </c>
+      <c r="F18">
+        <v>3</v>
+      </c>
+      <c r="G18" s="15">
+        <v>43683</v>
+      </c>
+      <c r="H18" s="15">
+        <v>44453</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B19">
+        <v>11110108</v>
+      </c>
+      <c r="C19" t="s">
+        <v>214</v>
+      </c>
+      <c r="D19" t="s">
+        <v>73</v>
+      </c>
+      <c r="E19" t="s">
+        <v>215</v>
+      </c>
+      <c r="F19">
+        <v>2</v>
+      </c>
+      <c r="G19" s="15">
+        <v>43005</v>
+      </c>
+      <c r="H19" s="15">
+        <v>44446</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B20">
+        <v>11110086</v>
+      </c>
+      <c r="C20" t="s">
+        <v>216</v>
+      </c>
+      <c r="D20" t="s">
+        <v>73</v>
+      </c>
+      <c r="E20" t="s">
+        <v>217</v>
+      </c>
+      <c r="F20">
+        <v>3</v>
+      </c>
+      <c r="G20" s="15">
+        <v>43656</v>
+      </c>
+      <c r="H20" s="15">
+        <v>44446</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B21">
+        <v>11084804</v>
+      </c>
+      <c r="C21" t="s">
+        <v>218</v>
+      </c>
+      <c r="D21" t="s">
+        <v>73</v>
+      </c>
+      <c r="E21" t="s">
+        <v>219</v>
+      </c>
+      <c r="F21">
+        <v>5</v>
+      </c>
+      <c r="G21" s="15">
+        <v>43874</v>
+      </c>
+      <c r="H21" s="15">
+        <v>44418</v>
+      </c>
+      <c r="I21" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B22">
+        <v>11066417</v>
+      </c>
+      <c r="C22" t="s">
+        <v>221</v>
+      </c>
+      <c r="D22" t="s">
+        <v>73</v>
+      </c>
+      <c r="E22" t="s">
+        <v>220</v>
+      </c>
+      <c r="F22">
+        <v>6</v>
+      </c>
+      <c r="G22" s="15">
+        <v>43510</v>
+      </c>
+      <c r="H22" s="15">
+        <v>44397</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B23">
+        <v>11059826</v>
+      </c>
+      <c r="C23" t="s">
+        <v>222</v>
+      </c>
+      <c r="D23" t="s">
+        <v>73</v>
+      </c>
+      <c r="E23" t="s">
+        <v>223</v>
+      </c>
+      <c r="F23">
+        <v>5</v>
+      </c>
+      <c r="G23" s="15">
+        <v>43578</v>
+      </c>
+      <c r="H23" s="15">
+        <v>44390</v>
+      </c>
+      <c r="I23" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B24">
+        <v>11052075</v>
+      </c>
+      <c r="C24" t="s">
+        <v>225</v>
+      </c>
+      <c r="D24" t="s">
+        <v>73</v>
+      </c>
+      <c r="E24" t="s">
+        <v>226</v>
+      </c>
+      <c r="G24" s="15">
+        <v>43679</v>
+      </c>
+      <c r="H24" s="15">
+        <v>44383</v>
+      </c>
+      <c r="I24" t="s">
+        <v>205</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{28B9CEB8-4D0A-4224-9448-513A0C99A972}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4728C55-E312-4CB5-A877-7A6998D5236F}">
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.26953125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F3" s="15">
+        <v>40686</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="15">
+        <v>42187</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C5" t="s">
+        <v>111</v>
+      </c>
+      <c r="E5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s">
+        <v>113</v>
+      </c>
+      <c r="E6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>103</v>
+      </c>
+      <c r="D9" t="s">
+        <v>105</v>
+      </c>
+      <c r="E9" t="s">
+        <v>96</v>
+      </c>
+      <c r="F9" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>104</v>
+      </c>
+      <c r="D10" t="s">
+        <v>105</v>
+      </c>
+      <c r="E10" t="s">
+        <v>96</v>
+      </c>
+      <c r="F10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D11" t="s">
+        <v>69</v>
+      </c>
+      <c r="E11" t="s">
+        <v>106</v>
+      </c>
+      <c r="F11" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>248</v>
+      </c>
+      <c r="D12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12" t="s">
+        <v>43</v>
+      </c>
+      <c r="F12" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>100</v>
+      </c>
+      <c r="D13" t="s">
+        <v>101</v>
+      </c>
+      <c r="E13" t="s">
+        <v>96</v>
+      </c>
+      <c r="F13" t="s">
+        <v>102</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{BFCC45F9-5F22-4038-BA76-0C957464411A}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE714A94-C7D9-4203-913D-E82693A2B152}">
-  <dimension ref="B2:N54"/>
+  <dimension ref="B2:N57"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.1796875" customWidth="1"/>
@@ -2440,7 +3864,7 @@
         <v>0</v>
       </c>
       <c r="M2" s="1">
-        <v>413</v>
+        <v>528</v>
       </c>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.25">
@@ -2466,10 +3890,10 @@
         <v>1</v>
       </c>
       <c r="M3" s="2">
-        <v>258</v>
+        <v>253.80500000000001</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>352</v>
+        <v>387</v>
       </c>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.25">
@@ -2496,7 +3920,7 @@
       </c>
       <c r="M4" s="2">
         <f>+M3*M2</f>
-        <v>106554</v>
+        <v>134009.04</v>
       </c>
       <c r="N4" s="3"/>
     </row>
@@ -2520,10 +3944,10 @@
         <v>3</v>
       </c>
       <c r="M5" s="2">
-        <v>12010</v>
+        <v>13000</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>352</v>
+        <v>387</v>
       </c>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.25">
@@ -2555,7 +3979,7 @@
         <v>0</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>352</v>
+        <v>387</v>
       </c>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.25">
@@ -2579,7 +4003,7 @@
       </c>
       <c r="M7" s="2">
         <f>+M4-M5+M6</f>
-        <v>94544</v>
+        <v>121009.04000000001</v>
       </c>
       <c r="N7" s="3"/>
     </row>
@@ -2636,7 +4060,7 @@
         <v>40</v>
       </c>
       <c r="F11" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H11" s="8"/>
       <c r="J11" t="s">
@@ -2645,19 +4069,19 @@
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B12" s="16" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C12" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D12" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E12" t="s">
         <v>361</v>
       </c>
       <c r="F12" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="H12" s="8"/>
       <c r="J12" t="s">
@@ -2669,7 +4093,7 @@
         <v>47</v>
       </c>
       <c r="C13" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D13" t="s">
         <v>48</v>
@@ -2699,7 +4123,7 @@
         <v>45</v>
       </c>
       <c r="F14" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="H14" s="8" t="s">
         <v>42</v>
@@ -2728,7 +4152,7 @@
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B16" s="7" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D16" t="s">
         <v>43</v>
@@ -2782,10 +4206,10 @@
         <v>329</v>
       </c>
       <c r="E19" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="F19" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="H19" s="8" t="s">
         <v>331</v>
@@ -2793,13 +4217,13 @@
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="D20" t="s">
         <v>375</v>
       </c>
-      <c r="D20" t="s">
-        <v>376</v>
-      </c>
       <c r="E20" t="s">
-        <v>50</v>
+        <v>409</v>
       </c>
       <c r="F20" t="s">
         <v>102</v>
@@ -2814,189 +4238,226 @@
         <v>332</v>
       </c>
       <c r="F21" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H21" s="8"/>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="7"/>
+      <c r="B22" s="7" t="s">
+        <v>411</v>
+      </c>
       <c r="D22" t="s">
+        <v>375</v>
+      </c>
+      <c r="E22" t="s">
+        <v>409</v>
+      </c>
+      <c r="H22" s="8"/>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="D23" t="s">
+        <v>375</v>
+      </c>
+      <c r="E23" t="s">
+        <v>409</v>
+      </c>
+      <c r="H23" s="8"/>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="7"/>
+      <c r="D24" t="s">
         <v>52</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E24" t="s">
         <v>46</v>
       </c>
-      <c r="F22" t="s">
-        <v>386</v>
-      </c>
-      <c r="H22" s="8"/>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="7"/>
-      <c r="D23" t="s">
+      <c r="F24" t="s">
+        <v>384</v>
+      </c>
+      <c r="H24" s="8"/>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="7"/>
+      <c r="D25" t="s">
+        <v>43</v>
+      </c>
+      <c r="E25" t="s">
+        <v>415</v>
+      </c>
+      <c r="H25" s="8"/>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="7"/>
+      <c r="D26" t="s">
         <v>123</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E26" t="s">
         <v>46</v>
       </c>
-      <c r="H23" s="8" t="s">
+      <c r="H26" s="8" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="27" t="s">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="27" t="s">
         <v>292</v>
       </c>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9" t="s">
+      <c r="C27" s="9"/>
+      <c r="D27" s="9" t="s">
         <v>293</v>
       </c>
-      <c r="E24" s="9" t="s">
+      <c r="E27" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="F24" s="9" t="s">
+      <c r="F27" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="G24" s="9"/>
-      <c r="H24" s="10"/>
-    </row>
-    <row r="26" spans="2:8" ht="13" x14ac:dyDescent="0.3">
-      <c r="B26" t="s">
+      <c r="G27" s="9"/>
+      <c r="H27" s="10"/>
+    </row>
+    <row r="29" spans="2:8" ht="13" x14ac:dyDescent="0.3">
+      <c r="B29" t="s">
         <v>314</v>
       </c>
-      <c r="E26" s="17" t="s">
+      <c r="E29" s="17" t="s">
         <v>345</v>
-      </c>
-    </row>
-    <row r="27" spans="2:8" ht="13" x14ac:dyDescent="0.3">
-      <c r="B27" t="s">
-        <v>374</v>
-      </c>
-      <c r="E27" s="17" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="28" spans="2:8" ht="13" x14ac:dyDescent="0.3">
-      <c r="B28" t="s">
-        <v>378</v>
-      </c>
-      <c r="E28" s="17" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="29" spans="2:8" ht="13" x14ac:dyDescent="0.3">
-      <c r="E29" s="17" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="30" spans="2:8" ht="13" x14ac:dyDescent="0.3">
       <c r="E30" s="17" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8" ht="13" x14ac:dyDescent="0.3">
+      <c r="B31" t="s">
+        <v>410</v>
+      </c>
+      <c r="E31" s="17" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8" ht="13" x14ac:dyDescent="0.3">
+      <c r="B32" t="s">
+        <v>414</v>
+      </c>
+      <c r="E32" s="17" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" ht="13" x14ac:dyDescent="0.3">
+      <c r="B33" t="s">
+        <v>416</v>
+      </c>
+      <c r="E33" s="17" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="31" spans="2:8" ht="13" x14ac:dyDescent="0.3">
-      <c r="E31" s="17" t="s">
+    <row r="34" spans="2:5" ht="13" x14ac:dyDescent="0.3">
+      <c r="E34" s="17" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="32" spans="2:8" ht="13" x14ac:dyDescent="0.3">
-      <c r="E32" s="17" t="s">
+    <row r="35" spans="2:5" ht="13" x14ac:dyDescent="0.3">
+      <c r="E35" s="17" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="33" spans="5:5" ht="13" x14ac:dyDescent="0.3">
-      <c r="E33" s="17" t="s">
+    <row r="36" spans="2:5" ht="13" x14ac:dyDescent="0.3">
+      <c r="E36" s="17" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="34" spans="5:5" ht="13" x14ac:dyDescent="0.3">
-      <c r="E34" s="17" t="s">
+    <row r="37" spans="2:5" ht="13" x14ac:dyDescent="0.3">
+      <c r="E37" s="17" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="35" spans="5:5" ht="13" x14ac:dyDescent="0.3">
-      <c r="E35" s="17" t="s">
+    <row r="38" spans="2:5" ht="13" x14ac:dyDescent="0.3">
+      <c r="E38" s="17" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="36" spans="5:5" ht="13" x14ac:dyDescent="0.3">
-      <c r="E36" s="17" t="s">
+    <row r="39" spans="2:5" ht="13" x14ac:dyDescent="0.3">
+      <c r="E39" s="17" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="37" spans="5:5" ht="13" x14ac:dyDescent="0.3">
-      <c r="E37" s="17" t="s">
+    <row r="40" spans="2:5" ht="13" x14ac:dyDescent="0.3">
+      <c r="E40" s="17" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="38" spans="5:5" ht="13" x14ac:dyDescent="0.3">
-      <c r="E38" s="17" t="s">
+    <row r="41" spans="2:5" ht="13" x14ac:dyDescent="0.3">
+      <c r="E41" s="17" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="39" spans="5:5" ht="13" x14ac:dyDescent="0.3">
-      <c r="E39" s="17" t="s">
+    <row r="42" spans="2:5" ht="13" x14ac:dyDescent="0.3">
+      <c r="E42" s="17" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="40" spans="5:5" ht="13" x14ac:dyDescent="0.3">
-      <c r="E40" s="17" t="s">
+    <row r="43" spans="2:5" ht="13" x14ac:dyDescent="0.3">
+      <c r="E43" s="17" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="41" spans="5:5" ht="13" x14ac:dyDescent="0.3">
-      <c r="E41" s="17" t="s">
+    <row r="44" spans="2:5" ht="13" x14ac:dyDescent="0.3">
+      <c r="E44" s="17" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="42" spans="5:5" ht="13" x14ac:dyDescent="0.3">
-      <c r="E42" s="17" t="s">
+    <row r="45" spans="2:5" ht="13" x14ac:dyDescent="0.3">
+      <c r="E45" s="17" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="43" spans="5:5" ht="13" x14ac:dyDescent="0.3">
-      <c r="E43" s="17" t="s">
+    <row r="46" spans="2:5" ht="13" x14ac:dyDescent="0.3">
+      <c r="E46" s="17" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="44" spans="5:5" ht="13" x14ac:dyDescent="0.3">
-      <c r="E44" s="17" t="s">
+    <row r="47" spans="2:5" ht="13" x14ac:dyDescent="0.3">
+      <c r="E47" s="17" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="45" spans="5:5" ht="13" x14ac:dyDescent="0.3">
-      <c r="E45" s="17" t="s">
+    <row r="48" spans="2:5" ht="13" x14ac:dyDescent="0.3">
+      <c r="E48" s="17" t="s">
         <v>243</v>
-      </c>
-    </row>
-    <row r="46" spans="5:5" ht="13" x14ac:dyDescent="0.3">
-      <c r="E46" s="17" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="47" spans="5:5" ht="13" x14ac:dyDescent="0.3">
-      <c r="E47" s="17" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="48" spans="5:5" ht="13" x14ac:dyDescent="0.3">
-      <c r="E48" s="17" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="49" spans="5:5" ht="13" x14ac:dyDescent="0.3">
       <c r="E49" s="17" t="s">
-        <v>247</v>
+        <v>244</v>
+      </c>
+    </row>
+    <row r="50" spans="5:5" ht="13" x14ac:dyDescent="0.3">
+      <c r="E50" s="17" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="51" spans="5:5" ht="13" x14ac:dyDescent="0.3">
       <c r="E51" s="17" t="s">
-        <v>362</v>
+        <v>246</v>
+      </c>
+    </row>
+    <row r="52" spans="5:5" ht="13" x14ac:dyDescent="0.3">
+      <c r="E52" s="17" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="54" spans="5:5" ht="13" x14ac:dyDescent="0.3">
       <c r="E54" s="17" t="s">
-        <v>408</v>
+        <v>362</v>
+      </c>
+    </row>
+    <row r="57" spans="5:5" ht="13" x14ac:dyDescent="0.3">
+      <c r="E57" s="17" t="s">
+        <v>406</v>
       </c>
     </row>
   </sheetData>
@@ -3008,7 +4469,7 @@
     <hyperlink ref="B11" location="inaxaplin!A1" display="VX-147" xr:uid="{362A6FBB-2244-4147-8746-8E7FC462FB02}"/>
     <hyperlink ref="B7" location="Casgevy!A1" display="Casgevy" xr:uid="{EE1FBA3F-8223-4960-A117-1323E22DA27E}"/>
     <hyperlink ref="B5" location="Orkambi!A1" display="Orkambi" xr:uid="{5B227DE1-747D-41D9-AFFC-27BF0DF44345}"/>
-    <hyperlink ref="B24" location="'VX-634'!A1" display="VX-634" xr:uid="{28A7C8E1-14DE-4193-86D6-B95B3E551AF5}"/>
+    <hyperlink ref="B27" location="'VX-634'!A1" display="VX-634" xr:uid="{28A7C8E1-14DE-4193-86D6-B95B3E551AF5}"/>
     <hyperlink ref="B8" location="Alyftrek!A1" display="Alyftrek" xr:uid="{ECC6416F-1E64-4473-A6C6-D23E81B80E70}"/>
     <hyperlink ref="B9" location="'VX-548'!A1" display="VX-548" xr:uid="{67203671-9821-4D42-B3BF-32EA7ACD3A76}"/>
     <hyperlink ref="B12" location="povetacicept!A1" display="ALPN-303" xr:uid="{E8DF8A0B-F5F3-4133-992E-15093D7ABE34}"/>
@@ -3018,1292 +4479,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF238714-88C7-42B3-B2FD-3531313A58EB}">
-  <dimension ref="A1:N14"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.81640625" customWidth="1"/>
-    <col min="3" max="3" width="12.26953125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>359</v>
-      </c>
-      <c r="H2" s="20"/>
-      <c r="N2" s="8"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>116</v>
-      </c>
-      <c r="C5" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="13" x14ac:dyDescent="0.3">
-      <c r="C7" s="18" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C8" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="13" x14ac:dyDescent="0.3">
-      <c r="C10" s="18" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="13" x14ac:dyDescent="0.3">
-      <c r="C14" s="18" t="s">
-        <v>317</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{D27BB88E-1A8F-41E5-B99C-BA493095DC2C}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11AB47AF-768E-4B06-9E84-BC4ABCFB8ABD}">
-  <dimension ref="A1:E40"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.26953125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>230</v>
-      </c>
-      <c r="C6" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>337</v>
-      </c>
-      <c r="C7" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
-        <v>387</v>
-      </c>
-      <c r="C8" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="13" x14ac:dyDescent="0.3">
-      <c r="C10" s="18" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C11" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="13" x14ac:dyDescent="0.3">
-      <c r="C13" s="18" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="17" spans="3:5" ht="13" x14ac:dyDescent="0.3">
-      <c r="C17" s="18" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="18" spans="3:5" ht="13" x14ac:dyDescent="0.3">
-      <c r="C18" s="18"/>
-      <c r="D18" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="19" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C19" t="s">
-        <v>231</v>
-      </c>
-      <c r="D19" s="22">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="20" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C20" t="s">
-        <v>233</v>
-      </c>
-      <c r="D20" s="22">
-        <v>137.80000000000001</v>
-      </c>
-      <c r="E20" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="21" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C21" t="s">
-        <v>235</v>
-      </c>
-      <c r="D21" s="22">
-        <v>86.9</v>
-      </c>
-      <c r="E21" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="22" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C22" t="s">
-        <v>236</v>
-      </c>
-      <c r="D22" s="22">
-        <v>112.9</v>
-      </c>
-      <c r="E22" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="23" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C23" t="s">
-        <v>237</v>
-      </c>
-      <c r="D23" s="22">
-        <v>115.6</v>
-      </c>
-      <c r="E23" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="24" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D24" s="22"/>
-    </row>
-    <row r="25" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D25" s="22"/>
-    </row>
-    <row r="26" spans="3:5" ht="13" x14ac:dyDescent="0.3">
-      <c r="C26" s="18" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="27" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="D27" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="28" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C28" t="s">
-        <v>231</v>
-      </c>
-      <c r="D28">
-        <v>72.7</v>
-      </c>
-    </row>
-    <row r="29" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C29" t="s">
-        <v>233</v>
-      </c>
-      <c r="D29">
-        <v>110.5</v>
-      </c>
-      <c r="E29" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="30" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C30" t="s">
-        <v>235</v>
-      </c>
-      <c r="D30">
-        <v>95.1</v>
-      </c>
-      <c r="E30" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="31" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C31" t="s">
-        <v>237</v>
-      </c>
-      <c r="D31">
-        <v>85.2</v>
-      </c>
-      <c r="E31" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="33" spans="3:3" ht="13" x14ac:dyDescent="0.3">
-      <c r="C33" s="18" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="35" spans="3:3" ht="13" x14ac:dyDescent="0.3">
-      <c r="C35" s="18" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="38" spans="3:3" ht="13" x14ac:dyDescent="0.3">
-      <c r="C38" s="18" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="39" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C39" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="40" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C40" t="s">
-        <v>336</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{9F1444FB-1FC7-4AF6-9D19-F860F1DDD4D6}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CA6AB23-686C-478E-AA6A-03F37C9331A3}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.81640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>129</v>
-      </c>
-      <c r="C4" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="13" x14ac:dyDescent="0.3">
-      <c r="C6" s="18" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C7" t="s">
-        <v>321</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{C0D50ABE-2133-4DD7-AC00-5588FBC472DA}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3500169-374E-454F-AD84-2EA69EF52EB1}">
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="13" x14ac:dyDescent="0.3">
-      <c r="C7" s="18" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C8" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C9" t="s">
-        <v>325</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{8E17983A-F281-41DE-94AE-3C971B03D303}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECE9D23D-12F6-4A5D-93D1-1862668A41BC}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.81640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>116</v>
-      </c>
-      <c r="C4" t="s">
-        <v>294</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{0A34DDFA-7AD8-4524-8897-4C2FF35B4CE5}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEF0003B-178C-466F-BE10-E90BCC8A1B78}">
-  <dimension ref="A1:I24"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.81640625" customWidth="1"/>
-    <col min="7" max="8" width="10.1796875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H2" t="s">
-        <v>72</v>
-      </c>
-      <c r="I2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B3">
-        <v>11390600</v>
-      </c>
-      <c r="C3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E3" t="s">
-        <v>65</v>
-      </c>
-      <c r="F3">
-        <v>2</v>
-      </c>
-      <c r="G3" s="15">
-        <v>44019</v>
-      </c>
-      <c r="H3" s="15">
-        <v>44761</v>
-      </c>
-      <c r="I3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B4">
-        <v>11370798</v>
-      </c>
-      <c r="C4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D4" t="s">
-        <v>73</v>
-      </c>
-      <c r="E4" t="s">
-        <v>74</v>
-      </c>
-      <c r="F4">
-        <v>2</v>
-      </c>
-      <c r="G4" s="15">
-        <v>44074</v>
-      </c>
-      <c r="H4" s="15">
-        <v>44740</v>
-      </c>
-      <c r="I4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B5">
-        <v>11369692</v>
-      </c>
-      <c r="C5" t="s">
-        <v>78</v>
-      </c>
-      <c r="D5" t="s">
-        <v>73</v>
-      </c>
-      <c r="E5" t="s">
-        <v>79</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
-      <c r="G5" s="15">
-        <v>42671</v>
-      </c>
-      <c r="H5" s="15">
-        <v>44740</v>
-      </c>
-      <c r="I5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B6">
-        <v>11358977</v>
-      </c>
-      <c r="C6" t="s">
-        <v>81</v>
-      </c>
-      <c r="D6" t="s">
-        <v>73</v>
-      </c>
-      <c r="E6" t="s">
-        <v>82</v>
-      </c>
-      <c r="F6">
-        <v>8</v>
-      </c>
-      <c r="G6" s="15">
-        <v>43236</v>
-      </c>
-      <c r="H6" s="15">
-        <v>44726</v>
-      </c>
-      <c r="I6" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B7">
-        <v>11345700</v>
-      </c>
-      <c r="C7" t="s">
-        <v>84</v>
-      </c>
-      <c r="D7" t="s">
-        <v>73</v>
-      </c>
-      <c r="E7" t="s">
-        <v>83</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7" s="15">
-        <v>43899</v>
-      </c>
-      <c r="H7" s="15">
-        <v>44712</v>
-      </c>
-      <c r="I7" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B8">
-        <v>11291662</v>
-      </c>
-      <c r="C8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D8" t="s">
-        <v>73</v>
-      </c>
-      <c r="E8" t="s">
-        <v>87</v>
-      </c>
-      <c r="F8">
-        <v>3</v>
-      </c>
-      <c r="G8" s="15">
-        <v>43804</v>
-      </c>
-      <c r="H8" s="15">
-        <v>44656</v>
-      </c>
-      <c r="I8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B9">
-        <v>11268077</v>
-      </c>
-      <c r="C9" t="s">
-        <v>90</v>
-      </c>
-      <c r="D9" t="s">
-        <v>73</v>
-      </c>
-      <c r="E9" t="s">
-        <v>91</v>
-      </c>
-      <c r="F9">
-        <v>5</v>
-      </c>
-      <c r="G9" s="15">
-        <v>43501</v>
-      </c>
-      <c r="H9" s="15">
-        <v>44628</v>
-      </c>
-      <c r="I9" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B10">
-        <v>11253509</v>
-      </c>
-      <c r="C10" t="s">
-        <v>93</v>
-      </c>
-      <c r="D10" t="s">
-        <v>73</v>
-      </c>
-      <c r="E10" t="s">
-        <v>94</v>
-      </c>
-      <c r="F10">
-        <v>2</v>
-      </c>
-      <c r="G10" s="15">
-        <v>43259</v>
-      </c>
-      <c r="H10" s="15">
-        <v>44614</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B11">
-        <v>11203571</v>
-      </c>
-      <c r="C11" t="s">
-        <v>195</v>
-      </c>
-      <c r="D11" t="s">
-        <v>73</v>
-      </c>
-      <c r="E11" t="s">
-        <v>196</v>
-      </c>
-      <c r="F11">
-        <v>8</v>
-      </c>
-      <c r="G11" s="15">
-        <v>41835</v>
-      </c>
-      <c r="H11" s="15">
-        <v>44551</v>
-      </c>
-      <c r="I11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B12">
-        <v>11186566</v>
-      </c>
-      <c r="C12" t="s">
-        <v>197</v>
-      </c>
-      <c r="D12" t="s">
-        <v>73</v>
-      </c>
-      <c r="E12" t="s">
-        <v>198</v>
-      </c>
-      <c r="F12">
-        <v>6</v>
-      </c>
-      <c r="G12" s="15">
-        <v>43803</v>
-      </c>
-      <c r="H12" s="15">
-        <v>44530</v>
-      </c>
-      <c r="I12" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B13">
-        <v>11179394</v>
-      </c>
-      <c r="C13" t="s">
-        <v>200</v>
-      </c>
-      <c r="D13" t="s">
-        <v>73</v>
-      </c>
-      <c r="E13" t="s">
-        <v>201</v>
-      </c>
-      <c r="F13">
-        <v>3</v>
-      </c>
-      <c r="G13" s="15">
-        <v>42172</v>
-      </c>
-      <c r="H13" s="15">
-        <v>44523</v>
-      </c>
-      <c r="I13" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B14">
-        <v>11179367</v>
-      </c>
-      <c r="C14" t="s">
-        <v>203</v>
-      </c>
-      <c r="D14" t="s">
-        <v>73</v>
-      </c>
-      <c r="E14" t="s">
-        <v>204</v>
-      </c>
-      <c r="F14">
-        <v>2</v>
-      </c>
-      <c r="G14" s="15">
-        <v>43500</v>
-      </c>
-      <c r="H14" s="15">
-        <v>44523</v>
-      </c>
-      <c r="I14" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B15">
-        <v>11155533</v>
-      </c>
-      <c r="C15" t="s">
-        <v>206</v>
-      </c>
-      <c r="D15" t="s">
-        <v>73</v>
-      </c>
-      <c r="E15" t="s">
-        <v>207</v>
-      </c>
-      <c r="F15">
-        <v>2</v>
-      </c>
-      <c r="G15" s="15">
-        <v>43915</v>
-      </c>
-      <c r="H15" s="15">
-        <v>44495</v>
-      </c>
-      <c r="I15" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B16">
-        <v>11147770</v>
-      </c>
-      <c r="C16" t="s">
-        <v>209</v>
-      </c>
-      <c r="D16" t="s">
-        <v>73</v>
-      </c>
-      <c r="E16" t="s">
-        <v>210</v>
-      </c>
-      <c r="F16">
-        <v>2</v>
-      </c>
-      <c r="G16" s="15">
-        <v>43536</v>
-      </c>
-      <c r="H16" s="15">
-        <v>44488</v>
-      </c>
-      <c r="I16" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B17">
-        <v>11124805</v>
-      </c>
-      <c r="C17" t="s">
-        <v>211</v>
-      </c>
-      <c r="D17" t="s">
-        <v>73</v>
-      </c>
-      <c r="E17" t="s">
-        <v>212</v>
-      </c>
-      <c r="F17">
-        <v>7</v>
-      </c>
-      <c r="G17" s="15">
-        <v>42929</v>
-      </c>
-      <c r="H17" s="15">
-        <v>44460</v>
-      </c>
-      <c r="I17" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B18">
-        <v>11117900</v>
-      </c>
-      <c r="C18" t="s">
-        <v>70</v>
-      </c>
-      <c r="D18" t="s">
-        <v>73</v>
-      </c>
-      <c r="E18" t="s">
-        <v>74</v>
-      </c>
-      <c r="F18">
-        <v>3</v>
-      </c>
-      <c r="G18" s="15">
-        <v>43683</v>
-      </c>
-      <c r="H18" s="15">
-        <v>44453</v>
-      </c>
-    </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B19">
-        <v>11110108</v>
-      </c>
-      <c r="C19" t="s">
-        <v>214</v>
-      </c>
-      <c r="D19" t="s">
-        <v>73</v>
-      </c>
-      <c r="E19" t="s">
-        <v>215</v>
-      </c>
-      <c r="F19">
-        <v>2</v>
-      </c>
-      <c r="G19" s="15">
-        <v>43005</v>
-      </c>
-      <c r="H19" s="15">
-        <v>44446</v>
-      </c>
-    </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B20">
-        <v>11110086</v>
-      </c>
-      <c r="C20" t="s">
-        <v>216</v>
-      </c>
-      <c r="D20" t="s">
-        <v>73</v>
-      </c>
-      <c r="E20" t="s">
-        <v>217</v>
-      </c>
-      <c r="F20">
-        <v>3</v>
-      </c>
-      <c r="G20" s="15">
-        <v>43656</v>
-      </c>
-      <c r="H20" s="15">
-        <v>44446</v>
-      </c>
-    </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B21">
-        <v>11084804</v>
-      </c>
-      <c r="C21" t="s">
-        <v>218</v>
-      </c>
-      <c r="D21" t="s">
-        <v>73</v>
-      </c>
-      <c r="E21" t="s">
-        <v>219</v>
-      </c>
-      <c r="F21">
-        <v>5</v>
-      </c>
-      <c r="G21" s="15">
-        <v>43874</v>
-      </c>
-      <c r="H21" s="15">
-        <v>44418</v>
-      </c>
-      <c r="I21" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B22">
-        <v>11066417</v>
-      </c>
-      <c r="C22" t="s">
-        <v>221</v>
-      </c>
-      <c r="D22" t="s">
-        <v>73</v>
-      </c>
-      <c r="E22" t="s">
-        <v>220</v>
-      </c>
-      <c r="F22">
-        <v>6</v>
-      </c>
-      <c r="G22" s="15">
-        <v>43510</v>
-      </c>
-      <c r="H22" s="15">
-        <v>44397</v>
-      </c>
-    </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B23">
-        <v>11059826</v>
-      </c>
-      <c r="C23" t="s">
-        <v>222</v>
-      </c>
-      <c r="D23" t="s">
-        <v>73</v>
-      </c>
-      <c r="E23" t="s">
-        <v>223</v>
-      </c>
-      <c r="F23">
-        <v>5</v>
-      </c>
-      <c r="G23" s="15">
-        <v>43578</v>
-      </c>
-      <c r="H23" s="15">
-        <v>44390</v>
-      </c>
-      <c r="I23" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B24">
-        <v>11052075</v>
-      </c>
-      <c r="C24" t="s">
-        <v>225</v>
-      </c>
-      <c r="D24" t="s">
-        <v>73</v>
-      </c>
-      <c r="E24" t="s">
-        <v>226</v>
-      </c>
-      <c r="G24" s="15">
-        <v>43679</v>
-      </c>
-      <c r="H24" s="15">
-        <v>44383</v>
-      </c>
-      <c r="I24" t="s">
-        <v>205</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{28B9CEB8-4D0A-4224-9448-513A0C99A972}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4728C55-E312-4CB5-A877-7A6998D5236F}">
-  <dimension ref="A1:F13"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.26953125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C3" t="s">
-        <v>95</v>
-      </c>
-      <c r="D3" t="s">
-        <v>97</v>
-      </c>
-      <c r="E3" t="s">
-        <v>96</v>
-      </c>
-      <c r="F3" s="15">
-        <v>40686</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>108</v>
-      </c>
-      <c r="C4" t="s">
-        <v>107</v>
-      </c>
-      <c r="D4" t="s">
-        <v>109</v>
-      </c>
-      <c r="E4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="15">
-        <v>42187</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>112</v>
-      </c>
-      <c r="C5" t="s">
-        <v>111</v>
-      </c>
-      <c r="E5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" t="s">
-        <v>113</v>
-      </c>
-      <c r="E6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>103</v>
-      </c>
-      <c r="D9" t="s">
-        <v>105</v>
-      </c>
-      <c r="E9" t="s">
-        <v>96</v>
-      </c>
-      <c r="F9" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
-        <v>104</v>
-      </c>
-      <c r="D10" t="s">
-        <v>105</v>
-      </c>
-      <c r="E10" t="s">
-        <v>96</v>
-      </c>
-      <c r="F10" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
-        <v>67</v>
-      </c>
-      <c r="C11" t="s">
-        <v>68</v>
-      </c>
-      <c r="D11" t="s">
-        <v>69</v>
-      </c>
-      <c r="E11" t="s">
-        <v>106</v>
-      </c>
-      <c r="F11" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
-        <v>248</v>
-      </c>
-      <c r="D12" t="s">
-        <v>44</v>
-      </c>
-      <c r="E12" t="s">
-        <v>43</v>
-      </c>
-      <c r="F12" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
-        <v>100</v>
-      </c>
-      <c r="D13" t="s">
-        <v>101</v>
-      </c>
-      <c r="E13" t="s">
-        <v>96</v>
-      </c>
-      <c r="F13" t="s">
-        <v>102</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{BFCC45F9-5F22-4038-BA76-0C957464411A}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4E8267B-C4D8-4F55-9938-4004F5DC3025}">
   <dimension ref="A1:DT80"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
@@ -4414,16 +4590,16 @@
         <v>353</v>
       </c>
       <c r="AG2" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="AH2" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="AI2" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="AH2" s="3" t="s">
+      <c r="AJ2" s="3" t="s">
         <v>390</v>
-      </c>
-      <c r="AI2" s="3" t="s">
-        <v>391</v>
-      </c>
-      <c r="AJ2" s="3" t="s">
-        <v>392</v>
       </c>
       <c r="AK2" s="3"/>
       <c r="AM2">
@@ -4534,9 +4710,7 @@
       <c r="B3" t="s">
         <v>47</v>
       </c>
-      <c r="AX3" s="2">
-        <v>200</v>
-      </c>
+      <c r="AX3" s="2"/>
       <c r="AY3" s="2">
         <v>800</v>
       </c>
@@ -4614,7 +4788,7 @@
       <c r="T4" s="12"/>
       <c r="U4" s="12"/>
       <c r="AC4" s="2">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD4" s="2">
         <v>12</v>
@@ -4623,14 +4797,30 @@
         <v>19.600000000000001</v>
       </c>
       <c r="AF4" s="2">
-        <v>50</v>
+        <v>26.7</v>
+      </c>
+      <c r="AG4" s="2">
+        <v>29</v>
+      </c>
+      <c r="AH4" s="2">
+        <f>+AG4+2</f>
+        <v>31</v>
+      </c>
+      <c r="AI4" s="2">
+        <f>+AH4+2</f>
+        <v>33</v>
+      </c>
+      <c r="AJ4" s="2">
+        <f>+AI4+2</f>
+        <v>35</v>
       </c>
       <c r="AW4" s="2">
-        <f>SUM(AC4:AF4)</f>
-        <v>81.599999999999994</v>
+        <f t="shared" ref="AW4:AW7" si="12">SUM(AD4:AG4)</f>
+        <v>87.3</v>
       </c>
       <c r="AX4" s="2">
-        <v>200</v>
+        <f>SUM(AG4:AJ4)</f>
+        <v>128</v>
       </c>
       <c r="AY4" s="2">
         <v>400</v>
@@ -4650,15 +4840,15 @@
         <v>816.08</v>
       </c>
       <c r="BD4" s="2">
-        <f t="shared" ref="BD4:BF5" si="12">+BC4*1.01</f>
+        <f t="shared" ref="BD4:BF5" si="13">+BC4*1.01</f>
         <v>824.24080000000004</v>
       </c>
       <c r="BE4" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>832.48320799999999</v>
       </c>
       <c r="BF4" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>840.80804007999996</v>
       </c>
       <c r="BG4" s="2">
@@ -4682,13 +4872,13 @@
         <v>883.69770032896361</v>
       </c>
       <c r="BL4" s="2">
-        <f t="shared" ref="BL4" si="13">+BK4*0.1</f>
+        <f t="shared" ref="BL4" si="14">+BK4*0.1</f>
         <v>88.369770032896369</v>
       </c>
     </row>
     <row r="5" spans="1:64" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C5" s="12"/>
       <c r="D5" s="12"/>
@@ -4726,19 +4916,19 @@
         <v>909</v>
       </c>
       <c r="BC5" s="2">
-        <f t="shared" ref="BC5" si="14">+BB5*1.01</f>
+        <f t="shared" ref="BC5" si="15">+BB5*1.01</f>
         <v>918.09</v>
       </c>
       <c r="BD5" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>927.2709000000001</v>
       </c>
       <c r="BE5" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>936.54360900000006</v>
       </c>
       <c r="BF5" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>945.90904509000006</v>
       </c>
       <c r="BG5" s="2">
@@ -4762,7 +4952,7 @@
         <v>994.15991287008421</v>
       </c>
       <c r="BL5" s="2">
-        <f t="shared" ref="BL5" si="15">+BK5*1.01</f>
+        <f t="shared" ref="BL5" si="16">+BK5*1.01</f>
         <v>1004.1015119987851</v>
       </c>
     </row>
@@ -4823,72 +5013,86 @@
         <v>16.899999999999999</v>
       </c>
       <c r="AF7" s="2">
-        <f>+AE7+5</f>
-        <v>21.9</v>
+        <v>54.3</v>
+      </c>
+      <c r="AG7" s="2">
+        <v>42.9</v>
+      </c>
+      <c r="AH7" s="2">
+        <f>+AG7+5</f>
+        <v>47.9</v>
+      </c>
+      <c r="AI7" s="2">
+        <f>+AH7+5</f>
+        <v>52.9</v>
+      </c>
+      <c r="AJ7" s="2">
+        <f>+AI7+5</f>
+        <v>57.9</v>
       </c>
       <c r="AW7" s="2">
-        <f>SUM(AC7:AF7)</f>
-        <v>83.399999999999991</v>
+        <f t="shared" ref="AW7:AW13" si="17">SUM(AD7:AG7)</f>
+        <v>144.5</v>
       </c>
       <c r="AX7" s="2">
-        <f>+AW7*1.01</f>
-        <v>84.233999999999995</v>
+        <f>SUM(AG7:AJ7)</f>
+        <v>201.6</v>
       </c>
       <c r="AY7" s="2">
-        <f t="shared" ref="AY7:BL7" si="16">+AX7*1.01</f>
-        <v>85.076340000000002</v>
+        <f t="shared" ref="AY7:BL7" si="18">+AX7*1.01</f>
+        <v>203.61599999999999</v>
       </c>
       <c r="AZ7" s="2">
-        <f t="shared" si="16"/>
-        <v>85.927103400000007</v>
+        <f t="shared" si="18"/>
+        <v>205.65215999999998</v>
       </c>
       <c r="BA7" s="2">
-        <f t="shared" si="16"/>
-        <v>86.78637443400001</v>
+        <f t="shared" si="18"/>
+        <v>207.70868159999998</v>
       </c>
       <c r="BB7" s="2">
-        <f t="shared" si="16"/>
-        <v>87.654238178340009</v>
+        <f t="shared" si="18"/>
+        <v>209.78576841599997</v>
       </c>
       <c r="BC7" s="2">
-        <f t="shared" si="16"/>
-        <v>88.530780560123404</v>
+        <f t="shared" si="18"/>
+        <v>211.88362610015997</v>
       </c>
       <c r="BD7" s="2">
-        <f t="shared" si="16"/>
-        <v>89.416088365724633</v>
+        <f t="shared" si="18"/>
+        <v>214.00246236116158</v>
       </c>
       <c r="BE7" s="2">
-        <f t="shared" si="16"/>
-        <v>90.310249249381883</v>
+        <f t="shared" si="18"/>
+        <v>216.1424869847732</v>
       </c>
       <c r="BF7" s="2">
-        <f t="shared" si="16"/>
-        <v>91.213351741875698</v>
+        <f t="shared" si="18"/>
+        <v>218.30391185462094</v>
       </c>
       <c r="BG7" s="2">
-        <f t="shared" si="16"/>
-        <v>92.12548525929445</v>
+        <f t="shared" si="18"/>
+        <v>220.48695097316715</v>
       </c>
       <c r="BH7" s="2">
-        <f t="shared" si="16"/>
-        <v>93.046740111887402</v>
+        <f t="shared" si="18"/>
+        <v>222.69182048289883</v>
       </c>
       <c r="BI7" s="2">
-        <f t="shared" si="16"/>
-        <v>93.977207513006277</v>
+        <f t="shared" si="18"/>
+        <v>224.91873868772782</v>
       </c>
       <c r="BJ7" s="2">
-        <f t="shared" si="16"/>
-        <v>94.916979588136343</v>
+        <f t="shared" si="18"/>
+        <v>227.16792607460511</v>
       </c>
       <c r="BK7" s="2">
-        <f t="shared" si="16"/>
-        <v>95.866149384017703</v>
+        <f t="shared" si="18"/>
+        <v>229.43960533535116</v>
       </c>
       <c r="BL7" s="2">
-        <f t="shared" si="16"/>
-        <v>96.824810877857885</v>
+        <f t="shared" si="18"/>
+        <v>231.73400138870468</v>
       </c>
     </row>
     <row r="8" spans="1:64" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4932,8 +5136,31 @@
         <v>139.30000000000001</v>
       </c>
       <c r="AF8" s="2">
-        <f>+AE8</f>
-        <v>139.30000000000001</v>
+        <f>237.4-AF7-AF4</f>
+        <v>156.40000000000003</v>
+      </c>
+      <c r="AG8" s="2">
+        <v>135.9</v>
+      </c>
+      <c r="AH8" s="2">
+        <f>+AG8</f>
+        <v>135.9</v>
+      </c>
+      <c r="AI8" s="2">
+        <f>+AH8</f>
+        <v>135.9</v>
+      </c>
+      <c r="AJ8" s="2">
+        <f>+AI8</f>
+        <v>135.9</v>
+      </c>
+      <c r="AW8" s="2">
+        <f t="shared" si="17"/>
+        <v>452.30000000000007</v>
+      </c>
+      <c r="AX8" s="2">
+        <f t="shared" ref="AX8" si="19">SUM(AG8:AJ8)</f>
+        <v>543.6</v>
       </c>
     </row>
     <row r="9" spans="1:64" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4969,76 +5196,90 @@
         <v>247</v>
       </c>
       <c r="AF9" s="2">
-        <f>+AE9+50</f>
-        <v>297</v>
+        <v>380.1</v>
+      </c>
+      <c r="AG9" s="2">
+        <v>424.4</v>
+      </c>
+      <c r="AH9" s="2">
+        <f>+AG9+15</f>
+        <v>439.4</v>
+      </c>
+      <c r="AI9" s="2">
+        <f>+AH9+15</f>
+        <v>454.4</v>
+      </c>
+      <c r="AJ9" s="2">
+        <f>+AI9+15</f>
+        <v>469.4</v>
       </c>
       <c r="AV9" s="2">
-        <f t="shared" ref="AV9:AV14" si="17">SUM(Y9:AB9)</f>
+        <f t="shared" ref="AV9:AV19" si="20">SUM(Y9:AB9)</f>
         <v>0</v>
       </c>
       <c r="AW9" s="2">
-        <f>SUM(AC9:AF9)</f>
-        <v>754.7</v>
+        <f t="shared" si="17"/>
+        <v>1208.3000000000002</v>
       </c>
       <c r="AX9" s="2">
-        <f>+AW9*1.8</f>
-        <v>1358.46</v>
+        <f t="shared" ref="AX9" si="21">SUM(AG9:AJ9)</f>
+        <v>1787.6</v>
       </c>
       <c r="AY9" s="2">
         <f>+AX9*1.5</f>
-        <v>2037.69</v>
+        <v>2681.3999999999996</v>
       </c>
       <c r="AZ9" s="2">
         <f>+AY9*1.5</f>
-        <v>3056.5349999999999</v>
+        <v>4022.0999999999995</v>
       </c>
       <c r="BA9" s="2">
         <f>+AZ9*1.3</f>
-        <v>3973.4955</v>
+        <v>5228.7299999999996</v>
       </c>
       <c r="BB9" s="2">
         <f>+BA9*1.3</f>
-        <v>5165.5441499999997</v>
+        <v>6797.3489999999993</v>
       </c>
       <c r="BC9" s="2">
         <f>+BB9*1.15</f>
-        <v>5940.3757724999996</v>
+        <v>7816.9513499999985</v>
       </c>
       <c r="BD9" s="2">
         <f>+BC9*1.03</f>
-        <v>6118.5870456749999</v>
+        <v>8051.4598904999984</v>
       </c>
       <c r="BE9" s="2">
-        <f t="shared" ref="BE9:BK9" si="18">+BD9*1.03</f>
-        <v>6302.1446570452499</v>
+        <f t="shared" ref="BE9:BK9" si="22">+BD9*1.03</f>
+        <v>8293.0036872149994</v>
       </c>
       <c r="BF9" s="2">
-        <f t="shared" si="18"/>
-        <v>6491.208996756608</v>
+        <f t="shared" si="22"/>
+        <v>8541.7937978314494</v>
       </c>
       <c r="BG9" s="2">
-        <f t="shared" si="18"/>
-        <v>6685.9452666593061</v>
+        <f t="shared" si="22"/>
+        <v>8798.0476117663929</v>
       </c>
       <c r="BH9" s="2">
-        <f t="shared" si="18"/>
-        <v>6886.5236246590857</v>
+        <f t="shared" si="22"/>
+        <v>9061.9890401193843</v>
       </c>
       <c r="BI9" s="2">
-        <f t="shared" si="18"/>
-        <v>7093.1193333988585</v>
+        <f t="shared" si="22"/>
+        <v>9333.8487113229658</v>
       </c>
       <c r="BJ9" s="2">
-        <f t="shared" si="18"/>
-        <v>7305.9129134008244</v>
+        <f t="shared" si="22"/>
+        <v>9613.8641726626556</v>
       </c>
       <c r="BK9" s="2">
-        <f t="shared" si="18"/>
-        <v>7525.090300802849</v>
+        <f t="shared" si="22"/>
+        <v>9902.2800978425348</v>
       </c>
       <c r="BL9" s="2">
         <f>+BK9*0.5</f>
-        <v>3762.5451504014245</v>
+        <v>4951.1400489212674</v>
       </c>
     </row>
     <row r="10" spans="1:64" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5133,15 +5374,29 @@
         <v>2653.6</v>
       </c>
       <c r="AF10" s="2">
-        <f>+AB10</f>
-        <v>2720.8</v>
+        <v>2572.5</v>
+      </c>
+      <c r="AG10" s="2">
+        <v>2354.6999999999998</v>
+      </c>
+      <c r="AH10" s="2">
+        <f>+AG10</f>
+        <v>2354.6999999999998</v>
+      </c>
+      <c r="AI10" s="2">
+        <f>+AH10</f>
+        <v>2354.6999999999998</v>
+      </c>
+      <c r="AJ10" s="2">
+        <f>+AI10</f>
+        <v>2354.6999999999998</v>
       </c>
       <c r="AS10" s="2">
         <f>SUM(M10:P10)</f>
         <v>5698.2</v>
       </c>
       <c r="AT10" s="2">
-        <f t="shared" ref="AT10:AT12" si="19">SUM(Q10:T10)</f>
+        <f t="shared" ref="AT10:AT12" si="23">SUM(Q10:T10)</f>
         <v>7687.1</v>
       </c>
       <c r="AU10" s="2">
@@ -5149,72 +5404,72 @@
         <v>8944.7000000000007</v>
       </c>
       <c r="AV10" s="2">
+        <f t="shared" si="20"/>
+        <v>10238.599999999999</v>
+      </c>
+      <c r="AW10" s="2">
         <f t="shared" si="17"/>
-        <v>10238.599999999999</v>
-      </c>
-      <c r="AW10" s="2">
-        <f>SUM(AC10:AF10)</f>
-        <v>10461</v>
+        <v>10131.9</v>
       </c>
       <c r="AX10" s="2">
-        <f>+AW10-1000</f>
-        <v>9461</v>
+        <f t="shared" ref="AX10" si="24">SUM(AG10:AJ10)</f>
+        <v>9418.7999999999993</v>
       </c>
       <c r="AY10" s="2">
         <f>+AX10-1200</f>
-        <v>8261</v>
+        <v>8218.7999999999993</v>
       </c>
       <c r="AZ10" s="2">
         <f>+AY10-1800</f>
-        <v>6461</v>
+        <v>6418.7999999999993</v>
       </c>
       <c r="BA10" s="2">
         <f>+AZ10-1600</f>
-        <v>4861</v>
+        <v>4818.7999999999993</v>
       </c>
       <c r="BB10" s="2">
         <f>+BA10-2000</f>
-        <v>2861</v>
+        <v>2818.7999999999993</v>
       </c>
       <c r="BC10" s="2">
         <f>+BB10-500</f>
-        <v>2361</v>
+        <v>2318.7999999999993</v>
       </c>
       <c r="BD10" s="2">
         <f>+BC10*0.8</f>
-        <v>1888.8000000000002</v>
+        <v>1855.0399999999995</v>
       </c>
       <c r="BE10" s="2">
-        <f t="shared" ref="BE10:BL10" si="20">+BD10*0.8</f>
-        <v>1511.0400000000002</v>
+        <f t="shared" ref="BE10:BL10" si="25">+BD10*0.8</f>
+        <v>1484.0319999999997</v>
       </c>
       <c r="BF10" s="2">
-        <f t="shared" si="20"/>
-        <v>1208.8320000000001</v>
+        <f t="shared" si="25"/>
+        <v>1187.2255999999998</v>
       </c>
       <c r="BG10" s="2">
-        <f t="shared" si="20"/>
-        <v>967.06560000000013</v>
+        <f t="shared" si="25"/>
+        <v>949.7804799999999</v>
       </c>
       <c r="BH10" s="2">
-        <f t="shared" si="20"/>
-        <v>773.6524800000002</v>
+        <f t="shared" si="25"/>
+        <v>759.82438400000001</v>
       </c>
       <c r="BI10" s="2">
-        <f t="shared" si="20"/>
-        <v>618.92198400000018</v>
+        <f t="shared" si="25"/>
+        <v>607.85950720000005</v>
       </c>
       <c r="BJ10" s="2">
-        <f t="shared" si="20"/>
-        <v>495.13758720000016</v>
+        <f t="shared" si="25"/>
+        <v>486.28760576000008</v>
       </c>
       <c r="BK10" s="2">
-        <f t="shared" si="20"/>
-        <v>396.11006976000016</v>
+        <f t="shared" si="25"/>
+        <v>389.0300846080001</v>
       </c>
       <c r="BL10" s="2">
-        <f t="shared" si="20"/>
-        <v>316.88805580800016</v>
+        <f t="shared" si="25"/>
+        <v>311.22406768640008</v>
       </c>
     </row>
     <row r="11" spans="1:64" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5277,18 +5532,26 @@
       </c>
       <c r="U11" s="12"/>
       <c r="AS11" s="2">
-        <f t="shared" ref="AS11:AS16" si="21">SUM(M11:P11)</f>
+        <f t="shared" ref="AS11:AS16" si="26">SUM(M11:P11)</f>
         <v>420.1</v>
       </c>
       <c r="AT11" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>180</v>
       </c>
       <c r="AU11" s="29" t="s">
         <v>343</v>
       </c>
       <c r="AV11" s="2">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AW11" s="2">
         <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AX11" s="2">
+        <f t="shared" ref="AX11:AX13" si="27">SUM(AG11:AJ11)</f>
         <v>0</v>
       </c>
     </row>
@@ -5352,18 +5615,26 @@
       </c>
       <c r="U12" s="12"/>
       <c r="AS12" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="26"/>
         <v>771.7</v>
       </c>
       <c r="AT12" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>511.29999999999995</v>
       </c>
       <c r="AU12" s="29" t="s">
         <v>342</v>
       </c>
       <c r="AV12" s="2">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AW12" s="2">
         <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="AX12" s="2">
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
     </row>
@@ -5426,72 +5697,72 @@
         <v>924.6</v>
       </c>
       <c r="AV13" s="2">
+        <f t="shared" si="20"/>
+        <v>781.5</v>
+      </c>
+      <c r="AW13" s="2">
         <f t="shared" si="17"/>
-        <v>781.5</v>
-      </c>
-      <c r="AW13" s="2">
-        <f>SUM(AC13:AF13)</f>
-        <v>360.3</v>
+        <v>193.7</v>
       </c>
       <c r="AX13" s="2">
-        <f>+AW13*1.01</f>
-        <v>363.90300000000002</v>
+        <f t="shared" si="27"/>
+        <v>0</v>
       </c>
       <c r="AY13" s="2">
-        <f t="shared" ref="AY13:BF13" si="22">+AX13*1.01</f>
-        <v>367.54203000000001</v>
+        <f t="shared" ref="AY13:BF13" si="28">+AX13*1.01</f>
+        <v>0</v>
       </c>
       <c r="AZ13" s="2">
-        <f t="shared" si="22"/>
-        <v>371.2174503</v>
+        <f t="shared" si="28"/>
+        <v>0</v>
       </c>
       <c r="BA13" s="2">
-        <f t="shared" si="22"/>
-        <v>374.92962480300002</v>
+        <f t="shared" si="28"/>
+        <v>0</v>
       </c>
       <c r="BB13" s="2">
-        <f t="shared" si="22"/>
-        <v>378.67892105103004</v>
+        <f t="shared" si="28"/>
+        <v>0</v>
       </c>
       <c r="BC13" s="2">
-        <f t="shared" si="22"/>
-        <v>382.46571026154032</v>
+        <f t="shared" si="28"/>
+        <v>0</v>
       </c>
       <c r="BD13" s="2">
-        <f t="shared" si="22"/>
-        <v>386.29036736415571</v>
+        <f t="shared" si="28"/>
+        <v>0</v>
       </c>
       <c r="BE13" s="2">
-        <f t="shared" si="22"/>
-        <v>390.15327103779725</v>
+        <f t="shared" si="28"/>
+        <v>0</v>
       </c>
       <c r="BF13" s="2">
-        <f t="shared" si="22"/>
-        <v>394.05480374817523</v>
+        <f t="shared" si="28"/>
+        <v>0</v>
       </c>
       <c r="BG13" s="2">
-        <f t="shared" ref="BG13:BL13" si="23">+BF13*0.5</f>
-        <v>197.02740187408762</v>
+        <f t="shared" ref="BG13:BL13" si="29">+BF13*0.5</f>
+        <v>0</v>
       </c>
       <c r="BH13" s="2">
-        <f t="shared" si="23"/>
-        <v>98.513700937043808</v>
+        <f t="shared" si="29"/>
+        <v>0</v>
       </c>
       <c r="BI13" s="2">
-        <f t="shared" si="23"/>
-        <v>49.256850468521904</v>
+        <f t="shared" si="29"/>
+        <v>0</v>
       </c>
       <c r="BJ13" s="2">
-        <f t="shared" si="23"/>
-        <v>24.628425234260952</v>
+        <f t="shared" si="29"/>
+        <v>0</v>
       </c>
       <c r="BK13" s="2">
-        <f t="shared" si="23"/>
-        <v>12.314212617130476</v>
+        <f t="shared" si="29"/>
+        <v>0</v>
       </c>
       <c r="BL13" s="2">
-        <f t="shared" si="23"/>
-        <v>6.157106308565238</v>
+        <f t="shared" si="29"/>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:64" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5554,7 +5825,7 @@
       </c>
       <c r="U14" s="12"/>
       <c r="AS14" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="26"/>
         <v>683.3</v>
       </c>
       <c r="AT14" s="2">
@@ -5565,7 +5836,7 @@
         <v>341</v>
       </c>
       <c r="AV14" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -5574,59 +5845,59 @@
         <v>24</v>
       </c>
       <c r="C15" s="14">
-        <f t="shared" ref="C15:K15" si="24">SUM(C10:C14)+C8</f>
+        <f t="shared" ref="C15:K15" si="30">SUM(C10:C14)+C8</f>
         <v>783</v>
       </c>
       <c r="D15" s="14">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>869.93299999999999</v>
       </c>
       <c r="E15" s="14">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>858.18200000000002</v>
       </c>
       <c r="F15" s="14">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>940.91300000000001</v>
       </c>
       <c r="G15" s="14">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>950</v>
       </c>
       <c r="H15" s="14">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>1257</v>
       </c>
       <c r="I15" s="14">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>1515</v>
       </c>
       <c r="J15" s="14">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>1524.4</v>
       </c>
       <c r="K15" s="14">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>1538</v>
       </c>
       <c r="L15" s="14">
-        <f t="shared" ref="L15:P15" si="25">SUM(L10:L14)</f>
+        <f t="shared" ref="L15:P15" si="31">SUM(L10:L14)</f>
         <v>1627</v>
       </c>
       <c r="M15" s="14">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>1723.3</v>
       </c>
       <c r="N15" s="14">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>1794</v>
       </c>
       <c r="O15" s="14">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>1984</v>
       </c>
       <c r="P15" s="14">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>2072</v>
       </c>
       <c r="Q15" s="14">
@@ -5634,27 +5905,27 @@
         <v>2097.5</v>
       </c>
       <c r="R15" s="14">
-        <f t="shared" ref="R15:W15" si="26">SUM(R10:R14)</f>
+        <f t="shared" ref="R15:W15" si="32">SUM(R10:R14)</f>
         <v>2197</v>
       </c>
       <c r="S15" s="14">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>2334.2999999999997</v>
       </c>
       <c r="T15" s="14">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>2303</v>
       </c>
       <c r="U15" s="14">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>2374.7999999999997</v>
       </c>
       <c r="V15" s="14">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>2493.2000000000003</v>
       </c>
       <c r="W15" s="14">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>2483.6000000000004</v>
       </c>
       <c r="X15" s="14">
@@ -5662,19 +5933,19 @@
         <v>2517.7000000000003</v>
       </c>
       <c r="Y15" s="14">
-        <f t="shared" ref="Y15:AB15" si="27">SUM(Y10:Y14)</f>
+        <f t="shared" ref="Y15:AB15" si="33">SUM(Y10:Y14)</f>
         <v>2690.6</v>
       </c>
       <c r="Z15" s="14">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>2645.6</v>
       </c>
       <c r="AA15" s="14">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>2771.9</v>
       </c>
       <c r="AB15" s="14">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>2912</v>
       </c>
       <c r="AC15" s="14">
@@ -5682,36 +5953,36 @@
         <v>2770.2</v>
       </c>
       <c r="AD15" s="14">
-        <f t="shared" ref="AD15:AJ15" si="28">SUM(AD3:AD14)</f>
+        <f t="shared" ref="AD15:AJ15" si="34">SUM(AD3:AD14)</f>
         <v>2964.7</v>
       </c>
       <c r="AE15" s="14">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>3076.4</v>
       </c>
       <c r="AF15" s="14">
-        <f t="shared" si="28"/>
-        <v>3229</v>
+        <f t="shared" si="34"/>
+        <v>3190</v>
       </c>
       <c r="AG15" s="14">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f t="shared" si="34"/>
+        <v>2986.8999999999996</v>
       </c>
       <c r="AH15" s="14">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f t="shared" si="34"/>
+        <v>3008.8999999999996</v>
       </c>
       <c r="AI15" s="14">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f t="shared" si="34"/>
+        <v>3030.8999999999996</v>
       </c>
       <c r="AJ15" s="14">
-        <f t="shared" si="28"/>
-        <v>0</v>
+        <f t="shared" si="34"/>
+        <v>3052.8999999999996</v>
       </c>
       <c r="AK15" s="14"/>
       <c r="AR15" s="13">
-        <f t="shared" ref="AR15" si="29">SUM(AR10:AR14)</f>
+        <f t="shared" ref="AR15" si="35">SUM(AR10:AR14)</f>
         <v>0</v>
       </c>
       <c r="AS15" s="13">
@@ -5723,76 +5994,76 @@
         <v>8931.7999999999993</v>
       </c>
       <c r="AU15" s="13">
-        <f t="shared" ref="AU15:BG15" si="30">SUM(AU3:AU14)</f>
+        <f t="shared" ref="AU15:BG15" si="36">SUM(AU3:AU14)</f>
         <v>9869.3000000000011</v>
       </c>
       <c r="AV15" s="13">
-        <f t="shared" si="30"/>
+        <f t="shared" si="36"/>
         <v>11020.099999999999</v>
       </c>
       <c r="AW15" s="13">
-        <f t="shared" si="30"/>
-        <v>11741</v>
+        <f>SUM(AW3:AW14)</f>
+        <v>12218</v>
       </c>
       <c r="AX15" s="13">
-        <f t="shared" si="30"/>
-        <v>11967.597</v>
+        <f>SUM(AX3:AX14)</f>
+        <v>12379.599999999999</v>
       </c>
       <c r="AY15" s="13">
-        <f t="shared" si="30"/>
-        <v>12451.308370000001</v>
+        <f t="shared" si="36"/>
+        <v>12803.815999999999</v>
       </c>
       <c r="AZ15" s="13">
-        <f t="shared" si="30"/>
-        <v>12474.6795537</v>
+        <f t="shared" si="36"/>
+        <v>13146.552159999999</v>
       </c>
       <c r="BA15" s="13">
-        <f t="shared" si="30"/>
-        <v>12396.211499237001</v>
+        <f t="shared" si="36"/>
+        <v>13355.2386816</v>
       </c>
       <c r="BB15" s="13">
-        <f t="shared" si="30"/>
-        <v>11809.87730922937</v>
+        <f t="shared" si="36"/>
+        <v>13142.934768415998</v>
       </c>
       <c r="BC15" s="13">
-        <f t="shared" si="30"/>
-        <v>12122.542263321664</v>
+        <f t="shared" si="36"/>
+        <v>13697.804976100157</v>
       </c>
       <c r="BD15" s="13">
-        <f t="shared" si="30"/>
-        <v>11866.76520140488</v>
+        <f t="shared" si="36"/>
+        <v>13504.174052861159</v>
       </c>
       <c r="BE15" s="13">
-        <f t="shared" si="30"/>
-        <v>11711.156594332431</v>
+        <f t="shared" si="36"/>
+        <v>13410.686591199772</v>
       </c>
       <c r="BF15" s="13">
-        <f t="shared" si="30"/>
-        <v>11636.992653416659</v>
+        <f t="shared" si="36"/>
+        <v>13399.00681085607</v>
       </c>
       <c r="BG15" s="13">
-        <f t="shared" si="30"/>
-        <v>11428.364089974388</v>
+        <f t="shared" si="36"/>
+        <v>13454.515378921258</v>
       </c>
       <c r="BH15" s="13">
-        <f t="shared" ref="BH15:BL15" si="31">SUM(BH3:BH14)</f>
-        <v>11372.798885251535</v>
+        <f t="shared" ref="BH15:BL15" si="37">SUM(BH3:BH14)</f>
+        <v>13565.5675841458</v>
       </c>
       <c r="BI15" s="13">
-        <f t="shared" si="31"/>
-        <v>11411.548338319339</v>
+        <f t="shared" si="37"/>
+        <v>13722.899920149646</v>
       </c>
       <c r="BJ15" s="13">
-        <f t="shared" si="31"/>
-        <v>11512.431597991565</v>
+        <f t="shared" si="37"/>
+        <v>13919.155397065602</v>
       </c>
       <c r="BK15" s="13">
-        <f t="shared" si="31"/>
-        <v>11657.134782058021</v>
+        <f t="shared" si="37"/>
+        <v>14148.503837279912</v>
       </c>
       <c r="BL15" s="13">
-        <f t="shared" si="31"/>
-        <v>7042.2818060854561</v>
+        <f t="shared" si="37"/>
+        <v>8353.9648006859807</v>
       </c>
     </row>
     <row r="16" spans="1:64" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5887,11 +6158,13 @@
         <v>407</v>
       </c>
       <c r="AF16" s="2">
-        <f>+AF15-AF17</f>
-        <v>419.77</v>
+        <v>457.7</v>
+      </c>
+      <c r="AG16" s="2">
+        <v>384.6</v>
       </c>
       <c r="AS16" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="26"/>
         <v>904.21199999999999</v>
       </c>
       <c r="AT16" s="2">
@@ -5899,76 +6172,76 @@
         <v>975.5</v>
       </c>
       <c r="AU16" s="2">
-        <f t="shared" ref="AU16:AU19" si="32">SUM(U16:X16)</f>
+        <f t="shared" ref="AU16:AU19" si="38">SUM(U16:X16)</f>
         <v>1253</v>
       </c>
       <c r="AV16" s="2">
-        <f t="shared" ref="AV16:BD16" si="33">+AV15*0.07</f>
-        <v>771.40699999999993</v>
+        <f t="shared" si="20"/>
+        <v>1502.8</v>
       </c>
       <c r="AW16" s="2">
-        <f t="shared" si="33"/>
-        <v>821.87000000000012</v>
+        <f t="shared" ref="AW16:AW19" si="39">SUM(AD16:AG16)</f>
+        <v>1649.1999999999998</v>
       </c>
       <c r="AX16" s="2">
-        <f t="shared" si="33"/>
-        <v>837.73179000000005</v>
+        <f t="shared" ref="AV16:BD16" si="40">+AX15*0.07</f>
+        <v>866.572</v>
       </c>
       <c r="AY16" s="2">
-        <f t="shared" si="33"/>
-        <v>871.59158590000015</v>
+        <f t="shared" si="40"/>
+        <v>896.26711999999998</v>
       </c>
       <c r="AZ16" s="2">
-        <f t="shared" si="33"/>
-        <v>873.22756875900006</v>
+        <f t="shared" si="40"/>
+        <v>920.25865120000003</v>
       </c>
       <c r="BA16" s="2">
-        <f t="shared" si="33"/>
-        <v>867.73480494659009</v>
+        <f t="shared" si="40"/>
+        <v>934.86670771200011</v>
       </c>
       <c r="BB16" s="2">
-        <f t="shared" si="33"/>
-        <v>826.69141164605605</v>
+        <f t="shared" si="40"/>
+        <v>920.00543378911993</v>
       </c>
       <c r="BC16" s="2">
-        <f t="shared" si="33"/>
-        <v>848.57795843251654</v>
+        <f t="shared" si="40"/>
+        <v>958.84634832701101</v>
       </c>
       <c r="BD16" s="2">
-        <f t="shared" si="33"/>
-        <v>830.67356409834167</v>
+        <f t="shared" si="40"/>
+        <v>945.29218370028127</v>
       </c>
       <c r="BE16" s="2">
-        <f t="shared" ref="BE16:BJ16" si="34">+BE15*0.05</f>
-        <v>585.55782971662154</v>
+        <f t="shared" ref="BE16:BJ16" si="41">+BE15*0.05</f>
+        <v>670.53432955998869</v>
       </c>
       <c r="BF16" s="2">
-        <f t="shared" si="34"/>
-        <v>581.84963267083299</v>
+        <f t="shared" si="41"/>
+        <v>669.95034054280359</v>
       </c>
       <c r="BG16" s="2">
-        <f t="shared" si="34"/>
-        <v>571.41820449871943</v>
+        <f t="shared" si="41"/>
+        <v>672.725768946063</v>
       </c>
       <c r="BH16" s="2">
-        <f t="shared" si="34"/>
-        <v>568.63994426257682</v>
+        <f t="shared" si="41"/>
+        <v>678.27837920729007</v>
       </c>
       <c r="BI16" s="2">
-        <f t="shared" si="34"/>
-        <v>570.57741691596698</v>
+        <f t="shared" si="41"/>
+        <v>686.1449960074824</v>
       </c>
       <c r="BJ16" s="2">
-        <f t="shared" si="34"/>
-        <v>575.62157989957825</v>
+        <f t="shared" si="41"/>
+        <v>695.95776985328018</v>
       </c>
       <c r="BK16" s="2">
         <f>+BK15*0.05</f>
-        <v>582.85673910290109</v>
+        <v>707.42519186399568</v>
       </c>
       <c r="BL16" s="2">
-        <f t="shared" ref="BL16" si="35">+BL15*0.07</f>
-        <v>492.95972642598196</v>
+        <f t="shared" ref="BL16" si="42">+BL15*0.07</f>
+        <v>584.77753604801865</v>
       </c>
     </row>
     <row r="17" spans="2:124" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5976,43 +6249,43 @@
         <v>54</v>
       </c>
       <c r="C17" s="12">
-        <f t="shared" ref="C17:J17" si="36">+C15-C16</f>
+        <f t="shared" ref="C17:J17" si="43">+C15-C16</f>
         <v>671.745</v>
       </c>
       <c r="D17" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="43"/>
         <v>747.64400000000001</v>
       </c>
       <c r="E17" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="43"/>
         <v>763.09</v>
       </c>
       <c r="F17" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="43"/>
         <v>805.173</v>
       </c>
       <c r="G17" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="43"/>
         <v>818.08600000000001</v>
       </c>
       <c r="H17" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="43"/>
         <v>1071.9880000000001</v>
       </c>
       <c r="I17" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="43"/>
         <v>1352.5029999999999</v>
       </c>
       <c r="J17" s="12">
-        <f t="shared" si="36"/>
+        <f t="shared" si="43"/>
         <v>1339.9</v>
       </c>
       <c r="K17" s="12">
-        <f t="shared" ref="K17:L17" si="37">+K15-K16</f>
+        <f t="shared" ref="K17:L17" si="44">+K15-K16</f>
         <v>1351.818</v>
       </c>
       <c r="L17" s="12">
-        <f t="shared" si="37"/>
+        <f t="shared" si="44"/>
         <v>1423.9</v>
       </c>
       <c r="M17" s="12">
@@ -6036,7 +6309,7 @@
         <v>1951.7</v>
       </c>
       <c r="R17" s="12">
-        <f t="shared" ref="R17:T17" si="38">+R15-R16</f>
+        <f t="shared" ref="R17:T17" si="45">+R15-R16</f>
         <v>1935.2</v>
       </c>
       <c r="S17" s="12">
@@ -6044,39 +6317,39 @@
         <v>2047.2999999999997</v>
       </c>
       <c r="T17" s="12">
-        <f t="shared" si="38"/>
+        <f t="shared" si="45"/>
         <v>2022.1</v>
       </c>
       <c r="U17" s="12">
-        <f t="shared" ref="U17:AB17" si="39">+U15-U16</f>
+        <f t="shared" ref="U17:AB17" si="46">+U15-U16</f>
         <v>2109.7999999999997</v>
       </c>
       <c r="V17" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="46"/>
         <v>2186.4</v>
       </c>
       <c r="W17" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="46"/>
         <v>2166.6000000000004</v>
       </c>
       <c r="X17" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="46"/>
         <v>2153.5000000000005</v>
       </c>
       <c r="Y17" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="46"/>
         <v>2354.7999999999997</v>
       </c>
       <c r="Z17" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="46"/>
         <v>2280.6</v>
       </c>
       <c r="AA17" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="46"/>
         <v>2386.2000000000003</v>
       </c>
       <c r="AB17" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="46"/>
         <v>2495.6999999999998</v>
       </c>
       <c r="AC17" s="2">
@@ -6093,10 +6366,14 @@
       </c>
       <c r="AF17" s="2">
         <f>+AF15*0.87</f>
-        <v>2809.23</v>
+        <v>2775.3</v>
+      </c>
+      <c r="AG17" s="2">
+        <f>+AG15-AG16</f>
+        <v>2602.2999999999997</v>
       </c>
       <c r="AR17" s="2">
-        <f t="shared" ref="AR17" si="40">+AR15-AR16</f>
+        <f t="shared" ref="AR17" si="47">+AR15-AR16</f>
         <v>0</v>
       </c>
       <c r="AS17" s="2">
@@ -6112,72 +6389,72 @@
         <v>8616.3000000000011</v>
       </c>
       <c r="AV17" s="2">
-        <f t="shared" ref="AV17:BG17" si="41">+AV15-AV16</f>
-        <v>10248.692999999999</v>
+        <f t="shared" ref="AV17:BG17" si="48">+AV15-AV16</f>
+        <v>9517.2999999999993</v>
       </c>
       <c r="AW17" s="2">
-        <f t="shared" si="41"/>
-        <v>10919.13</v>
+        <f>+AW15-AW16</f>
+        <v>10568.8</v>
       </c>
       <c r="AX17" s="2">
-        <f t="shared" si="41"/>
-        <v>11129.86521</v>
+        <f t="shared" si="48"/>
+        <v>11513.027999999998</v>
       </c>
       <c r="AY17" s="2">
-        <f t="shared" si="41"/>
-        <v>11579.716784100001</v>
+        <f t="shared" si="48"/>
+        <v>11907.548879999998</v>
       </c>
       <c r="AZ17" s="2">
-        <f t="shared" si="41"/>
-        <v>11601.451984940999</v>
+        <f t="shared" si="48"/>
+        <v>12226.293508799999</v>
       </c>
       <c r="BA17" s="2">
-        <f t="shared" si="41"/>
-        <v>11528.47669429041</v>
+        <f t="shared" si="48"/>
+        <v>12420.371973887999</v>
       </c>
       <c r="BB17" s="2">
-        <f t="shared" si="41"/>
-        <v>10983.185897583315</v>
+        <f t="shared" si="48"/>
+        <v>12222.929334626879</v>
       </c>
       <c r="BC17" s="2">
-        <f t="shared" si="41"/>
-        <v>11273.964304889147</v>
+        <f t="shared" si="48"/>
+        <v>12738.958627773145</v>
       </c>
       <c r="BD17" s="2">
-        <f t="shared" si="41"/>
-        <v>11036.091637306537</v>
+        <f t="shared" si="48"/>
+        <v>12558.881869160878</v>
       </c>
       <c r="BE17" s="2">
-        <f t="shared" si="41"/>
-        <v>11125.59876461581</v>
+        <f t="shared" si="48"/>
+        <v>12740.152261639783</v>
       </c>
       <c r="BF17" s="2">
-        <f t="shared" si="41"/>
-        <v>11055.143020745825</v>
+        <f t="shared" si="48"/>
+        <v>12729.056470313266</v>
       </c>
       <c r="BG17" s="2">
-        <f t="shared" si="41"/>
-        <v>10856.945885475669</v>
+        <f t="shared" si="48"/>
+        <v>12781.789609975196</v>
       </c>
       <c r="BH17" s="2">
-        <f t="shared" ref="BH17:BL17" si="42">+BH15-BH16</f>
-        <v>10804.158940988958</v>
+        <f t="shared" ref="BH17:BL17" si="49">+BH15-BH16</f>
+        <v>12887.28920493851</v>
       </c>
       <c r="BI17" s="2">
-        <f t="shared" si="42"/>
-        <v>10840.970921403372</v>
+        <f t="shared" si="49"/>
+        <v>13036.754924142164</v>
       </c>
       <c r="BJ17" s="2">
-        <f t="shared" si="42"/>
-        <v>10936.810018091986</v>
+        <f t="shared" si="49"/>
+        <v>13223.197627212323</v>
       </c>
       <c r="BK17" s="2">
-        <f t="shared" si="42"/>
-        <v>11074.27804295512</v>
+        <f t="shared" si="49"/>
+        <v>13441.078645415917</v>
       </c>
       <c r="BL17" s="2">
-        <f t="shared" si="42"/>
-        <v>6549.3220796594742</v>
+        <f t="shared" si="49"/>
+        <v>7769.1872646379616</v>
       </c>
     </row>
     <row r="18" spans="2:124" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6272,8 +6549,10 @@
         <v>369</v>
       </c>
       <c r="AF18" s="2">
-        <f t="shared" ref="AF18:AF19" si="43">+AB18</f>
-        <v>310.10000000000002</v>
+        <v>487</v>
+      </c>
+      <c r="AG18" s="2">
+        <v>493.7</v>
       </c>
       <c r="AR18" s="2">
         <v>609</v>
@@ -6282,80 +6561,80 @@
         <v>673</v>
       </c>
       <c r="AT18" s="2">
-        <f t="shared" ref="AT18:AT19" si="44">SUM(Q18:T18)</f>
+        <f t="shared" ref="AT18:AT19" si="50">SUM(Q18:T18)</f>
         <v>746.30000000000007</v>
       </c>
       <c r="AU18" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="38"/>
         <v>917.80000000000007</v>
       </c>
       <c r="AV18" s="2">
-        <f t="shared" ref="AV18:BG18" si="45">+AV15*0.1</f>
-        <v>1102.01</v>
+        <f t="shared" si="20"/>
+        <v>1162.5999999999999</v>
       </c>
       <c r="AW18" s="2">
-        <f t="shared" si="45"/>
-        <v>1174.1000000000001</v>
+        <f t="shared" si="39"/>
+        <v>1709.1000000000001</v>
       </c>
       <c r="AX18" s="2">
-        <f t="shared" si="45"/>
-        <v>1196.7597000000001</v>
+        <f t="shared" ref="AV18:BG18" si="51">+AX15*0.1</f>
+        <v>1237.96</v>
       </c>
       <c r="AY18" s="2">
-        <f t="shared" si="45"/>
-        <v>1245.1308370000002</v>
+        <f t="shared" si="51"/>
+        <v>1280.3815999999999</v>
       </c>
       <c r="AZ18" s="2">
-        <f t="shared" si="45"/>
-        <v>1247.46795537</v>
+        <f t="shared" si="51"/>
+        <v>1314.6552160000001</v>
       </c>
       <c r="BA18" s="2">
-        <f t="shared" si="45"/>
-        <v>1239.6211499237002</v>
+        <f t="shared" si="51"/>
+        <v>1335.5238681600001</v>
       </c>
       <c r="BB18" s="2">
-        <f t="shared" si="45"/>
-        <v>1180.9877309229371</v>
+        <f t="shared" si="51"/>
+        <v>1314.2934768415998</v>
       </c>
       <c r="BC18" s="2">
-        <f t="shared" si="45"/>
-        <v>1212.2542263321664</v>
+        <f t="shared" si="51"/>
+        <v>1369.7804976100158</v>
       </c>
       <c r="BD18" s="2">
-        <f t="shared" si="45"/>
-        <v>1186.676520140488</v>
+        <f t="shared" si="51"/>
+        <v>1350.417405286116</v>
       </c>
       <c r="BE18" s="2">
-        <f t="shared" si="45"/>
-        <v>1171.1156594332431</v>
+        <f t="shared" si="51"/>
+        <v>1341.0686591199774</v>
       </c>
       <c r="BF18" s="2">
-        <f t="shared" si="45"/>
-        <v>1163.699265341666</v>
+        <f t="shared" si="51"/>
+        <v>1339.9006810856072</v>
       </c>
       <c r="BG18" s="2">
-        <f t="shared" si="45"/>
-        <v>1142.8364089974389</v>
+        <f t="shared" si="51"/>
+        <v>1345.451537892126</v>
       </c>
       <c r="BH18" s="2">
-        <f t="shared" ref="BH18:BL18" si="46">+BH15*0.1</f>
-        <v>1137.2798885251536</v>
+        <f t="shared" ref="BH18:BL18" si="52">+BH15*0.1</f>
+        <v>1356.5567584145801</v>
       </c>
       <c r="BI18" s="2">
-        <f t="shared" si="46"/>
-        <v>1141.154833831934</v>
+        <f t="shared" si="52"/>
+        <v>1372.2899920149648</v>
       </c>
       <c r="BJ18" s="2">
-        <f t="shared" si="46"/>
-        <v>1151.2431597991565</v>
+        <f t="shared" si="52"/>
+        <v>1391.9155397065604</v>
       </c>
       <c r="BK18" s="2">
-        <f t="shared" si="46"/>
-        <v>1165.7134782058022</v>
+        <f t="shared" si="52"/>
+        <v>1414.8503837279914</v>
       </c>
       <c r="BL18" s="2">
-        <f t="shared" si="46"/>
-        <v>704.2281806085457</v>
+        <f t="shared" si="52"/>
+        <v>835.39648006859807</v>
       </c>
     </row>
     <row r="19" spans="2:124" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6450,8 +6729,10 @@
         <v>861.1</v>
       </c>
       <c r="AF19" s="2">
-        <f t="shared" si="43"/>
-        <v>899.8</v>
+        <v>973.7</v>
+      </c>
+      <c r="AG19" s="2">
+        <v>961.6</v>
       </c>
       <c r="AR19" s="2">
         <v>1372</v>
@@ -6460,12 +6741,20 @@
         <v>1658</v>
       </c>
       <c r="AT19" s="2">
-        <f t="shared" si="44"/>
+        <f t="shared" si="50"/>
         <v>2206.5</v>
       </c>
       <c r="AU19" s="2">
-        <f t="shared" si="32"/>
+        <f t="shared" si="38"/>
         <v>2796.7</v>
+      </c>
+      <c r="AV19" s="2">
+        <f>SUM(Y19:AB19)</f>
+        <v>3030.7</v>
+      </c>
+      <c r="AW19" s="2">
+        <f t="shared" si="39"/>
+        <v>3674.5</v>
       </c>
     </row>
     <row r="20" spans="2:124" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6473,43 +6762,43 @@
         <v>57</v>
       </c>
       <c r="C20" s="12">
-        <f t="shared" ref="C20:D20" si="47">SUM(C18:C19)</f>
+        <f t="shared" ref="C20:D20" si="53">SUM(C18:C19)</f>
         <v>467.80499999999995</v>
       </c>
       <c r="D20" s="12">
-        <f t="shared" si="47"/>
+        <f t="shared" si="53"/>
         <v>591.09100000000001</v>
       </c>
       <c r="E20" s="12">
-        <f t="shared" ref="E20:G20" si="48">SUM(E18:E19)</f>
+        <f t="shared" ref="E20:G20" si="54">SUM(E18:E19)</f>
         <v>486.53499999999997</v>
       </c>
       <c r="F20" s="12">
-        <f t="shared" si="48"/>
+        <f t="shared" si="54"/>
         <v>535.59300000000007</v>
       </c>
       <c r="G20" s="12">
-        <f t="shared" si="48"/>
+        <f t="shared" si="54"/>
         <v>715.62199999999996</v>
       </c>
       <c r="H20" s="12">
-        <f t="shared" ref="H20:I20" si="49">SUM(H18:H19)</f>
+        <f t="shared" ref="H20:I20" si="55">SUM(H18:H19)</f>
         <v>675.28800000000001</v>
       </c>
       <c r="I20" s="12">
-        <f t="shared" si="49"/>
+        <f t="shared" si="55"/>
         <v>630.78600000000006</v>
       </c>
       <c r="J20" s="12">
-        <f t="shared" ref="J20" si="50">SUM(J18:J19)</f>
+        <f t="shared" ref="J20" si="56">SUM(J18:J19)</f>
         <v>612.70000000000005</v>
       </c>
       <c r="K20" s="12">
-        <f t="shared" ref="K20:L20" si="51">SUM(K18:K19)</f>
+        <f t="shared" ref="K20:L20" si="57">SUM(K18:K19)</f>
         <v>678.048</v>
       </c>
       <c r="L20" s="12">
-        <f t="shared" si="51"/>
+        <f t="shared" si="57"/>
         <v>539</v>
       </c>
       <c r="M20" s="12">
@@ -6517,11 +6806,11 @@
         <v>531</v>
       </c>
       <c r="N20" s="12">
-        <f t="shared" ref="N20:Q20" si="52">SUM(N18:N19)</f>
+        <f t="shared" ref="N20:Q20" si="58">SUM(N18:N19)</f>
         <v>643.29999999999995</v>
       </c>
       <c r="O20" s="12">
-        <f t="shared" si="52"/>
+        <f t="shared" si="58"/>
         <v>691.93999999999994</v>
       </c>
       <c r="P20" s="12">
@@ -6529,7 +6818,7 @@
         <v>703</v>
       </c>
       <c r="Q20" s="12">
-        <f t="shared" si="52"/>
+        <f t="shared" si="58"/>
         <v>687</v>
       </c>
       <c r="R20" s="12">
@@ -6541,145 +6830,148 @@
         <v>728.9</v>
       </c>
       <c r="T20" s="12">
-        <f t="shared" ref="T20:U20" si="53">SUM(T18:T19)</f>
+        <f t="shared" ref="T20:U20" si="59">SUM(T18:T19)</f>
         <v>848.80000000000007</v>
       </c>
       <c r="U20" s="12">
-        <f t="shared" si="53"/>
+        <f t="shared" si="59"/>
         <v>860.4</v>
       </c>
       <c r="V20" s="12">
-        <f t="shared" ref="V20:Y20" si="54">SUM(V18:V19)</f>
+        <f t="shared" ref="V20:Y20" si="60">SUM(V18:V19)</f>
         <v>928</v>
       </c>
       <c r="W20" s="12">
-        <f t="shared" si="54"/>
+        <f t="shared" si="60"/>
         <v>941.7</v>
       </c>
       <c r="X20" s="12">
-        <f t="shared" si="54"/>
+        <f t="shared" si="60"/>
         <v>984.4</v>
       </c>
       <c r="Y20" s="12">
-        <f t="shared" si="54"/>
+        <f t="shared" si="60"/>
         <v>941.7</v>
       </c>
       <c r="Z20" s="12">
-        <f t="shared" ref="Z20:AB20" si="55">SUM(Z18:Z19)</f>
+        <f t="shared" ref="Z20:AB20" si="61">SUM(Z18:Z19)</f>
         <v>977.6</v>
       </c>
       <c r="AA20" s="12">
-        <f t="shared" si="55"/>
+        <f t="shared" si="61"/>
         <v>1064.0999999999999</v>
       </c>
       <c r="AB20" s="12">
-        <f t="shared" si="55"/>
+        <f t="shared" si="61"/>
         <v>1209.9000000000001</v>
       </c>
       <c r="AC20" s="12">
-        <f t="shared" ref="AC20:AF20" si="56">SUM(AC18:AC19)</f>
+        <f t="shared" ref="AC20:AG20" si="62">SUM(AC18:AC19)</f>
         <v>1212</v>
       </c>
       <c r="AD20" s="12">
-        <f t="shared" si="56"/>
+        <f t="shared" si="62"/>
         <v>1237.5</v>
       </c>
       <c r="AE20" s="12">
-        <f t="shared" si="56"/>
+        <f t="shared" si="62"/>
         <v>1230.0999999999999</v>
       </c>
       <c r="AF20" s="12">
-        <f t="shared" si="56"/>
-        <v>1209.9000000000001</v>
-      </c>
-      <c r="AG20" s="12"/>
+        <f t="shared" si="62"/>
+        <v>1460.7</v>
+      </c>
+      <c r="AG20" s="12">
+        <f t="shared" si="62"/>
+        <v>1455.3</v>
+      </c>
       <c r="AH20" s="12"/>
       <c r="AI20" s="12"/>
       <c r="AJ20" s="12"/>
       <c r="AK20" s="12"/>
       <c r="AR20" s="12">
-        <f t="shared" ref="AR20:AT20" si="57">SUM(AR18:AR19)</f>
+        <f t="shared" ref="AR20:AT20" si="63">SUM(AR18:AR19)</f>
         <v>1981</v>
       </c>
       <c r="AS20" s="12">
-        <f t="shared" si="57"/>
+        <f t="shared" si="63"/>
         <v>2331</v>
       </c>
       <c r="AT20" s="12">
-        <f t="shared" si="57"/>
+        <f t="shared" si="63"/>
         <v>2952.8</v>
       </c>
       <c r="AU20" s="12">
-        <f t="shared" ref="AU20:BG20" si="58">SUM(AU18:AU19)</f>
+        <f t="shared" ref="AU20:BG22" si="64">SUM(AU18:AU19)</f>
         <v>3714.5</v>
       </c>
       <c r="AV20" s="12">
-        <f t="shared" si="58"/>
-        <v>1102.01</v>
+        <f>SUM(AV18:AV19)</f>
+        <v>4193.2999999999993</v>
       </c>
       <c r="AW20" s="12">
-        <f t="shared" si="58"/>
-        <v>1174.1000000000001</v>
+        <f t="shared" si="64"/>
+        <v>5383.6</v>
       </c>
       <c r="AX20" s="12">
-        <f t="shared" si="58"/>
-        <v>1196.7597000000001</v>
+        <f t="shared" si="64"/>
+        <v>1237.96</v>
       </c>
       <c r="AY20" s="12">
-        <f t="shared" si="58"/>
-        <v>1245.1308370000002</v>
+        <f t="shared" si="64"/>
+        <v>1280.3815999999999</v>
       </c>
       <c r="AZ20" s="12">
-        <f t="shared" si="58"/>
-        <v>1247.46795537</v>
+        <f t="shared" si="64"/>
+        <v>1314.6552160000001</v>
       </c>
       <c r="BA20" s="12">
-        <f t="shared" si="58"/>
-        <v>1239.6211499237002</v>
+        <f t="shared" si="64"/>
+        <v>1335.5238681600001</v>
       </c>
       <c r="BB20" s="12">
-        <f t="shared" si="58"/>
-        <v>1180.9877309229371</v>
+        <f t="shared" si="64"/>
+        <v>1314.2934768415998</v>
       </c>
       <c r="BC20" s="12">
-        <f t="shared" si="58"/>
-        <v>1212.2542263321664</v>
+        <f t="shared" si="64"/>
+        <v>1369.7804976100158</v>
       </c>
       <c r="BD20" s="12">
-        <f t="shared" si="58"/>
-        <v>1186.676520140488</v>
+        <f t="shared" si="64"/>
+        <v>1350.417405286116</v>
       </c>
       <c r="BE20" s="12">
-        <f t="shared" si="58"/>
-        <v>1171.1156594332431</v>
+        <f t="shared" si="64"/>
+        <v>1341.0686591199774</v>
       </c>
       <c r="BF20" s="12">
-        <f t="shared" si="58"/>
-        <v>1163.699265341666</v>
+        <f t="shared" si="64"/>
+        <v>1339.9006810856072</v>
       </c>
       <c r="BG20" s="12">
-        <f t="shared" si="58"/>
-        <v>1142.8364089974389</v>
+        <f t="shared" si="64"/>
+        <v>1345.451537892126</v>
       </c>
       <c r="BH20" s="12">
-        <f t="shared" ref="BH20:BL20" si="59">SUM(BH18:BH19)</f>
-        <v>1137.2798885251536</v>
+        <f t="shared" ref="BH20:BL20" si="65">SUM(BH18:BH19)</f>
+        <v>1356.5567584145801</v>
       </c>
       <c r="BI20" s="12">
-        <f t="shared" si="59"/>
-        <v>1141.154833831934</v>
+        <f t="shared" si="65"/>
+        <v>1372.2899920149648</v>
       </c>
       <c r="BJ20" s="12">
-        <f t="shared" si="59"/>
-        <v>1151.2431597991565</v>
+        <f t="shared" si="65"/>
+        <v>1391.9155397065604</v>
       </c>
       <c r="BK20" s="12">
-        <f t="shared" si="59"/>
-        <v>1165.7134782058022</v>
+        <f t="shared" si="65"/>
+        <v>1414.8503837279914</v>
       </c>
       <c r="BL20" s="12">
-        <f t="shared" si="59"/>
-        <v>704.2281806085457</v>
+        <f t="shared" si="65"/>
+        <v>835.39648006859807</v>
       </c>
     </row>
     <row r="21" spans="2:124" x14ac:dyDescent="0.25">
@@ -6687,43 +6979,43 @@
         <v>58</v>
       </c>
       <c r="C21" s="12">
-        <f t="shared" ref="C21:D21" si="60">C17-C20</f>
+        <f t="shared" ref="C21:D21" si="66">C17-C20</f>
         <v>203.94000000000005</v>
       </c>
       <c r="D21" s="12">
-        <f t="shared" si="60"/>
+        <f t="shared" si="66"/>
         <v>156.553</v>
       </c>
       <c r="E21" s="12">
-        <f t="shared" ref="E21:G21" si="61">E17-E20</f>
+        <f t="shared" ref="E21:G21" si="67">E17-E20</f>
         <v>276.55500000000006</v>
       </c>
       <c r="F21" s="12">
-        <f t="shared" si="61"/>
+        <f t="shared" si="67"/>
         <v>269.57999999999993</v>
       </c>
       <c r="G21" s="12">
-        <f t="shared" si="61"/>
+        <f t="shared" si="67"/>
         <v>102.46400000000006</v>
       </c>
       <c r="H21" s="12">
-        <f t="shared" ref="H21:I21" si="62">H17-H20</f>
+        <f t="shared" ref="H21:I21" si="68">H17-H20</f>
         <v>396.70000000000005</v>
       </c>
       <c r="I21" s="12">
-        <f t="shared" si="62"/>
+        <f t="shared" si="68"/>
         <v>721.71699999999987</v>
       </c>
       <c r="J21" s="12">
-        <f t="shared" ref="J21" si="63">J17-J20</f>
+        <f t="shared" ref="J21" si="69">J17-J20</f>
         <v>727.2</v>
       </c>
       <c r="K21" s="12">
-        <f t="shared" ref="K21:L21" si="64">K17-K20</f>
+        <f t="shared" ref="K21:L21" si="70">K17-K20</f>
         <v>673.77</v>
       </c>
       <c r="L21" s="12">
-        <f t="shared" si="64"/>
+        <f t="shared" si="70"/>
         <v>884.90000000000009</v>
       </c>
       <c r="M21" s="12">
@@ -6731,11 +7023,11 @@
         <v>1000</v>
       </c>
       <c r="N21" s="12">
-        <f t="shared" ref="N21:Q21" si="65">N17-N20</f>
+        <f t="shared" ref="N21:Q21" si="71">N17-N20</f>
         <v>922.7</v>
       </c>
       <c r="O21" s="12">
-        <f t="shared" si="65"/>
+        <f t="shared" si="71"/>
         <v>1055.5480000000002</v>
       </c>
       <c r="P21" s="12">
@@ -6743,7 +7035,7 @@
         <v>1121.5999999999999</v>
       </c>
       <c r="Q21" s="12">
-        <f t="shared" si="65"/>
+        <f t="shared" si="71"/>
         <v>1264.7</v>
       </c>
       <c r="R21" s="12">
@@ -6755,19 +7047,19 @@
         <v>1318.3999999999996</v>
       </c>
       <c r="T21" s="12">
-        <f t="shared" ref="T21:U21" si="66">T17-T20</f>
+        <f t="shared" ref="T21:U21" si="72">T17-T20</f>
         <v>1173.2999999999997</v>
       </c>
       <c r="U21" s="12">
-        <f t="shared" si="66"/>
+        <f t="shared" si="72"/>
         <v>1249.3999999999996</v>
       </c>
       <c r="V21" s="12">
-        <f t="shared" ref="V21:Y21" si="67">V17-V20</f>
+        <f t="shared" ref="V21:Y21" si="73">V17-V20</f>
         <v>1258.4000000000001</v>
       </c>
       <c r="W21" s="12">
-        <f t="shared" si="67"/>
+        <f t="shared" si="73"/>
         <v>1224.9000000000003</v>
       </c>
       <c r="X21" s="12">
@@ -6775,125 +7067,128 @@
         <v>1169.1000000000004</v>
       </c>
       <c r="Y21" s="12">
-        <f t="shared" si="67"/>
+        <f t="shared" si="73"/>
         <v>1413.0999999999997</v>
       </c>
       <c r="Z21" s="12">
-        <f t="shared" ref="Z21:AB21" si="68">Z17-Z20</f>
+        <f t="shared" ref="Z21:AB21" si="74">Z17-Z20</f>
         <v>1303</v>
       </c>
       <c r="AA21" s="12">
-        <f t="shared" si="68"/>
+        <f t="shared" si="74"/>
         <v>1322.1000000000004</v>
       </c>
       <c r="AB21" s="12">
-        <f t="shared" si="68"/>
+        <f t="shared" si="74"/>
         <v>1285.7999999999997</v>
       </c>
       <c r="AC21" s="12">
-        <f t="shared" ref="AC21:AF21" si="69">AC17-AC20</f>
+        <f t="shared" ref="AC21:AG21" si="75">AC17-AC20</f>
         <v>1202.7999999999997</v>
       </c>
       <c r="AD21" s="12">
-        <f t="shared" si="69"/>
+        <f t="shared" si="75"/>
         <v>1327.2999999999997</v>
       </c>
       <c r="AE21" s="12">
-        <f t="shared" si="69"/>
+        <f t="shared" si="75"/>
         <v>1439.3000000000002</v>
       </c>
       <c r="AF21" s="12">
-        <f t="shared" si="69"/>
-        <v>1599.33</v>
-      </c>
-      <c r="AG21" s="12"/>
+        <f t="shared" si="75"/>
+        <v>1314.6000000000001</v>
+      </c>
+      <c r="AG21" s="12">
+        <f t="shared" si="75"/>
+        <v>1146.9999999999998</v>
+      </c>
       <c r="AH21" s="12"/>
       <c r="AI21" s="12"/>
       <c r="AJ21" s="12"/>
       <c r="AK21" s="12"/>
       <c r="AR21" s="12">
-        <f t="shared" ref="AR21:AT21" si="70">AR17-AR20</f>
+        <f t="shared" ref="AR21:AT21" si="76">AR17-AR20</f>
         <v>-1981</v>
       </c>
       <c r="AS21" s="12">
-        <f t="shared" si="70"/>
+        <f t="shared" si="76"/>
         <v>4338.0879999999997</v>
       </c>
       <c r="AT21" s="12">
-        <f t="shared" si="70"/>
+        <f t="shared" si="76"/>
         <v>5003.4999999999991</v>
       </c>
       <c r="AU21" s="12">
-        <f t="shared" ref="AU21:BG21" si="71">AU17-AU20</f>
+        <f t="shared" ref="AU21:BG21" si="77">AU17-AU20</f>
         <v>4901.8000000000011</v>
       </c>
       <c r="AV21" s="12">
-        <f t="shared" si="71"/>
-        <v>9146.6829999999991</v>
+        <f t="shared" si="77"/>
+        <v>5324</v>
       </c>
       <c r="AW21" s="12">
-        <f t="shared" si="71"/>
-        <v>9745.0299999999988</v>
+        <f t="shared" si="77"/>
+        <v>5185.1999999999989</v>
       </c>
       <c r="AX21" s="12">
-        <f t="shared" si="71"/>
-        <v>9933.1055099999994</v>
+        <f t="shared" si="77"/>
+        <v>10275.067999999999</v>
       </c>
       <c r="AY21" s="12">
-        <f t="shared" si="71"/>
-        <v>10334.5859471</v>
+        <f t="shared" si="77"/>
+        <v>10627.167279999998</v>
       </c>
       <c r="AZ21" s="12">
-        <f t="shared" si="71"/>
-        <v>10353.984029570998</v>
+        <f t="shared" si="77"/>
+        <v>10911.638292799998</v>
       </c>
       <c r="BA21" s="12">
-        <f t="shared" si="71"/>
-        <v>10288.85554436671</v>
+        <f t="shared" si="77"/>
+        <v>11084.848105727999</v>
       </c>
       <c r="BB21" s="12">
-        <f t="shared" si="71"/>
-        <v>9802.198166660377</v>
+        <f t="shared" si="77"/>
+        <v>10908.635857785279</v>
       </c>
       <c r="BC21" s="12">
-        <f t="shared" si="71"/>
-        <v>10061.71007855698</v>
+        <f t="shared" si="77"/>
+        <v>11369.178130163129</v>
       </c>
       <c r="BD21" s="12">
-        <f t="shared" si="71"/>
-        <v>9849.4151171660487</v>
+        <f t="shared" si="77"/>
+        <v>11208.464463874761</v>
       </c>
       <c r="BE21" s="12">
-        <f t="shared" si="71"/>
-        <v>9954.4831051825677</v>
+        <f t="shared" si="77"/>
+        <v>11399.083602519806</v>
       </c>
       <c r="BF21" s="12">
-        <f t="shared" si="71"/>
-        <v>9891.4437554041597</v>
+        <f t="shared" si="77"/>
+        <v>11389.155789227658</v>
       </c>
       <c r="BG21" s="12">
-        <f t="shared" si="71"/>
-        <v>9714.1094764782301</v>
+        <f t="shared" si="77"/>
+        <v>11436.33807208307</v>
       </c>
       <c r="BH21" s="12">
-        <f t="shared" ref="BH21:BL21" si="72">BH17-BH20</f>
-        <v>9666.8790524638043</v>
+        <f t="shared" ref="BH21:BL21" si="78">BH17-BH20</f>
+        <v>11530.732446523929</v>
       </c>
       <c r="BI21" s="12">
-        <f t="shared" si="72"/>
-        <v>9699.8160875714384</v>
+        <f t="shared" si="78"/>
+        <v>11664.464932127199</v>
       </c>
       <c r="BJ21" s="12">
-        <f t="shared" si="72"/>
-        <v>9785.5668582928301</v>
+        <f t="shared" si="78"/>
+        <v>11831.282087505762</v>
       </c>
       <c r="BK21" s="12">
-        <f t="shared" si="72"/>
-        <v>9908.5645647493184</v>
+        <f t="shared" si="78"/>
+        <v>12026.228261687926</v>
       </c>
       <c r="BL21" s="12">
-        <f t="shared" si="72"/>
-        <v>5845.0938990509285</v>
+        <f t="shared" si="78"/>
+        <v>6933.7907845693635</v>
       </c>
     </row>
     <row r="22" spans="2:124" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7016,11 +7311,14 @@
         <v>122.4</v>
       </c>
       <c r="AF22" s="2">
-        <f>+AE22</f>
-        <v>122.4</v>
+        <f>121.9-3.3</f>
+        <v>118.60000000000001</v>
+      </c>
+      <c r="AG22" s="2">
+        <v>114.8</v>
       </c>
       <c r="AT22" s="2">
-        <f t="shared" ref="AT22:AT24" si="73">SUM(Q22:T22)</f>
+        <f t="shared" ref="AT22:AT24" si="79">SUM(Q22:T22)</f>
         <v>89.6</v>
       </c>
       <c r="AU22" s="2">
@@ -7028,72 +7326,72 @@
         <v>548</v>
       </c>
       <c r="AV22" s="2">
-        <f t="shared" ref="AV22:BI22" si="74">+AU34*$BO$32</f>
-        <v>411.48300000000006</v>
+        <f>SUM(Y22:AB22)</f>
+        <v>539.09999999999991</v>
       </c>
       <c r="AW22" s="2">
-        <f t="shared" si="74"/>
-        <v>640.87898399999995</v>
+        <f t="shared" ref="AW22:AW24" si="80">SUM(AD22:AG22)</f>
+        <v>363.6</v>
       </c>
       <c r="AX22" s="2">
-        <f t="shared" si="74"/>
-        <v>890.14079961599987</v>
+        <f t="shared" ref="AV22:BI22" si="81">+AW34*$BO$32</f>
+        <v>689.31</v>
       </c>
       <c r="AY22" s="2">
-        <f t="shared" si="74"/>
-        <v>1149.8987110467838</v>
+        <f t="shared" si="81"/>
+        <v>952.45507199999986</v>
       </c>
       <c r="AZ22" s="2">
-        <f t="shared" si="74"/>
-        <v>1425.5263428423066</v>
+        <f t="shared" si="81"/>
+        <v>1230.3660084479998</v>
       </c>
       <c r="BA22" s="2">
-        <f t="shared" si="74"/>
-        <v>1708.2345917802261</v>
+        <f t="shared" si="81"/>
+        <v>1521.7741116779519</v>
       </c>
       <c r="BB22" s="2">
-        <f t="shared" si="74"/>
-        <v>1996.1647550477526</v>
+        <f t="shared" si="81"/>
+        <v>1824.3330448956947</v>
       </c>
       <c r="BC22" s="2">
-        <f t="shared" si="74"/>
-        <v>2279.3254651687475</v>
+        <f t="shared" si="81"/>
+        <v>2129.9242985600381</v>
       </c>
       <c r="BD22" s="2">
-        <f t="shared" si="74"/>
-        <v>2575.5103182181647</v>
+        <f t="shared" si="81"/>
+        <v>2453.9027568493939</v>
       </c>
       <c r="BE22" s="2">
-        <f t="shared" si="74"/>
-        <v>2873.708528667386</v>
+        <f t="shared" si="81"/>
+        <v>2781.7995701467735</v>
       </c>
       <c r="BF22" s="2">
-        <f t="shared" si="74"/>
-        <v>3181.5851278797845</v>
+        <f t="shared" si="81"/>
+        <v>3122.1407662907714</v>
       </c>
       <c r="BG22" s="2">
-        <f t="shared" si="74"/>
-        <v>3495.3378210785995</v>
+        <f t="shared" si="81"/>
+        <v>3470.4118836232142</v>
       </c>
       <c r="BH22" s="2">
-        <f t="shared" si="74"/>
-        <v>3812.3645562199636</v>
+        <f t="shared" si="81"/>
+        <v>3828.1738825601651</v>
       </c>
       <c r="BI22" s="2">
-        <f t="shared" si="74"/>
-        <v>4135.8664028283738</v>
+        <f t="shared" si="81"/>
+        <v>4196.7876344581828</v>
       </c>
       <c r="BJ22" s="2">
-        <f t="shared" ref="BJ22:BL22" si="75">+BI34*$BO$32</f>
-        <v>4467.9227825979697</v>
+        <f t="shared" ref="BJ22:BL22" si="82">+BI34*$BO$32</f>
+        <v>4577.4576960562326</v>
       </c>
       <c r="BK22" s="2">
         <f>+BJ34*$BO$32</f>
-        <v>4810.0065339793491</v>
+        <v>4971.2674508617201</v>
       </c>
       <c r="BL22" s="2">
-        <f t="shared" si="75"/>
-        <v>5163.2522403488374</v>
+        <f t="shared" si="82"/>
+        <v>5379.2073479629116</v>
       </c>
     </row>
     <row r="23" spans="2:124" x14ac:dyDescent="0.25">
@@ -7101,35 +7399,35 @@
         <v>118</v>
       </c>
       <c r="C23" s="12">
-        <f t="shared" ref="C23:D23" si="76">+C21+C22</f>
+        <f t="shared" ref="C23:D23" si="83">+C21+C22</f>
         <v>195.79700000000005</v>
       </c>
       <c r="D23" s="12">
-        <f t="shared" si="76"/>
+        <f t="shared" si="83"/>
         <v>151.78</v>
       </c>
       <c r="E23" s="12">
-        <f t="shared" ref="E23:F23" si="77">+E21+E22</f>
+        <f t="shared" ref="E23:F23" si="84">+E21+E22</f>
         <v>277.30200000000008</v>
       </c>
       <c r="F23" s="12">
-        <f t="shared" si="77"/>
+        <f t="shared" si="84"/>
         <v>272.8189999999999</v>
       </c>
       <c r="G23" s="12">
-        <f t="shared" ref="G23:J23" si="78">+G21+G22</f>
+        <f t="shared" ref="G23:J23" si="85">+G21+G22</f>
         <v>105.54400000000005</v>
       </c>
       <c r="H23" s="12">
-        <f t="shared" si="78"/>
+        <f t="shared" si="85"/>
         <v>394.81000000000006</v>
       </c>
       <c r="I23" s="12">
-        <f t="shared" si="78"/>
+        <f t="shared" si="85"/>
         <v>720.15699999999993</v>
       </c>
       <c r="J23" s="12">
-        <f t="shared" si="78"/>
+        <f t="shared" si="85"/>
         <v>717.572</v>
       </c>
       <c r="K23" s="12">
@@ -7145,82 +7443,85 @@
         <v>985.8</v>
       </c>
       <c r="N23" s="12">
-        <f t="shared" ref="N23:Q23" si="79">+N21+N22</f>
+        <f t="shared" ref="N23:Q23" si="86">+N21+N22</f>
         <v>908.30000000000007</v>
       </c>
       <c r="O23" s="12">
-        <f t="shared" si="79"/>
+        <f t="shared" si="86"/>
         <v>1041.4090000000003</v>
       </c>
       <c r="P23" s="12">
-        <f t="shared" si="79"/>
+        <f t="shared" si="86"/>
         <v>1107.6999999999998</v>
       </c>
       <c r="Q23" s="12">
-        <f t="shared" si="79"/>
+        <f t="shared" si="86"/>
         <v>1251.4000000000001</v>
       </c>
       <c r="R23" s="12">
-        <f t="shared" ref="R23" si="80">+R21+R22</f>
+        <f t="shared" ref="R23" si="87">+R21+R22</f>
         <v>1243.3000000000002</v>
       </c>
       <c r="S23" s="12">
-        <f t="shared" ref="S23" si="81">+S21+S22</f>
+        <f t="shared" ref="S23" si="88">+S21+S22</f>
         <v>1350.6999999999996</v>
       </c>
       <c r="T23" s="12">
-        <f t="shared" ref="T23:AF23" si="82">+T21+T22</f>
+        <f t="shared" ref="T23:AG23" si="89">+T21+T22</f>
         <v>1247.6999999999998</v>
       </c>
       <c r="U23" s="12">
-        <f t="shared" si="82"/>
+        <f t="shared" si="89"/>
         <v>1355.4999999999995</v>
       </c>
       <c r="V23" s="12">
-        <f t="shared" si="82"/>
+        <f t="shared" si="89"/>
         <v>1393.9</v>
       </c>
       <c r="W23" s="12">
-        <f t="shared" si="82"/>
+        <f t="shared" si="89"/>
         <v>1372.2000000000003</v>
       </c>
       <c r="X23" s="12">
-        <f t="shared" si="82"/>
+        <f t="shared" si="89"/>
         <v>1328.2000000000003</v>
       </c>
       <c r="Y23" s="12">
-        <f t="shared" si="82"/>
+        <f t="shared" si="89"/>
         <v>1579.6999999999996</v>
       </c>
       <c r="Z23" s="12">
-        <f t="shared" si="82"/>
+        <f t="shared" si="89"/>
         <v>1439.2</v>
       </c>
       <c r="AA23" s="12">
-        <f t="shared" si="82"/>
+        <f t="shared" si="89"/>
         <v>1440.7000000000003</v>
       </c>
       <c r="AB23" s="12">
-        <f t="shared" si="82"/>
+        <f t="shared" si="89"/>
         <v>1403.4999999999998</v>
       </c>
       <c r="AC23" s="12">
-        <f t="shared" si="82"/>
+        <f t="shared" si="89"/>
         <v>1320.4999999999998</v>
       </c>
       <c r="AD23" s="12">
-        <f t="shared" si="82"/>
+        <f t="shared" si="89"/>
         <v>1335.0999999999997</v>
       </c>
       <c r="AE23" s="12">
-        <f t="shared" si="82"/>
+        <f t="shared" si="89"/>
         <v>1561.7000000000003</v>
       </c>
       <c r="AF23" s="12">
-        <f t="shared" si="82"/>
-        <v>1721.73</v>
-      </c>
-      <c r="AG23" s="12"/>
+        <f t="shared" si="89"/>
+        <v>1433.2</v>
+      </c>
+      <c r="AG23" s="12">
+        <f t="shared" si="89"/>
+        <v>1261.7999999999997</v>
+      </c>
       <c r="AH23" s="12"/>
       <c r="AI23" s="12"/>
       <c r="AJ23" s="12"/>
@@ -7230,76 +7531,76 @@
         <v>5093.0999999999995</v>
       </c>
       <c r="AU23" s="2">
-        <f t="shared" ref="AU23:BG23" si="83">+AU21+AU22</f>
+        <f t="shared" ref="AU23:BG23" si="90">+AU21+AU22</f>
         <v>5449.8000000000011</v>
       </c>
       <c r="AV23" s="2">
-        <f t="shared" si="83"/>
-        <v>9558.1659999999993</v>
+        <f t="shared" si="90"/>
+        <v>5863.1</v>
       </c>
       <c r="AW23" s="2">
-        <f t="shared" si="83"/>
-        <v>10385.908983999998</v>
+        <f t="shared" si="90"/>
+        <v>5548.7999999999993</v>
       </c>
       <c r="AX23" s="2">
-        <f t="shared" si="83"/>
-        <v>10823.246309615999</v>
+        <f t="shared" si="90"/>
+        <v>10964.377999999999</v>
       </c>
       <c r="AY23" s="2">
-        <f t="shared" si="83"/>
-        <v>11484.484658146785</v>
+        <f t="shared" si="90"/>
+        <v>11579.622351999999</v>
       </c>
       <c r="AZ23" s="2">
-        <f t="shared" si="83"/>
-        <v>11779.510372413304</v>
+        <f t="shared" si="90"/>
+        <v>12142.004301247998</v>
       </c>
       <c r="BA23" s="2">
-        <f t="shared" si="83"/>
-        <v>11997.090136146937</v>
+        <f t="shared" si="90"/>
+        <v>12606.622217405951</v>
       </c>
       <c r="BB23" s="2">
-        <f t="shared" si="83"/>
-        <v>11798.362921708129</v>
+        <f t="shared" si="90"/>
+        <v>12732.968902680974</v>
       </c>
       <c r="BC23" s="2">
-        <f t="shared" si="83"/>
-        <v>12341.035543725728</v>
+        <f t="shared" si="90"/>
+        <v>13499.102428723167</v>
       </c>
       <c r="BD23" s="2">
-        <f t="shared" si="83"/>
-        <v>12424.925435384213</v>
+        <f t="shared" si="90"/>
+        <v>13662.367220724154</v>
       </c>
       <c r="BE23" s="2">
-        <f t="shared" si="83"/>
-        <v>12828.191633849954</v>
+        <f t="shared" si="90"/>
+        <v>14180.883172666579</v>
       </c>
       <c r="BF23" s="2">
-        <f t="shared" si="83"/>
-        <v>13073.028883283943</v>
+        <f t="shared" si="90"/>
+        <v>14511.296555518429</v>
       </c>
       <c r="BG23" s="2">
-        <f t="shared" si="83"/>
-        <v>13209.44729755683</v>
+        <f t="shared" si="90"/>
+        <v>14906.749955706284</v>
       </c>
       <c r="BH23" s="2">
-        <f t="shared" ref="BH23:BL23" si="84">+BH21+BH22</f>
-        <v>13479.243608683768</v>
+        <f t="shared" ref="BH23:BL23" si="91">+BH21+BH22</f>
+        <v>15358.906329084093</v>
       </c>
       <c r="BI23" s="2">
-        <f t="shared" si="84"/>
-        <v>13835.682490399813</v>
+        <f t="shared" si="91"/>
+        <v>15861.252566585383</v>
       </c>
       <c r="BJ23" s="2">
-        <f t="shared" si="84"/>
-        <v>14253.489640890799</v>
+        <f t="shared" si="91"/>
+        <v>16408.739783561996</v>
       </c>
       <c r="BK23" s="2">
-        <f t="shared" si="84"/>
-        <v>14718.571098728667</v>
+        <f t="shared" si="91"/>
+        <v>16997.495712549644</v>
       </c>
       <c r="BL23" s="2">
-        <f t="shared" si="84"/>
-        <v>11008.346139399766</v>
+        <f t="shared" si="91"/>
+        <v>12312.998132532275</v>
       </c>
     </row>
     <row r="24" spans="2:124" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7395,11 +7696,13 @@
         <v>263.7</v>
       </c>
       <c r="AF24" s="2">
-        <f>+AF23*0.1</f>
-        <v>172.173</v>
+        <v>200.9</v>
+      </c>
+      <c r="AG24" s="2">
+        <v>280.10000000000002</v>
       </c>
       <c r="AT24" s="2">
-        <f t="shared" si="73"/>
+        <f t="shared" si="79"/>
         <v>1011.4</v>
       </c>
       <c r="AU24" s="2">
@@ -7407,72 +7710,72 @@
         <v>919.39999999999986</v>
       </c>
       <c r="AV24" s="2">
-        <f t="shared" ref="AV24:BG24" si="85">+AV23*0.2</f>
-        <v>1911.6332</v>
+        <f>SUM(Y24:AB24)</f>
+        <v>1124.1000000000001</v>
       </c>
       <c r="AW24" s="2">
-        <f t="shared" si="85"/>
-        <v>2077.1817967999996</v>
+        <f t="shared" si="80"/>
+        <v>1026.9000000000001</v>
       </c>
       <c r="AX24" s="2">
-        <f t="shared" si="85"/>
-        <v>2164.6492619231999</v>
+        <f t="shared" ref="AV24:BG24" si="92">+AX23*0.2</f>
+        <v>2192.8755999999998</v>
       </c>
       <c r="AY24" s="2">
-        <f t="shared" si="85"/>
-        <v>2296.8969316293569</v>
+        <f t="shared" si="92"/>
+        <v>2315.9244703999998</v>
       </c>
       <c r="AZ24" s="2">
-        <f t="shared" si="85"/>
-        <v>2355.9020744826607</v>
+        <f t="shared" si="92"/>
+        <v>2428.4008602495996</v>
       </c>
       <c r="BA24" s="2">
-        <f t="shared" si="85"/>
-        <v>2399.4180272293875</v>
+        <f t="shared" si="92"/>
+        <v>2521.3244434811904</v>
       </c>
       <c r="BB24" s="2">
-        <f t="shared" si="85"/>
-        <v>2359.6725843416257</v>
+        <f t="shared" si="92"/>
+        <v>2546.593780536195</v>
       </c>
       <c r="BC24" s="2">
-        <f t="shared" si="85"/>
-        <v>2468.2071087451459</v>
+        <f t="shared" si="92"/>
+        <v>2699.8204857446335</v>
       </c>
       <c r="BD24" s="2">
-        <f t="shared" si="85"/>
-        <v>2484.9850870768428</v>
+        <f t="shared" si="92"/>
+        <v>2732.4734441448309</v>
       </c>
       <c r="BE24" s="2">
-        <f t="shared" si="85"/>
-        <v>2565.6383267699912</v>
+        <f t="shared" si="92"/>
+        <v>2836.1766345333162</v>
       </c>
       <c r="BF24" s="2">
-        <f t="shared" si="85"/>
-        <v>2614.6057766567887</v>
+        <f t="shared" si="92"/>
+        <v>2902.2593111036858</v>
       </c>
       <c r="BG24" s="2">
-        <f t="shared" si="85"/>
-        <v>2641.8894595113661</v>
+        <f t="shared" si="92"/>
+        <v>2981.3499911412569</v>
       </c>
       <c r="BH24" s="2">
-        <f t="shared" ref="BH24:BL24" si="86">+BH23*0.2</f>
-        <v>2695.8487217367538</v>
+        <f t="shared" ref="BH24:BL24" si="93">+BH23*0.2</f>
+        <v>3071.7812658168186</v>
       </c>
       <c r="BI24" s="2">
-        <f t="shared" si="86"/>
-        <v>2767.1364980799626</v>
+        <f t="shared" si="93"/>
+        <v>3172.2505133170766</v>
       </c>
       <c r="BJ24" s="2">
         <f>+BJ23*0.2</f>
-        <v>2850.6979281781601</v>
+        <v>3281.7479567123992</v>
       </c>
       <c r="BK24" s="2">
         <f>+BK23*0.2</f>
-        <v>2943.7142197457338</v>
+        <v>3399.4991425099288</v>
       </c>
       <c r="BL24" s="2">
-        <f t="shared" si="86"/>
-        <v>2201.6692278799533</v>
+        <f t="shared" si="93"/>
+        <v>2462.599626506455</v>
       </c>
     </row>
     <row r="25" spans="2:124" x14ac:dyDescent="0.25">
@@ -7480,35 +7783,35 @@
         <v>120</v>
       </c>
       <c r="C25" s="12">
-        <f t="shared" ref="C25:D25" si="87">+C23-C24</f>
+        <f t="shared" ref="C25:D25" si="94">+C23-C24</f>
         <v>187.74200000000005</v>
       </c>
       <c r="D25" s="12">
-        <f t="shared" si="87"/>
+        <f t="shared" si="94"/>
         <v>151.78</v>
       </c>
       <c r="E25" s="12">
-        <f t="shared" ref="E25:F25" si="88">+E23-E24</f>
+        <f t="shared" ref="E25:F25" si="95">+E23-E24</f>
         <v>225.76800000000009</v>
       </c>
       <c r="F25" s="12">
-        <f t="shared" si="88"/>
+        <f t="shared" si="95"/>
         <v>213.10799999999989</v>
       </c>
       <c r="G25" s="12">
-        <f t="shared" ref="G25:J25" si="89">+G23-G24</f>
+        <f t="shared" ref="G25:J25" si="96">+G23-G24</f>
         <v>92.396000000000058</v>
       </c>
       <c r="H25" s="12">
-        <f t="shared" si="89"/>
+        <f t="shared" si="96"/>
         <v>301.09400000000005</v>
       </c>
       <c r="I25" s="12">
-        <f t="shared" si="89"/>
+        <f t="shared" si="96"/>
         <v>665.37599999999998</v>
       </c>
       <c r="J25" s="12">
-        <f t="shared" si="89"/>
+        <f t="shared" si="96"/>
         <v>730.072</v>
       </c>
       <c r="K25" s="12">
@@ -7524,82 +7827,85 @@
         <v>779.8</v>
       </c>
       <c r="N25" s="12">
-        <f t="shared" ref="N25:Y25" si="90">+N23-N24</f>
+        <f t="shared" ref="N25:Y25" si="97">+N23-N24</f>
         <v>897.40000000000009</v>
       </c>
       <c r="O25" s="12">
-        <f t="shared" si="90"/>
+        <f t="shared" si="97"/>
         <v>810.59600000000034</v>
       </c>
       <c r="P25" s="12">
-        <f t="shared" si="90"/>
+        <f t="shared" si="97"/>
         <v>868.69999999999982</v>
       </c>
       <c r="Q25" s="12">
-        <f t="shared" si="90"/>
+        <f t="shared" si="97"/>
         <v>1002.4000000000001</v>
       </c>
       <c r="R25" s="12">
-        <f t="shared" si="90"/>
+        <f t="shared" si="97"/>
         <v>984.70000000000016</v>
       </c>
       <c r="S25" s="12">
-        <f t="shared" si="90"/>
+        <f t="shared" si="97"/>
         <v>1104.7999999999995</v>
       </c>
       <c r="T25" s="12">
-        <f t="shared" si="90"/>
+        <f t="shared" si="97"/>
         <v>989.79999999999984</v>
       </c>
       <c r="U25" s="12">
-        <f t="shared" si="90"/>
+        <f t="shared" si="97"/>
         <v>1141.0999999999995</v>
       </c>
       <c r="V25" s="12">
-        <f t="shared" si="90"/>
+        <f t="shared" si="97"/>
         <v>1124.5</v>
       </c>
       <c r="W25" s="12">
-        <f t="shared" si="90"/>
+        <f t="shared" si="97"/>
         <v>1115.4000000000003</v>
       </c>
       <c r="X25" s="12">
-        <f t="shared" si="90"/>
+        <f t="shared" si="97"/>
         <v>1149.4000000000003</v>
       </c>
       <c r="Y25" s="12">
-        <f t="shared" si="90"/>
+        <f t="shared" si="97"/>
         <v>1318.5999999999995</v>
       </c>
       <c r="Z25" s="12">
-        <f t="shared" ref="Z25:AF25" si="91">+Z23-Z24</f>
+        <f t="shared" ref="Z25:AG25" si="98">+Z23-Z24</f>
         <v>1138.5999999999999</v>
       </c>
       <c r="AA25" s="12">
-        <f t="shared" si="91"/>
+        <f t="shared" si="98"/>
         <v>1158.0000000000002</v>
       </c>
       <c r="AB25" s="12">
-        <f t="shared" si="91"/>
+        <f t="shared" si="98"/>
         <v>1123.7999999999997</v>
       </c>
       <c r="AC25" s="12">
-        <f t="shared" si="91"/>
+        <f t="shared" si="98"/>
         <v>1188.4499999999998</v>
       </c>
       <c r="AD25" s="12">
-        <f t="shared" si="91"/>
+        <f t="shared" si="98"/>
         <v>1052.8999999999996</v>
       </c>
       <c r="AE25" s="12">
-        <f t="shared" si="91"/>
+        <f t="shared" si="98"/>
         <v>1298.0000000000002</v>
       </c>
       <c r="AF25" s="12">
-        <f t="shared" si="91"/>
-        <v>1549.557</v>
-      </c>
-      <c r="AG25" s="12"/>
+        <f t="shared" si="98"/>
+        <v>1232.3</v>
+      </c>
+      <c r="AG25" s="12">
+        <f t="shared" si="98"/>
+        <v>981.6999999999997</v>
+      </c>
       <c r="AH25" s="12"/>
       <c r="AI25" s="12"/>
       <c r="AJ25" s="12"/>
@@ -7609,316 +7915,316 @@
         <v>4081.6999999999994</v>
       </c>
       <c r="AU25" s="2">
-        <f t="shared" ref="AU25:BA25" si="92">+AU23-AU24</f>
+        <f t="shared" ref="AU25:BA25" si="99">+AU23-AU24</f>
         <v>4530.4000000000015</v>
       </c>
       <c r="AV25" s="2">
-        <f t="shared" si="92"/>
-        <v>7646.532799999999</v>
+        <f t="shared" si="99"/>
+        <v>4739</v>
       </c>
       <c r="AW25" s="2">
-        <f t="shared" si="92"/>
-        <v>8308.7271871999983</v>
+        <f t="shared" si="99"/>
+        <v>4521.8999999999996</v>
       </c>
       <c r="AX25" s="2">
-        <f t="shared" si="92"/>
-        <v>8658.5970476927996</v>
+        <f t="shared" si="99"/>
+        <v>8771.5023999999994</v>
       </c>
       <c r="AY25" s="2">
-        <f t="shared" si="92"/>
-        <v>9187.5877265174277</v>
+        <f t="shared" si="99"/>
+        <v>9263.6978815999992</v>
       </c>
       <c r="AZ25" s="2">
-        <f t="shared" si="92"/>
-        <v>9423.6082979306429</v>
+        <f t="shared" si="99"/>
+        <v>9713.6034409983986</v>
       </c>
       <c r="BA25" s="2">
-        <f t="shared" si="92"/>
-        <v>9597.6721089175498</v>
+        <f t="shared" si="99"/>
+        <v>10085.297773924762</v>
       </c>
       <c r="BB25" s="2">
-        <f t="shared" ref="BB25:BG25" si="93">+BB23-BB24</f>
-        <v>9438.6903373665027</v>
+        <f t="shared" ref="BB25:BG25" si="100">+BB23-BB24</f>
+        <v>10186.375122144778</v>
       </c>
       <c r="BC25" s="2">
-        <f t="shared" si="93"/>
-        <v>9872.8284349805817</v>
+        <f t="shared" si="100"/>
+        <v>10799.281942978534</v>
       </c>
       <c r="BD25" s="2">
-        <f t="shared" si="93"/>
-        <v>9939.9403483073711</v>
+        <f t="shared" si="100"/>
+        <v>10929.893776579323</v>
       </c>
       <c r="BE25" s="2">
-        <f t="shared" si="93"/>
-        <v>10262.553307079963</v>
+        <f t="shared" si="100"/>
+        <v>11344.706538133263</v>
       </c>
       <c r="BF25" s="2">
-        <f t="shared" si="93"/>
-        <v>10458.423106627155</v>
+        <f t="shared" si="100"/>
+        <v>11609.037244414743</v>
       </c>
       <c r="BG25" s="2">
-        <f t="shared" si="93"/>
-        <v>10567.557838045464</v>
+        <f t="shared" si="100"/>
+        <v>11925.399964565027</v>
       </c>
       <c r="BH25" s="2">
-        <f t="shared" ref="BH25:BL25" si="94">+BH23-BH24</f>
-        <v>10783.394886947015</v>
+        <f t="shared" ref="BH25:BL25" si="101">+BH23-BH24</f>
+        <v>12287.125063267275</v>
       </c>
       <c r="BI25" s="2">
-        <f t="shared" si="94"/>
-        <v>11068.54599231985</v>
+        <f t="shared" si="101"/>
+        <v>12689.002053268307</v>
       </c>
       <c r="BJ25" s="2">
-        <f t="shared" si="94"/>
-        <v>11402.791712712638</v>
+        <f t="shared" si="101"/>
+        <v>13126.991826849597</v>
       </c>
       <c r="BK25" s="2">
-        <f t="shared" si="94"/>
-        <v>11774.856878982933</v>
+        <f t="shared" si="101"/>
+        <v>13597.996570039715</v>
       </c>
       <c r="BL25" s="2">
-        <f t="shared" si="94"/>
-        <v>8806.6769115198131</v>
+        <f t="shared" si="101"/>
+        <v>9850.3985060258201</v>
       </c>
       <c r="BM25" s="2">
-        <f t="shared" ref="BM25:CR25" si="95">+BL25*(1+$BO$30)</f>
-        <v>8366.3430659438218</v>
+        <f t="shared" ref="BM25:CR25" si="102">+BL25*(1+$BO$30)</f>
+        <v>9357.8785807245295</v>
       </c>
       <c r="BN25" s="2">
-        <f t="shared" si="95"/>
-        <v>7948.0259126466299</v>
+        <f t="shared" si="102"/>
+        <v>8889.9846516883026</v>
       </c>
       <c r="BO25" s="2">
-        <f t="shared" si="95"/>
-        <v>7550.6246170142977</v>
+        <f t="shared" si="102"/>
+        <v>8445.4854191038867</v>
       </c>
       <c r="BP25" s="2">
-        <f t="shared" si="95"/>
-        <v>7173.0933861635822</v>
+        <f t="shared" si="102"/>
+        <v>8023.2111481486918</v>
       </c>
       <c r="BQ25" s="2">
-        <f t="shared" si="95"/>
-        <v>6814.4387168554031</v>
+        <f t="shared" si="102"/>
+        <v>7622.0505907412571</v>
       </c>
       <c r="BR25" s="2">
-        <f t="shared" si="95"/>
-        <v>6473.716781012633</v>
+        <f t="shared" si="102"/>
+        <v>7240.9480612041943</v>
       </c>
       <c r="BS25" s="2">
-        <f t="shared" si="95"/>
-        <v>6150.0309419620007</v>
+        <f t="shared" si="102"/>
+        <v>6878.9006581439844</v>
       </c>
       <c r="BT25" s="2">
-        <f t="shared" si="95"/>
-        <v>5842.5293948639001</v>
+        <f t="shared" si="102"/>
+        <v>6534.9556252367847</v>
       </c>
       <c r="BU25" s="2">
-        <f t="shared" si="95"/>
-        <v>5550.4029251207048</v>
+        <f t="shared" si="102"/>
+        <v>6208.2078439749448</v>
       </c>
       <c r="BV25" s="2">
-        <f t="shared" si="95"/>
-        <v>5272.8827788646695</v>
+        <f t="shared" si="102"/>
+        <v>5897.7974517761977</v>
       </c>
       <c r="BW25" s="2">
-        <f t="shared" si="95"/>
-        <v>5009.2386399214356</v>
+        <f t="shared" si="102"/>
+        <v>5602.9075791873875</v>
       </c>
       <c r="BX25" s="2">
-        <f t="shared" si="95"/>
-        <v>4758.7767079253636</v>
+        <f t="shared" si="102"/>
+        <v>5322.7622002280177</v>
       </c>
       <c r="BY25" s="2">
-        <f t="shared" si="95"/>
-        <v>4520.837872529095</v>
+        <f t="shared" si="102"/>
+        <v>5056.6240902166164</v>
       </c>
       <c r="BZ25" s="2">
-        <f t="shared" si="95"/>
-        <v>4294.7959789026399</v>
+        <f t="shared" si="102"/>
+        <v>4803.792885705785</v>
       </c>
       <c r="CA25" s="2">
-        <f t="shared" si="95"/>
-        <v>4080.0561799575075</v>
+        <f t="shared" si="102"/>
+        <v>4563.6032414204956</v>
       </c>
       <c r="CB25" s="2">
-        <f t="shared" si="95"/>
-        <v>3876.053370959632</v>
+        <f t="shared" si="102"/>
+        <v>4335.4230793494708</v>
       </c>
       <c r="CC25" s="2">
-        <f t="shared" si="95"/>
-        <v>3682.2507024116503</v>
+        <f t="shared" si="102"/>
+        <v>4118.651925381997</v>
       </c>
       <c r="CD25" s="2">
-        <f t="shared" si="95"/>
-        <v>3498.1381672910675</v>
+        <f t="shared" si="102"/>
+        <v>3912.719329112897</v>
       </c>
       <c r="CE25" s="2">
-        <f t="shared" si="95"/>
-        <v>3323.2312589265139</v>
+        <f t="shared" si="102"/>
+        <v>3717.0833626572521</v>
       </c>
       <c r="CF25" s="2">
-        <f t="shared" si="95"/>
-        <v>3157.069695980188</v>
+        <f t="shared" si="102"/>
+        <v>3531.2291945243892</v>
       </c>
       <c r="CG25" s="2">
-        <f t="shared" si="95"/>
-        <v>2999.2162111811786</v>
+        <f t="shared" si="102"/>
+        <v>3354.6677347981695</v>
       </c>
       <c r="CH25" s="2">
-        <f t="shared" si="95"/>
-        <v>2849.2554006221194</v>
+        <f t="shared" si="102"/>
+        <v>3186.9343480582606</v>
       </c>
       <c r="CI25" s="2">
-        <f t="shared" si="95"/>
-        <v>2706.7926305910132</v>
+        <f t="shared" si="102"/>
+        <v>3027.5876306553473</v>
       </c>
       <c r="CJ25" s="2">
-        <f t="shared" si="95"/>
-        <v>2571.4529990614624</v>
+        <f t="shared" si="102"/>
+        <v>2876.2082491225797</v>
       </c>
       <c r="CK25" s="2">
-        <f t="shared" si="95"/>
-        <v>2442.8803491083891</v>
+        <f t="shared" si="102"/>
+        <v>2732.3978366664505</v>
       </c>
       <c r="CL25" s="2">
-        <f t="shared" si="95"/>
-        <v>2320.7363316529695</v>
+        <f t="shared" si="102"/>
+        <v>2595.777944833128</v>
       </c>
       <c r="CM25" s="2">
-        <f t="shared" si="95"/>
-        <v>2204.699515070321</v>
+        <f t="shared" si="102"/>
+        <v>2465.9890475914713</v>
       </c>
       <c r="CN25" s="2">
-        <f t="shared" si="95"/>
-        <v>2094.4645393168048</v>
+        <f t="shared" si="102"/>
+        <v>2342.6895952118975</v>
       </c>
       <c r="CO25" s="2">
-        <f t="shared" si="95"/>
-        <v>1989.7413123509646</v>
+        <f t="shared" si="102"/>
+        <v>2225.5551154513028</v>
       </c>
       <c r="CP25" s="2">
-        <f t="shared" si="95"/>
-        <v>1890.2542467334163</v>
+        <f t="shared" si="102"/>
+        <v>2114.2773596787374</v>
       </c>
       <c r="CQ25" s="2">
-        <f t="shared" si="95"/>
-        <v>1795.7415343967455</v>
+        <f t="shared" si="102"/>
+        <v>2008.5634916948004</v>
       </c>
       <c r="CR25" s="2">
-        <f t="shared" si="95"/>
-        <v>1705.9544576769081</v>
+        <f t="shared" si="102"/>
+        <v>1908.1353171100602</v>
       </c>
       <c r="CS25" s="2">
-        <f t="shared" ref="CS25:DT25" si="96">+CR25*(1+$BO$30)</f>
-        <v>1620.6567347930627</v>
+        <f t="shared" ref="CS25:DT25" si="103">+CR25*(1+$BO$30)</f>
+        <v>1812.728551254557</v>
       </c>
       <c r="CT25" s="2">
-        <f t="shared" si="96"/>
-        <v>1539.6238980534094</v>
+        <f t="shared" si="103"/>
+        <v>1722.0921236918291</v>
       </c>
       <c r="CU25" s="2">
-        <f t="shared" si="96"/>
-        <v>1462.642703150739</v>
+        <f t="shared" si="103"/>
+        <v>1635.9875175072375</v>
       </c>
       <c r="CV25" s="2">
-        <f t="shared" si="96"/>
-        <v>1389.5105679932019</v>
+        <f t="shared" si="103"/>
+        <v>1554.1881416318756</v>
       </c>
       <c r="CW25" s="2">
-        <f t="shared" si="96"/>
-        <v>1320.0350395935418</v>
+        <f t="shared" si="103"/>
+        <v>1476.4787345502818</v>
       </c>
       <c r="CX25" s="2">
-        <f t="shared" si="96"/>
-        <v>1254.0332876138646</v>
+        <f t="shared" si="103"/>
+        <v>1402.6547978227677</v>
       </c>
       <c r="CY25" s="2">
-        <f t="shared" si="96"/>
-        <v>1191.3316232331713</v>
+        <f t="shared" si="103"/>
+        <v>1332.5220579316292</v>
       </c>
       <c r="CZ25" s="2">
-        <f t="shared" si="96"/>
-        <v>1131.7650420715127</v>
+        <f t="shared" si="103"/>
+        <v>1265.8959550350478</v>
       </c>
       <c r="DA25" s="2">
-        <f t="shared" si="96"/>
-        <v>1075.1767899679369</v>
+        <f t="shared" si="103"/>
+        <v>1202.6011572832954</v>
       </c>
       <c r="DB25" s="2">
-        <f t="shared" si="96"/>
-        <v>1021.41795046954</v>
+        <f t="shared" si="103"/>
+        <v>1142.4710994191305</v>
       </c>
       <c r="DC25" s="2">
-        <f t="shared" si="96"/>
-        <v>970.34705294606295</v>
+        <f t="shared" si="103"/>
+        <v>1085.3475444481739</v>
       </c>
       <c r="DD25" s="2">
-        <f t="shared" si="96"/>
-        <v>921.8297002987598</v>
+        <f t="shared" si="103"/>
+        <v>1031.0801672257653</v>
       </c>
       <c r="DE25" s="2">
-        <f t="shared" si="96"/>
-        <v>875.73821528382177</v>
+        <f t="shared" si="103"/>
+        <v>979.526158864477</v>
       </c>
       <c r="DF25" s="2">
-        <f t="shared" si="96"/>
-        <v>831.95130451963064</v>
+        <f t="shared" si="103"/>
+        <v>930.5498509212531</v>
       </c>
       <c r="DG25" s="2">
-        <f t="shared" si="96"/>
-        <v>790.35373929364903</v>
+        <f t="shared" si="103"/>
+        <v>884.02235837519038</v>
       </c>
       <c r="DH25" s="2">
-        <f t="shared" si="96"/>
-        <v>750.8360523289665</v>
+        <f t="shared" si="103"/>
+        <v>839.82124045643081</v>
       </c>
       <c r="DI25" s="2">
-        <f t="shared" si="96"/>
-        <v>713.29424971251819</v>
+        <f t="shared" si="103"/>
+        <v>797.83017843360926</v>
       </c>
       <c r="DJ25" s="2">
-        <f t="shared" si="96"/>
-        <v>677.62953722689224</v>
+        <f t="shared" si="103"/>
+        <v>757.93866951192877</v>
       </c>
       <c r="DK25" s="2">
-        <f t="shared" si="96"/>
-        <v>643.74806036554764</v>
+        <f t="shared" si="103"/>
+        <v>720.04173603633228</v>
       </c>
       <c r="DL25" s="2">
-        <f t="shared" si="96"/>
-        <v>611.56065734727019</v>
+        <f t="shared" si="103"/>
+        <v>684.03964923451565</v>
       </c>
       <c r="DM25" s="2">
-        <f t="shared" si="96"/>
-        <v>580.98262447990669</v>
+        <f t="shared" si="103"/>
+        <v>649.83766677278982</v>
       </c>
       <c r="DN25" s="2">
-        <f t="shared" si="96"/>
-        <v>551.93349325591134</v>
+        <f t="shared" si="103"/>
+        <v>617.34578343415035</v>
       </c>
       <c r="DO25" s="2">
-        <f t="shared" si="96"/>
-        <v>524.33681859311571</v>
+        <f t="shared" si="103"/>
+        <v>586.47849426244284</v>
       </c>
       <c r="DP25" s="2">
-        <f t="shared" si="96"/>
-        <v>498.11997766345991</v>
+        <f t="shared" si="103"/>
+        <v>557.15456954932063</v>
       </c>
       <c r="DQ25" s="2">
-        <f t="shared" si="96"/>
-        <v>473.21397878028688</v>
+        <f t="shared" si="103"/>
+        <v>529.2968410718546</v>
       </c>
       <c r="DR25" s="2">
-        <f t="shared" si="96"/>
-        <v>449.55327984127251</v>
+        <f t="shared" si="103"/>
+        <v>502.83199901826185</v>
       </c>
       <c r="DS25" s="2">
-        <f t="shared" si="96"/>
-        <v>427.07561584920887</v>
+        <f t="shared" si="103"/>
+        <v>477.69039906734872</v>
       </c>
       <c r="DT25" s="2">
-        <f t="shared" si="96"/>
-        <v>405.72183505674843</v>
+        <f t="shared" si="103"/>
+        <v>453.80587911398129</v>
       </c>
     </row>
     <row r="26" spans="2:124" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -7926,59 +8232,59 @@
         <v>121</v>
       </c>
       <c r="C26" s="21">
-        <f t="shared" ref="C26:D26" si="97">+C25/C27</f>
+        <f t="shared" ref="C26:D26" si="104">+C25/C27</f>
         <v>0.72267387254222692</v>
       </c>
       <c r="D26" s="21">
-        <f t="shared" si="97"/>
+        <f t="shared" si="104"/>
         <v>0.58419164626730091</v>
       </c>
       <c r="E26" s="21">
-        <f t="shared" ref="E26:G26" si="98">+E25/E27</f>
+        <f t="shared" ref="E26:G26" si="105">+E25/E27</f>
         <v>0.86775439607956217</v>
       </c>
       <c r="F26" s="21">
-        <f t="shared" si="98"/>
+        <f t="shared" si="105"/>
         <v>0.82020768064290128</v>
       </c>
       <c r="G26" s="21">
-        <f t="shared" si="98"/>
+        <f t="shared" si="105"/>
         <v>0.35472390612462734</v>
       </c>
       <c r="H26" s="21">
-        <f t="shared" ref="H26:I26" si="99">+H25/H27</f>
+        <f t="shared" ref="H26:I26" si="106">+H25/H27</f>
         <v>1.1487402139576055</v>
       </c>
       <c r="I26" s="21">
-        <f t="shared" si="99"/>
+        <f t="shared" si="106"/>
         <v>2.5250023717814924</v>
       </c>
       <c r="J26" s="21">
-        <f t="shared" ref="J26:K26" si="100">+J25/J27</f>
+        <f t="shared" ref="J26:K26" si="107">+J25/J27</f>
         <v>2.771692046028329</v>
       </c>
       <c r="K26" s="21">
-        <f t="shared" si="100"/>
+        <f t="shared" si="107"/>
         <v>2.2136444018645935</v>
       </c>
       <c r="L26" s="21">
-        <f t="shared" ref="L26:P26" si="101">+L25/L27</f>
+        <f t="shared" ref="L26:P26" si="108">+L25/L27</f>
         <v>2.5575826681870013</v>
       </c>
       <c r="M26" s="21">
-        <f t="shared" si="101"/>
+        <f t="shared" si="108"/>
         <v>2.9774723176785032</v>
       </c>
       <c r="N26" s="21">
-        <f t="shared" si="101"/>
+        <f t="shared" si="108"/>
         <v>3.438314176245211</v>
       </c>
       <c r="O26" s="21">
-        <f t="shared" si="101"/>
+        <f t="shared" si="108"/>
         <v>3.1211942689261374</v>
       </c>
       <c r="P26" s="21">
-        <f t="shared" si="101"/>
+        <f t="shared" si="108"/>
         <v>3.3801556420233454</v>
       </c>
       <c r="Q26" s="21">
@@ -7986,66 +8292,69 @@
         <v>3.8867778208607993</v>
       </c>
       <c r="R26" s="21">
-        <f t="shared" ref="R26:Y26" si="102">+R25/R27</f>
+        <f t="shared" ref="R26:Y26" si="109">+R25/R27</f>
         <v>3.8063393892539628</v>
       </c>
       <c r="S26" s="21">
-        <f t="shared" si="102"/>
+        <f t="shared" si="109"/>
         <v>4.2574181117533696</v>
       </c>
       <c r="T26" s="21">
-        <f t="shared" si="102"/>
+        <f t="shared" si="109"/>
         <v>3.8025355359200916</v>
       </c>
       <c r="U26" s="21">
-        <f t="shared" si="102"/>
+        <f t="shared" si="109"/>
         <v>4.3837879369957715</v>
       </c>
       <c r="V26" s="21">
-        <f t="shared" si="102"/>
+        <f t="shared" si="109"/>
         <v>4.3183563748079878</v>
       </c>
       <c r="W26" s="21">
-        <f t="shared" si="102"/>
+        <f t="shared" si="109"/>
         <v>4.280122793553339</v>
       </c>
       <c r="X26" s="21">
-        <f t="shared" si="102"/>
+        <f t="shared" si="109"/>
         <v>4.4055193560751258</v>
       </c>
       <c r="Y26" s="21">
-        <f t="shared" si="102"/>
+        <f t="shared" si="109"/>
         <v>5.0501723477594762</v>
       </c>
       <c r="Z26" s="21">
-        <f t="shared" ref="Z26:AF26" si="103">+Z25/Z27</f>
+        <f t="shared" ref="Z26:AG26" si="110">+Z25/Z27</f>
         <v>4.411468423091824</v>
       </c>
       <c r="AA26" s="21">
-        <f t="shared" si="103"/>
+        <f t="shared" si="110"/>
         <v>4.4367816091954033</v>
       </c>
       <c r="AB26" s="21">
-        <f t="shared" si="103"/>
+        <f t="shared" si="110"/>
         <v>4.3140115163147783</v>
       </c>
       <c r="AC26" s="21">
-        <f t="shared" si="103"/>
+        <f t="shared" si="110"/>
         <v>4.5797687861271665</v>
       </c>
       <c r="AD26" s="21">
-        <f t="shared" si="103"/>
+        <f t="shared" si="110"/>
         <v>4.0668211664735407</v>
       </c>
       <c r="AE26" s="21">
-        <f t="shared" si="103"/>
+        <f t="shared" si="110"/>
         <v>5.0388198757763982</v>
       </c>
       <c r="AF26" s="21">
-        <f t="shared" si="103"/>
-        <v>6.0153610248447205</v>
-      </c>
-      <c r="AG26" s="21"/>
+        <f t="shared" si="110"/>
+        <v>4.8117922686450596</v>
+      </c>
+      <c r="AG26" s="21">
+        <f t="shared" si="110"/>
+        <v>3.8302770191182196</v>
+      </c>
       <c r="AH26" s="21"/>
       <c r="AI26" s="21"/>
       <c r="AJ26" s="21"/>
@@ -8055,76 +8364,76 @@
         <v>15.753377074488615</v>
       </c>
       <c r="AU26" s="1">
-        <f t="shared" ref="AU26:BG26" si="104">+AU25/AU27</f>
+        <f t="shared" ref="AU26:BG26" si="111">+AU25/AU27</f>
         <v>17.38783342928421</v>
       </c>
       <c r="AV26" s="1">
-        <f t="shared" si="104"/>
-        <v>29.347659950105541</v>
+        <f t="shared" si="111"/>
+        <v>18.214663207456518</v>
       </c>
       <c r="AW26" s="1">
-        <f t="shared" si="104"/>
-        <v>31.88918513605833</v>
+        <f t="shared" si="111"/>
+        <v>17.525046022672221</v>
       </c>
       <c r="AX26" s="1">
-        <f t="shared" si="104"/>
-        <v>33.231997880225677</v>
+        <f t="shared" si="111"/>
+        <v>33.994777250266445</v>
       </c>
       <c r="AY26" s="1">
-        <f t="shared" si="104"/>
-        <v>35.262282581145371</v>
+        <f t="shared" si="111"/>
+        <v>35.902326834996607</v>
       </c>
       <c r="AZ26" s="1">
-        <f t="shared" si="104"/>
-        <v>36.168137777511582</v>
+        <f t="shared" si="111"/>
+        <v>37.645977874230788</v>
       </c>
       <c r="BA26" s="1">
-        <f t="shared" si="104"/>
-        <v>36.836200763452503</v>
+        <f t="shared" si="111"/>
+        <v>39.086513996414155</v>
       </c>
       <c r="BB26" s="1">
-        <f t="shared" si="104"/>
-        <v>36.226023171623496</v>
+        <f t="shared" si="111"/>
+        <v>39.478248705143997</v>
       </c>
       <c r="BC26" s="1">
-        <f t="shared" si="104"/>
-        <v>37.892260353024682</v>
+        <f t="shared" si="111"/>
+        <v>41.853626365579053</v>
       </c>
       <c r="BD26" s="1">
-        <f t="shared" si="104"/>
-        <v>38.149838220331496</v>
+        <f t="shared" si="111"/>
+        <v>42.359824732407034</v>
       </c>
       <c r="BE26" s="1">
-        <f t="shared" si="104"/>
-        <v>39.388038023718913</v>
+        <f t="shared" si="111"/>
+        <v>43.967470354164377</v>
       </c>
       <c r="BF26" s="1">
-        <f t="shared" si="104"/>
-        <v>40.139793155352734</v>
+        <f t="shared" si="111"/>
+        <v>44.991908708128065</v>
       </c>
       <c r="BG26" s="1">
-        <f t="shared" si="104"/>
-        <v>40.558656066188696</v>
+        <f t="shared" si="111"/>
+        <v>46.218001994244851</v>
       </c>
       <c r="BH26" s="1">
-        <f t="shared" ref="BH26:BL26" si="105">+BH25/BH27</f>
-        <v>41.387046198223047</v>
+        <f t="shared" ref="BH26:BL26" si="112">+BH25/BH27</f>
+        <v>47.619901417565259</v>
       </c>
       <c r="BI26" s="1">
-        <f t="shared" si="105"/>
-        <v>42.481466099865095</v>
+        <f t="shared" si="112"/>
+        <v>49.177413247818265</v>
       </c>
       <c r="BJ26" s="1">
-        <f t="shared" si="105"/>
-        <v>43.764312848638028</v>
+        <f t="shared" si="112"/>
+        <v>50.874883545585107</v>
       </c>
       <c r="BK26" s="1">
-        <f t="shared" si="105"/>
-        <v>45.192311951575256</v>
+        <f t="shared" si="112"/>
+        <v>52.700306443328039</v>
       </c>
       <c r="BL26" s="1">
-        <f t="shared" si="105"/>
-        <v>33.800333569448526</v>
+        <f t="shared" si="112"/>
+        <v>38.176139932277188</v>
       </c>
     </row>
     <row r="27" spans="2:124" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8219,8 +8528,10 @@
         <v>257.60000000000002</v>
       </c>
       <c r="AF27" s="2">
-        <f>+AE27</f>
-        <v>257.60000000000002</v>
+        <v>256.10000000000002</v>
+      </c>
+      <c r="AG27" s="2">
+        <v>256.3</v>
       </c>
       <c r="AT27" s="2">
         <f>AVERAGE(Q27:T27)</f>
@@ -8231,72 +8542,72 @@
         <v>260.55</v>
       </c>
       <c r="AV27" s="2">
-        <f t="shared" ref="AV27:BG27" si="106">+AU27</f>
-        <v>260.55</v>
+        <f>AVERAGE(Y27:AB27)</f>
+        <v>260.17500000000001</v>
       </c>
       <c r="AW27" s="2">
-        <f t="shared" si="106"/>
-        <v>260.55</v>
+        <f>AVERAGE(AC27:AF27)</f>
+        <v>258.02499999999998</v>
       </c>
       <c r="AX27" s="2">
-        <f t="shared" si="106"/>
-        <v>260.55</v>
+        <f t="shared" ref="AV27:BG27" si="113">+AW27</f>
+        <v>258.02499999999998</v>
       </c>
       <c r="AY27" s="2">
-        <f t="shared" si="106"/>
-        <v>260.55</v>
+        <f t="shared" si="113"/>
+        <v>258.02499999999998</v>
       </c>
       <c r="AZ27" s="2">
-        <f t="shared" si="106"/>
-        <v>260.55</v>
+        <f t="shared" si="113"/>
+        <v>258.02499999999998</v>
       </c>
       <c r="BA27" s="2">
-        <f t="shared" si="106"/>
-        <v>260.55</v>
+        <f t="shared" si="113"/>
+        <v>258.02499999999998</v>
       </c>
       <c r="BB27" s="2">
-        <f t="shared" si="106"/>
-        <v>260.55</v>
+        <f t="shared" si="113"/>
+        <v>258.02499999999998</v>
       </c>
       <c r="BC27" s="2">
-        <f t="shared" si="106"/>
-        <v>260.55</v>
+        <f t="shared" si="113"/>
+        <v>258.02499999999998</v>
       </c>
       <c r="BD27" s="2">
-        <f t="shared" si="106"/>
-        <v>260.55</v>
+        <f t="shared" si="113"/>
+        <v>258.02499999999998</v>
       </c>
       <c r="BE27" s="2">
-        <f t="shared" si="106"/>
-        <v>260.55</v>
+        <f t="shared" si="113"/>
+        <v>258.02499999999998</v>
       </c>
       <c r="BF27" s="2">
-        <f t="shared" si="106"/>
-        <v>260.55</v>
+        <f t="shared" si="113"/>
+        <v>258.02499999999998</v>
       </c>
       <c r="BG27" s="2">
-        <f t="shared" si="106"/>
-        <v>260.55</v>
+        <f t="shared" si="113"/>
+        <v>258.02499999999998</v>
       </c>
       <c r="BH27" s="2">
-        <f t="shared" ref="BH27" si="107">+BG27</f>
-        <v>260.55</v>
+        <f t="shared" ref="BH27" si="114">+BG27</f>
+        <v>258.02499999999998</v>
       </c>
       <c r="BI27" s="2">
-        <f t="shared" ref="BI27" si="108">+BH27</f>
-        <v>260.55</v>
+        <f t="shared" ref="BI27" si="115">+BH27</f>
+        <v>258.02499999999998</v>
       </c>
       <c r="BJ27" s="2">
-        <f t="shared" ref="BJ27" si="109">+BI27</f>
-        <v>260.55</v>
+        <f t="shared" ref="BJ27" si="116">+BI27</f>
+        <v>258.02499999999998</v>
       </c>
       <c r="BK27" s="2">
-        <f t="shared" ref="BK27" si="110">+BJ27</f>
-        <v>260.55</v>
+        <f t="shared" ref="BK27" si="117">+BJ27</f>
+        <v>258.02499999999998</v>
       </c>
       <c r="BL27" s="2">
-        <f t="shared" ref="BL27" si="111">+BK27</f>
-        <v>260.55</v>
+        <f t="shared" ref="BL27" si="118">+BK27</f>
+        <v>258.02499999999998</v>
       </c>
     </row>
     <row r="29" spans="2:124" s="26" customFormat="1" ht="13" x14ac:dyDescent="0.3">
@@ -8308,83 +8619,83 @@
       <c r="E29" s="24"/>
       <c r="F29" s="24"/>
       <c r="G29" s="25">
-        <f t="shared" ref="G29:P29" si="112">+G15/C15-1</f>
+        <f t="shared" ref="G29:P29" si="119">+G15/C15-1</f>
         <v>0.21328224776500648</v>
       </c>
       <c r="H29" s="25">
-        <f t="shared" si="112"/>
+        <f t="shared" si="119"/>
         <v>0.44493886310784858</v>
       </c>
       <c r="I29" s="25">
-        <f t="shared" si="112"/>
+        <f t="shared" si="119"/>
         <v>0.76535979547461963</v>
       </c>
       <c r="J29" s="25">
-        <f t="shared" si="112"/>
+        <f t="shared" si="119"/>
         <v>0.62012853473169161</v>
       </c>
       <c r="K29" s="25">
-        <f t="shared" si="112"/>
+        <f t="shared" si="119"/>
         <v>0.61894736842105269</v>
       </c>
       <c r="L29" s="25">
-        <f t="shared" si="112"/>
+        <f t="shared" si="119"/>
         <v>0.29435163086714389</v>
       </c>
       <c r="M29" s="25">
-        <f t="shared" si="112"/>
+        <f t="shared" si="119"/>
         <v>0.13749174917491747</v>
       </c>
       <c r="N29" s="25">
-        <f t="shared" si="112"/>
+        <f t="shared" si="119"/>
         <v>0.176856468118604</v>
       </c>
       <c r="O29" s="25">
-        <f t="shared" si="112"/>
+        <f t="shared" si="119"/>
         <v>0.28998699609882972</v>
       </c>
       <c r="P29" s="25">
-        <f t="shared" si="112"/>
+        <f t="shared" si="119"/>
         <v>0.27350952673632456</v>
       </c>
       <c r="Q29" s="25">
-        <f t="shared" ref="Q29:T29" si="113">+Q15/M15-1</f>
+        <f t="shared" ref="Q29:T29" si="120">+Q15/M15-1</f>
         <v>0.21714153078396103</v>
       </c>
       <c r="R29" s="25">
-        <f t="shared" si="113"/>
+        <f t="shared" si="120"/>
         <v>0.2246376811594204</v>
       </c>
       <c r="S29" s="25">
-        <f t="shared" si="113"/>
+        <f t="shared" si="120"/>
         <v>0.17656249999999996</v>
       </c>
       <c r="T29" s="25">
-        <f t="shared" si="113"/>
+        <f t="shared" si="120"/>
         <v>0.1114864864864864</v>
       </c>
       <c r="U29" s="25">
-        <f t="shared" ref="U29" si="114">+U15/Q15-1</f>
+        <f t="shared" ref="U29" si="121">+U15/Q15-1</f>
         <v>0.13220500595947549</v>
       </c>
       <c r="V29" s="25">
-        <f t="shared" ref="V29" si="115">+V15/R15-1</f>
+        <f t="shared" ref="V29" si="122">+V15/R15-1</f>
         <v>0.13482020937642258</v>
       </c>
       <c r="W29" s="25">
-        <f t="shared" ref="W29" si="116">+W15/S15-1</f>
+        <f t="shared" ref="W29" si="123">+W15/S15-1</f>
         <v>6.3959216895857818E-2</v>
       </c>
       <c r="X29" s="25">
-        <f t="shared" ref="X29:Y29" si="117">+X15/T15-1</f>
+        <f t="shared" ref="X29:Y29" si="124">+X15/T15-1</f>
         <v>9.3226226660877209E-2</v>
       </c>
       <c r="Y29" s="25">
-        <f t="shared" si="117"/>
+        <f t="shared" si="124"/>
         <v>0.13297961933636526</v>
       </c>
       <c r="Z29" s="25">
-        <f t="shared" ref="Z29" si="118">+Z15/V15-1</f>
+        <f t="shared" ref="Z29" si="125">+Z15/V15-1</f>
         <v>6.1126263436547257E-2</v>
       </c>
       <c r="AA29" s="25">
@@ -8392,7 +8703,7 @@
         <v>0.11608149460460604</v>
       </c>
       <c r="AB29" s="25">
-        <f t="shared" ref="AB29" si="119">+AB15/X15-1</f>
+        <f t="shared" ref="AB29" si="126">+AB15/X15-1</f>
         <v>0.15661119275529245</v>
       </c>
       <c r="AC29" s="25">
@@ -8400,21 +8711,33 @@
         <v>2.9584479298297772E-2</v>
       </c>
       <c r="AD29" s="25">
-        <f t="shared" ref="AD29" si="120">+AD15/Z15-1</f>
+        <f t="shared" ref="AD29" si="127">+AD15/Z15-1</f>
         <v>0.12061536135470208</v>
       </c>
       <c r="AE29" s="25">
-        <f t="shared" ref="AE29" si="121">+AE15/AA15-1</f>
+        <f t="shared" ref="AE29" si="128">+AE15/AA15-1</f>
         <v>0.10985244777950132</v>
       </c>
       <c r="AF29" s="25">
-        <f t="shared" ref="AF29" si="122">+AF15/AB15-1</f>
-        <v>0.10885989010989006</v>
-      </c>
-      <c r="AG29" s="25"/>
-      <c r="AH29" s="25"/>
-      <c r="AI29" s="25"/>
-      <c r="AJ29" s="25"/>
+        <f t="shared" ref="AF29:AG29" si="129">+AF15/AB15-1</f>
+        <v>9.5467032967033072E-2</v>
+      </c>
+      <c r="AG29" s="25">
+        <f t="shared" si="129"/>
+        <v>7.822539888816693E-2</v>
+      </c>
+      <c r="AH29" s="25">
+        <f t="shared" ref="AH29" si="130">+AH15/AD15-1</f>
+        <v>1.4908759739602706E-2</v>
+      </c>
+      <c r="AI29" s="25">
+        <f t="shared" ref="AI29" si="131">+AI15/AE15-1</f>
+        <v>-1.4790014302431542E-2</v>
+      </c>
+      <c r="AJ29" s="25">
+        <f t="shared" ref="AJ29" si="132">+AJ15/AF15-1</f>
+        <v>-4.2978056426332456E-2</v>
+      </c>
       <c r="AK29" s="25"/>
       <c r="AT29" s="30">
         <f>+AT15/AS15-1</f>
@@ -8430,67 +8753,67 @@
       </c>
       <c r="AW29" s="30">
         <f>+AW15/AV15-1</f>
-        <v>6.5416829248373665E-2</v>
+        <v>0.10870137294579929</v>
       </c>
       <c r="AX29" s="30">
-        <f t="shared" ref="AX29:BL29" si="123">+AX15/AW15-1</f>
-        <v>1.9299633762030366E-2</v>
+        <f t="shared" ref="AX29:BL29" si="133">+AX15/AW15-1</f>
+        <v>1.3226387297429865E-2</v>
       </c>
       <c r="AY29" s="30">
-        <f t="shared" si="123"/>
-        <v>4.0418420673757671E-2</v>
+        <f t="shared" si="133"/>
+        <v>3.426734304824075E-2</v>
       </c>
       <c r="AZ29" s="30">
-        <f t="shared" si="123"/>
-        <v>1.877006255528002E-3</v>
+        <f t="shared" si="133"/>
+        <v>2.6768282205867466E-2</v>
       </c>
       <c r="BA29" s="30">
-        <f t="shared" si="123"/>
-        <v>-6.2901859823505379E-3</v>
+        <f t="shared" si="133"/>
+        <v>1.5873859477388619E-2</v>
       </c>
       <c r="BB29" s="30">
-        <f t="shared" si="123"/>
-        <v>-4.7299466457451089E-2</v>
+        <f t="shared" si="133"/>
+        <v>-1.5896676820647215E-2</v>
       </c>
       <c r="BC29" s="30">
-        <f t="shared" si="123"/>
-        <v>2.6474868951258834E-2</v>
+        <f t="shared" si="133"/>
+        <v>4.2218136014611884E-2</v>
       </c>
       <c r="BD29" s="30">
-        <f t="shared" si="123"/>
-        <v>-2.1099292240924661E-2</v>
+        <f t="shared" si="133"/>
+        <v>-1.4135908897581984E-2</v>
       </c>
       <c r="BE29" s="30">
-        <f t="shared" si="123"/>
-        <v>-1.3112975982201625E-2</v>
+        <f t="shared" si="133"/>
+        <v>-6.9228566882681974E-3</v>
       </c>
       <c r="BF29" s="30">
-        <f t="shared" si="123"/>
-        <v>-6.3327597337109465E-3</v>
+        <f t="shared" si="133"/>
+        <v>-8.7093082552291978E-4</v>
       </c>
       <c r="BG29" s="30">
-        <f t="shared" si="123"/>
-        <v>-1.7928048049511869E-2</v>
+        <f t="shared" si="133"/>
+        <v>4.1427375065004046E-3</v>
       </c>
       <c r="BH29" s="30">
-        <f t="shared" si="123"/>
-        <v>-4.862043621063572E-3</v>
+        <f t="shared" si="133"/>
+        <v>8.2538985683962007E-3</v>
       </c>
       <c r="BI29" s="30">
-        <f t="shared" si="123"/>
-        <v>3.4072046343889273E-3</v>
+        <f t="shared" si="133"/>
+        <v>1.1597917671187119E-2</v>
       </c>
       <c r="BJ29" s="30">
-        <f t="shared" si="123"/>
-        <v>8.8404532567649685E-3</v>
+        <f t="shared" si="133"/>
+        <v>1.4301312263291344E-2</v>
       </c>
       <c r="BK29" s="30">
-        <f t="shared" si="123"/>
-        <v>1.256929805269813E-2</v>
+        <f t="shared" si="133"/>
+        <v>1.6477180811032444E-2</v>
       </c>
       <c r="BL29" s="30">
-        <f t="shared" si="123"/>
-        <v>-0.39588226972167095</v>
+        <f t="shared" si="133"/>
+        <v>-0.40955136339758358</v>
       </c>
     </row>
     <row r="30" spans="2:124" x14ac:dyDescent="0.25">
@@ -8498,67 +8821,67 @@
         <v>174</v>
       </c>
       <c r="C30" s="19">
-        <f t="shared" ref="C30" si="124">C17/C15</f>
+        <f t="shared" ref="C30" si="134">C17/C15</f>
         <v>0.85791187739463604</v>
       </c>
       <c r="D30" s="19">
-        <f t="shared" ref="D30:H30" si="125">D17/D15</f>
+        <f t="shared" ref="D30:H30" si="135">D17/D15</f>
         <v>0.8594271053058109</v>
       </c>
       <c r="E30" s="19">
-        <f t="shared" si="125"/>
+        <f t="shared" si="135"/>
         <v>0.88919366754371454</v>
       </c>
       <c r="F30" s="19">
-        <f t="shared" si="125"/>
+        <f t="shared" si="135"/>
         <v>0.8557358650587249</v>
       </c>
       <c r="G30" s="19">
-        <f t="shared" si="125"/>
+        <f t="shared" si="135"/>
         <v>0.86114315789473683</v>
       </c>
       <c r="H30" s="19">
-        <f t="shared" si="125"/>
+        <f t="shared" si="135"/>
         <v>0.8528146380270486</v>
       </c>
       <c r="I30" s="19">
-        <f t="shared" ref="I30:J30" si="126">I17/I15</f>
+        <f t="shared" ref="I30:J30" si="136">I17/I15</f>
         <v>0.8927412541254125</v>
       </c>
       <c r="J30" s="19">
-        <f t="shared" si="126"/>
+        <f t="shared" si="136"/>
         <v>0.87896877459984257</v>
       </c>
       <c r="K30" s="19">
-        <f t="shared" ref="K30:L30" si="127">K17/K15</f>
+        <f t="shared" ref="K30:L30" si="137">K17/K15</f>
         <v>0.87894538361508456</v>
       </c>
       <c r="L30" s="19">
-        <f t="shared" si="127"/>
+        <f t="shared" si="137"/>
         <v>0.87516902274124164</v>
       </c>
       <c r="M30" s="19">
-        <f t="shared" ref="M30:P30" si="128">M17/M15</f>
+        <f t="shared" ref="M30:P30" si="138">M17/M15</f>
         <v>0.888411768119306</v>
       </c>
       <c r="N30" s="19">
-        <f t="shared" si="128"/>
+        <f t="shared" si="138"/>
         <v>0.87290969899665549</v>
       </c>
       <c r="O30" s="19">
-        <f t="shared" si="128"/>
+        <f t="shared" si="138"/>
         <v>0.88079032258064516</v>
       </c>
       <c r="P30" s="19">
-        <f t="shared" si="128"/>
+        <f t="shared" si="138"/>
         <v>0.88059845559845551</v>
       </c>
       <c r="Q30" s="19">
-        <f t="shared" ref="Q30:R30" si="129">Q17/Q15</f>
+        <f t="shared" ref="Q30:R30" si="139">Q17/Q15</f>
         <v>0.93048867699642435</v>
       </c>
       <c r="R30" s="19">
-        <f t="shared" si="129"/>
+        <f t="shared" si="139"/>
         <v>0.88083750568957675</v>
       </c>
       <c r="S30" s="19">
@@ -8570,137 +8893,149 @@
         <v>0.87802865827181931</v>
       </c>
       <c r="U30" s="19">
-        <f t="shared" ref="U30:X30" si="130">U17/U15</f>
+        <f t="shared" ref="U30:X30" si="140">U17/U15</f>
         <v>0.88841165571837633</v>
       </c>
       <c r="V30" s="19">
-        <f t="shared" si="130"/>
+        <f t="shared" si="140"/>
         <v>0.87694529119204234</v>
       </c>
       <c r="W30" s="19">
-        <f t="shared" si="130"/>
+        <f t="shared" si="140"/>
         <v>0.87236269930745691</v>
       </c>
       <c r="X30" s="19">
-        <f t="shared" si="130"/>
+        <f t="shared" si="140"/>
         <v>0.85534416332366847</v>
       </c>
       <c r="Y30" s="19">
-        <f t="shared" ref="Y30:AF30" si="131">Y17/Y15</f>
+        <f t="shared" ref="Y30:AF30" si="141">Y17/Y15</f>
         <v>0.87519512376421604</v>
       </c>
       <c r="Z30" s="19">
-        <f t="shared" si="131"/>
+        <f t="shared" si="141"/>
         <v>0.86203507710916238</v>
       </c>
       <c r="AA30" s="19">
-        <f t="shared" si="131"/>
+        <f t="shared" si="141"/>
         <v>0.86085356614596498</v>
       </c>
       <c r="AB30" s="19">
-        <f t="shared" si="131"/>
+        <f t="shared" si="141"/>
         <v>0.85703983516483506</v>
       </c>
       <c r="AC30" s="19">
-        <f t="shared" si="131"/>
+        <f t="shared" si="141"/>
         <v>0.87170601400620895</v>
       </c>
       <c r="AD30" s="19">
-        <f t="shared" si="131"/>
+        <f t="shared" si="141"/>
         <v>0.86511282760481667</v>
       </c>
       <c r="AE30" s="19">
-        <f t="shared" si="131"/>
+        <f t="shared" si="141"/>
         <v>0.86770250942660254</v>
       </c>
       <c r="AF30" s="19">
-        <f t="shared" si="131"/>
-        <v>0.87</v>
-      </c>
-      <c r="AG30" s="19"/>
-      <c r="AH30" s="19"/>
-      <c r="AI30" s="19"/>
-      <c r="AJ30" s="19"/>
+        <f t="shared" si="141"/>
+        <v>0.87000000000000011</v>
+      </c>
+      <c r="AG30" s="19">
+        <f t="shared" ref="AG30:AJ30" si="142">AG17/AG15</f>
+        <v>0.87123773812313776</v>
+      </c>
+      <c r="AH30" s="19">
+        <f t="shared" si="142"/>
+        <v>0</v>
+      </c>
+      <c r="AI30" s="19">
+        <f t="shared" si="142"/>
+        <v>0</v>
+      </c>
+      <c r="AJ30" s="19">
+        <f t="shared" si="142"/>
+        <v>0</v>
+      </c>
       <c r="AK30" s="19"/>
       <c r="AS30" s="19">
-        <f t="shared" ref="AS30:AT30" si="132">AS17/AS15</f>
+        <f t="shared" ref="AS30:AT30" si="143">AS17/AS15</f>
         <v>0.88060528435424446</v>
       </c>
       <c r="AT30" s="19">
-        <f t="shared" si="132"/>
+        <f t="shared" si="143"/>
         <v>0.89078349268904367</v>
       </c>
       <c r="AU30" s="19">
-        <f t="shared" ref="AU30:BG30" si="133">AU17/AU15</f>
+        <f t="shared" ref="AU30:BG30" si="144">AU17/AU15</f>
         <v>0.87304064118022551</v>
       </c>
       <c r="AV30" s="19">
-        <f t="shared" si="133"/>
+        <f t="shared" si="144"/>
+        <v>0.86363100153356143</v>
+      </c>
+      <c r="AW30" s="19">
+        <f t="shared" si="144"/>
+        <v>0.86501882468489111</v>
+      </c>
+      <c r="AX30" s="19">
+        <f t="shared" si="144"/>
+        <v>0.92999999999999994</v>
+      </c>
+      <c r="AY30" s="19">
+        <f t="shared" si="144"/>
+        <v>0.92999999999999994</v>
+      </c>
+      <c r="AZ30" s="19">
+        <f t="shared" si="144"/>
         <v>0.93</v>
       </c>
-      <c r="AW30" s="19">
-        <f t="shared" si="133"/>
+      <c r="BA30" s="19">
+        <f t="shared" si="144"/>
         <v>0.92999999999999994</v>
       </c>
-      <c r="AX30" s="19">
-        <f t="shared" si="133"/>
+      <c r="BB30" s="19">
+        <f t="shared" si="144"/>
         <v>0.93</v>
       </c>
-      <c r="AY30" s="19">
-        <f t="shared" si="133"/>
-        <v>0.93</v>
-      </c>
-      <c r="AZ30" s="19">
-        <f t="shared" si="133"/>
+      <c r="BC30" s="19">
+        <f t="shared" si="144"/>
         <v>0.92999999999999994</v>
       </c>
-      <c r="BA30" s="19">
-        <f t="shared" si="133"/>
+      <c r="BD30" s="19">
+        <f t="shared" si="144"/>
         <v>0.92999999999999994</v>
       </c>
-      <c r="BB30" s="19">
-        <f t="shared" si="133"/>
-        <v>0.93</v>
-      </c>
-      <c r="BC30" s="19">
-        <f t="shared" si="133"/>
+      <c r="BE30" s="19">
+        <f t="shared" si="144"/>
+        <v>0.95</v>
+      </c>
+      <c r="BF30" s="19">
+        <f t="shared" si="144"/>
+        <v>0.95</v>
+      </c>
+      <c r="BG30" s="19">
+        <f t="shared" si="144"/>
+        <v>0.95000000000000007</v>
+      </c>
+      <c r="BH30" s="19">
+        <f t="shared" ref="BH30:BL30" si="145">BH17/BH15</f>
+        <v>0.95000000000000007</v>
+      </c>
+      <c r="BI30" s="19">
+        <f t="shared" si="145"/>
+        <v>0.95</v>
+      </c>
+      <c r="BJ30" s="19">
+        <f t="shared" si="145"/>
+        <v>0.95000000000000007</v>
+      </c>
+      <c r="BK30" s="19">
+        <f t="shared" si="145"/>
+        <v>0.95000000000000007</v>
+      </c>
+      <c r="BL30" s="19">
+        <f t="shared" si="145"/>
         <v>0.92999999999999994</v>
-      </c>
-      <c r="BD30" s="19">
-        <f t="shared" si="133"/>
-        <v>0.92999999999999994</v>
-      </c>
-      <c r="BE30" s="19">
-        <f t="shared" si="133"/>
-        <v>0.95000000000000007</v>
-      </c>
-      <c r="BF30" s="19">
-        <f t="shared" si="133"/>
-        <v>0.95</v>
-      </c>
-      <c r="BG30" s="19">
-        <f t="shared" si="133"/>
-        <v>0.95000000000000007</v>
-      </c>
-      <c r="BH30" s="19">
-        <f t="shared" ref="BH30:BL30" si="134">BH17/BH15</f>
-        <v>0.95</v>
-      </c>
-      <c r="BI30" s="19">
-        <f t="shared" si="134"/>
-        <v>0.95000000000000007</v>
-      </c>
-      <c r="BJ30" s="19">
-        <f t="shared" si="134"/>
-        <v>0.95</v>
-      </c>
-      <c r="BK30" s="19">
-        <f t="shared" si="134"/>
-        <v>0.95</v>
-      </c>
-      <c r="BL30" s="19">
-        <f t="shared" si="134"/>
-        <v>0.93</v>
       </c>
       <c r="BN30" t="s">
         <v>285</v>
@@ -8714,71 +9049,71 @@
         <v>281</v>
       </c>
       <c r="C31" s="19">
-        <f t="shared" ref="C31" si="135">+C18/C15</f>
+        <f t="shared" ref="C31" si="146">+C18/C15</f>
         <v>0.17534482758620687</v>
       </c>
       <c r="D31" s="19">
-        <f t="shared" ref="D31:H31" si="136">+D18/D15</f>
+        <f t="shared" ref="D31:H31" si="147">+D18/D15</f>
         <v>0.17611701131006641</v>
       </c>
       <c r="E31" s="19">
-        <f t="shared" si="136"/>
+        <f t="shared" si="147"/>
         <v>0.1713447730201752</v>
       </c>
       <c r="F31" s="19">
-        <f t="shared" si="136"/>
+        <f t="shared" si="147"/>
         <v>0.16632993698673523</v>
       </c>
       <c r="G31" s="19">
-        <f t="shared" si="136"/>
+        <f t="shared" si="147"/>
         <v>0.16807789473684212</v>
       </c>
       <c r="H31" s="19">
-        <f t="shared" si="136"/>
+        <f t="shared" si="147"/>
         <v>0.15535163086714399</v>
       </c>
       <c r="I31" s="19">
-        <f t="shared" ref="I31:J31" si="137">+I18/I15</f>
+        <f t="shared" ref="I31:J31" si="148">+I18/I15</f>
         <v>0.12030231023102311</v>
       </c>
       <c r="J31" s="19">
-        <f t="shared" si="137"/>
+        <f t="shared" si="148"/>
         <v>0.12581999475203359</v>
       </c>
       <c r="K31" s="19">
-        <f t="shared" ref="K31:S31" si="138">+K18/K15</f>
+        <f t="shared" ref="K31:S31" si="149">+K18/K15</f>
         <v>0.11999414824447334</v>
       </c>
       <c r="L31" s="19">
-        <f t="shared" si="138"/>
+        <f t="shared" si="149"/>
         <v>0.107559926244622</v>
       </c>
       <c r="M31" s="19">
-        <f t="shared" si="138"/>
+        <f t="shared" si="149"/>
         <v>8.7622584576103987E-2</v>
       </c>
       <c r="N31" s="19">
-        <f t="shared" si="138"/>
+        <f t="shared" si="149"/>
         <v>0.1084726867335563</v>
       </c>
       <c r="O31" s="19">
-        <f t="shared" si="138"/>
+        <f t="shared" si="149"/>
         <v>9.9893649193548387E-2</v>
       </c>
       <c r="P31" s="19">
-        <f t="shared" si="138"/>
+        <f t="shared" si="149"/>
         <v>0.10135135135135136</v>
       </c>
       <c r="Q31" s="19">
-        <f t="shared" si="138"/>
+        <f t="shared" si="149"/>
         <v>7.9618593563766382E-2</v>
       </c>
       <c r="R31" s="19">
-        <f t="shared" si="138"/>
+        <f t="shared" si="149"/>
         <v>7.8880291306326816E-2</v>
       </c>
       <c r="S31" s="19">
-        <f t="shared" si="138"/>
+        <f t="shared" si="149"/>
         <v>7.7282268774364921E-2</v>
       </c>
       <c r="T31" s="19">
@@ -8786,57 +9121,69 @@
         <v>9.7959183673469383E-2</v>
       </c>
       <c r="U31" s="19">
-        <f t="shared" ref="U31:X31" si="139">+U18/U15</f>
+        <f t="shared" ref="U31:X31" si="150">+U18/U15</f>
         <v>8.2912245241704582E-2</v>
       </c>
       <c r="V31" s="19">
-        <f t="shared" si="139"/>
+        <f t="shared" si="150"/>
         <v>8.8079576447938374E-2</v>
       </c>
       <c r="W31" s="19">
-        <f t="shared" si="139"/>
+        <f t="shared" si="150"/>
         <v>8.6849734256724098E-2</v>
       </c>
       <c r="X31" s="19">
-        <f t="shared" si="139"/>
+        <f t="shared" si="150"/>
         <v>0.11343686698176907</v>
       </c>
       <c r="Y31" s="19">
-        <f t="shared" ref="Y31:AB31" si="140">+Y18/Y15</f>
+        <f t="shared" ref="Y31:AB31" si="151">+Y18/Y15</f>
         <v>0.1010926930796105</v>
       </c>
       <c r="Z31" s="19">
-        <f t="shared" si="140"/>
+        <f t="shared" si="151"/>
         <v>0.10598729966737223</v>
       </c>
       <c r="AA31" s="19">
-        <f t="shared" si="140"/>
+        <f t="shared" si="151"/>
         <v>0.10826508892817202</v>
       </c>
       <c r="AB31" s="19">
-        <f t="shared" si="140"/>
+        <f t="shared" si="151"/>
         <v>0.10649038461538463</v>
       </c>
       <c r="AC31" s="19">
-        <f t="shared" ref="AC31:AF31" si="141">+AC18/AC15</f>
+        <f t="shared" ref="AC31:AF31" si="152">+AC18/AC15</f>
         <v>0.12020792722547109</v>
       </c>
       <c r="AD31" s="19">
-        <f t="shared" si="141"/>
+        <f t="shared" si="152"/>
         <v>0.12122643100482343</v>
       </c>
       <c r="AE31" s="19">
-        <f t="shared" si="141"/>
+        <f t="shared" si="152"/>
         <v>0.11994539071642178</v>
       </c>
       <c r="AF31" s="19">
-        <f t="shared" si="141"/>
-        <v>9.6035924434809544E-2</v>
-      </c>
-      <c r="AG31" s="19"/>
-      <c r="AH31" s="19"/>
-      <c r="AI31" s="19"/>
-      <c r="AJ31" s="19"/>
+        <f t="shared" si="152"/>
+        <v>0.15266457680250783</v>
+      </c>
+      <c r="AG31" s="19">
+        <f t="shared" ref="AG31:AJ31" si="153">+AG18/AG15</f>
+        <v>0.16528842612742309</v>
+      </c>
+      <c r="AH31" s="19">
+        <f t="shared" si="153"/>
+        <v>0</v>
+      </c>
+      <c r="AI31" s="19">
+        <f t="shared" si="153"/>
+        <v>0</v>
+      </c>
+      <c r="AJ31" s="19">
+        <f t="shared" si="153"/>
+        <v>0</v>
+      </c>
       <c r="AK31" s="19"/>
       <c r="AS31" s="19"/>
       <c r="AT31" s="19">
@@ -8844,76 +9191,76 @@
         <v>8.3555386372287793E-2</v>
       </c>
       <c r="AU31" s="19">
-        <f t="shared" ref="AU31:BG31" si="142">+AU18/AU15</f>
+        <f t="shared" ref="AU31:BG31" si="154">+AU18/AU15</f>
         <v>9.2995450538538693E-2</v>
       </c>
       <c r="AV31" s="19">
-        <f t="shared" si="142"/>
+        <f t="shared" si="154"/>
+        <v>0.10549813522563317</v>
+      </c>
+      <c r="AW31" s="19">
+        <f t="shared" si="154"/>
+        <v>0.1398837780324112</v>
+      </c>
+      <c r="AX31" s="19">
+        <f t="shared" si="154"/>
+        <v>0.10000000000000002</v>
+      </c>
+      <c r="AY31" s="19">
+        <f t="shared" si="154"/>
         <v>0.1</v>
       </c>
-      <c r="AW31" s="19">
-        <f t="shared" si="142"/>
+      <c r="AZ31" s="19">
+        <f t="shared" si="154"/>
+        <v>0.10000000000000002</v>
+      </c>
+      <c r="BA31" s="19">
+        <f t="shared" si="154"/>
         <v>0.1</v>
       </c>
-      <c r="AX31" s="19">
-        <f t="shared" si="142"/>
+      <c r="BB31" s="19">
+        <f t="shared" si="154"/>
         <v>0.1</v>
       </c>
-      <c r="AY31" s="19">
-        <f t="shared" si="142"/>
+      <c r="BC31" s="19">
+        <f t="shared" si="154"/>
         <v>0.1</v>
       </c>
-      <c r="AZ31" s="19">
-        <f t="shared" si="142"/>
+      <c r="BD31" s="19">
+        <f t="shared" si="154"/>
         <v>0.1</v>
       </c>
-      <c r="BA31" s="19">
-        <f t="shared" si="142"/>
+      <c r="BE31" s="19">
+        <f t="shared" si="154"/>
+        <v>0.10000000000000002</v>
+      </c>
+      <c r="BF31" s="19">
+        <f t="shared" si="154"/>
+        <v>0.10000000000000002</v>
+      </c>
+      <c r="BG31" s="19">
+        <f t="shared" si="154"/>
+        <v>0.10000000000000002</v>
+      </c>
+      <c r="BH31" s="19">
+        <f t="shared" ref="BH31:BL31" si="155">+BH18/BH15</f>
+        <v>0.10000000000000002</v>
+      </c>
+      <c r="BI31" s="19">
+        <f t="shared" si="155"/>
+        <v>0.10000000000000002</v>
+      </c>
+      <c r="BJ31" s="19">
+        <f t="shared" si="155"/>
         <v>0.1</v>
       </c>
-      <c r="BB31" s="19">
-        <f t="shared" si="142"/>
+      <c r="BK31" s="19">
+        <f t="shared" si="155"/>
+        <v>0.10000000000000002</v>
+      </c>
+      <c r="BL31" s="19">
+        <f t="shared" si="155"/>
         <v>0.1</v>
-      </c>
-      <c r="BC31" s="19">
-        <f t="shared" si="142"/>
-        <v>9.9999999999999992E-2</v>
-      </c>
-      <c r="BD31" s="19">
-        <f t="shared" si="142"/>
-        <v>0.1</v>
-      </c>
-      <c r="BE31" s="19">
-        <f t="shared" si="142"/>
-        <v>9.9999999999999992E-2</v>
-      </c>
-      <c r="BF31" s="19">
-        <f t="shared" si="142"/>
-        <v>0.1</v>
-      </c>
-      <c r="BG31" s="19">
-        <f t="shared" si="142"/>
-        <v>0.1</v>
-      </c>
-      <c r="BH31" s="19">
-        <f t="shared" ref="BH31:BL31" si="143">+BH18/BH15</f>
-        <v>0.1</v>
-      </c>
-      <c r="BI31" s="19">
-        <f t="shared" si="143"/>
-        <v>0.1</v>
-      </c>
-      <c r="BJ31" s="19">
-        <f t="shared" si="143"/>
-        <v>0.1</v>
-      </c>
-      <c r="BK31" s="19">
-        <f t="shared" si="143"/>
-        <v>0.1</v>
-      </c>
-      <c r="BL31" s="19">
-        <f t="shared" si="143"/>
-        <v>0.10000000000000002</v>
       </c>
       <c r="BN31" t="s">
         <v>283</v>
@@ -8927,43 +9274,43 @@
         <v>177</v>
       </c>
       <c r="C32" s="19">
-        <f t="shared" ref="C32" si="144">C24/C23</f>
+        <f t="shared" ref="C32" si="156">C24/C23</f>
         <v>4.1139547592659732E-2</v>
       </c>
       <c r="D32" s="19">
-        <f t="shared" ref="D32:H32" si="145">D24/D23</f>
+        <f t="shared" ref="D32:H32" si="157">D24/D23</f>
         <v>0</v>
       </c>
       <c r="E32" s="19">
-        <f t="shared" si="145"/>
+        <f t="shared" si="157"/>
         <v>0.18584070796460173</v>
       </c>
       <c r="F32" s="19">
-        <f t="shared" si="145"/>
+        <f t="shared" si="157"/>
         <v>0.21886672115945011</v>
       </c>
       <c r="G32" s="19">
-        <f t="shared" si="145"/>
+        <f t="shared" si="157"/>
         <v>0.1245736375350564</v>
       </c>
       <c r="H32" s="19">
-        <f t="shared" si="145"/>
+        <f t="shared" si="157"/>
         <v>0.23736987411666366</v>
       </c>
       <c r="I32" s="19">
-        <f t="shared" ref="I32:J32" si="146">I24/I23</f>
+        <f t="shared" ref="I32:J32" si="158">I24/I23</f>
         <v>7.6068135142753596E-2</v>
       </c>
       <c r="J32" s="19">
-        <f t="shared" si="146"/>
+        <f t="shared" si="158"/>
         <v>-1.7419854732347417E-2</v>
       </c>
       <c r="K32" s="19">
-        <f t="shared" ref="K32:L32" si="147">K24/K23</f>
+        <f t="shared" ref="K32:L32" si="159">K24/K23</f>
         <v>0.1183036858950188</v>
       </c>
       <c r="L32" s="19">
-        <f t="shared" si="147"/>
+        <f t="shared" si="159"/>
         <v>0.22735101619014811</v>
       </c>
       <c r="M32" s="19">
@@ -8971,160 +9318,172 @@
         <v>0.20896733617366606</v>
       </c>
       <c r="N32" s="19">
-        <f t="shared" ref="N32:T32" si="148">N24/N23</f>
+        <f t="shared" ref="N32:T32" si="160">N24/N23</f>
         <v>1.2000440383133325E-2</v>
       </c>
       <c r="O32" s="19">
-        <f t="shared" si="148"/>
+        <f t="shared" si="160"/>
         <v>0.22163530370872531</v>
       </c>
       <c r="P32" s="19">
-        <f t="shared" si="148"/>
+        <f t="shared" si="160"/>
         <v>0.21576239053895463</v>
       </c>
       <c r="Q32" s="19">
-        <f t="shared" si="148"/>
+        <f t="shared" si="160"/>
         <v>0.19897714559693142</v>
       </c>
       <c r="R32" s="19">
-        <f t="shared" si="148"/>
+        <f t="shared" si="160"/>
         <v>0.20799485240891175</v>
       </c>
       <c r="S32" s="19">
-        <f t="shared" si="148"/>
+        <f t="shared" si="160"/>
         <v>0.18205374990745546</v>
       </c>
       <c r="T32" s="19">
-        <f t="shared" si="148"/>
+        <f t="shared" si="160"/>
         <v>0.20670032860463253</v>
       </c>
       <c r="U32" s="19">
-        <f t="shared" ref="U32:X32" si="149">U24/U23</f>
+        <f t="shared" ref="U32:X32" si="161">U24/U23</f>
         <v>0.15817041682036154</v>
       </c>
       <c r="V32" s="19">
-        <f t="shared" si="149"/>
+        <f t="shared" si="161"/>
         <v>0.1932706793887653</v>
       </c>
       <c r="W32" s="19">
-        <f t="shared" si="149"/>
+        <f t="shared" si="161"/>
         <v>0.18714473108876253</v>
       </c>
       <c r="X32" s="19">
-        <f t="shared" si="149"/>
+        <f t="shared" si="161"/>
         <v>0.13461828037946091</v>
       </c>
       <c r="Y32" s="19">
-        <f t="shared" ref="Y32:AB32" si="150">Y24/Y23</f>
+        <f t="shared" ref="Y32:AB32" si="162">Y24/Y23</f>
         <v>0.16528454769893022</v>
       </c>
       <c r="Z32" s="19">
-        <f t="shared" si="150"/>
+        <f t="shared" si="162"/>
         <v>0.20886603668704837</v>
       </c>
       <c r="AA32" s="19">
-        <f t="shared" si="150"/>
+        <f t="shared" si="162"/>
         <v>0.19622405774970497</v>
       </c>
       <c r="AB32" s="19">
-        <f t="shared" si="150"/>
+        <f t="shared" si="162"/>
         <v>0.19928749554684719</v>
       </c>
       <c r="AC32" s="19">
-        <f t="shared" ref="AC32:AF32" si="151">AC24/AC23</f>
+        <f t="shared" ref="AC32:AF32" si="163">AC24/AC23</f>
         <v>0.1</v>
       </c>
       <c r="AD32" s="19">
-        <f t="shared" si="151"/>
+        <f t="shared" si="163"/>
         <v>0.21136993483634189</v>
       </c>
       <c r="AE32" s="19">
-        <f t="shared" si="151"/>
+        <f t="shared" si="163"/>
         <v>0.16885445348018183</v>
       </c>
       <c r="AF32" s="19">
-        <f t="shared" si="151"/>
-        <v>0.1</v>
-      </c>
-      <c r="AG32" s="19"/>
-      <c r="AH32" s="19"/>
-      <c r="AI32" s="19"/>
-      <c r="AJ32" s="19"/>
+        <f t="shared" si="163"/>
+        <v>0.14017583030979627</v>
+      </c>
+      <c r="AG32" s="19">
+        <f t="shared" ref="AG32:AJ32" si="164">AG24/AG23</f>
+        <v>0.22198446663496599</v>
+      </c>
+      <c r="AH32" s="19" t="e">
+        <f t="shared" si="164"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AI32" s="19" t="e">
+        <f t="shared" si="164"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AJ32" s="19" t="e">
+        <f t="shared" si="164"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="AK32" s="19"/>
       <c r="AT32" s="23">
         <f>+AT24/AT23</f>
         <v>0.19858239579038309</v>
       </c>
       <c r="AU32" s="23">
-        <f t="shared" ref="AU32:BG32" si="152">+AU24/AU23</f>
+        <f t="shared" ref="AU32:BG32" si="165">+AU24/AU23</f>
         <v>0.16870343865829932</v>
       </c>
       <c r="AV32" s="23">
-        <f t="shared" si="152"/>
+        <f t="shared" si="165"/>
+        <v>0.19172451433541984</v>
+      </c>
+      <c r="AW32" s="23">
+        <f t="shared" si="165"/>
+        <v>0.1850670415224914</v>
+      </c>
+      <c r="AX32" s="23">
+        <f t="shared" si="165"/>
         <v>0.2</v>
       </c>
-      <c r="AW32" s="23">
-        <f t="shared" si="152"/>
+      <c r="AY32" s="23">
+        <f t="shared" si="165"/>
         <v>0.2</v>
       </c>
-      <c r="AX32" s="23">
-        <f t="shared" si="152"/>
+      <c r="AZ32" s="23">
+        <f t="shared" si="165"/>
         <v>0.2</v>
       </c>
-      <c r="AY32" s="23">
-        <f t="shared" si="152"/>
+      <c r="BA32" s="23">
+        <f t="shared" si="165"/>
         <v>0.2</v>
       </c>
-      <c r="AZ32" s="23">
-        <f t="shared" si="152"/>
-        <v>0.19999999999999998</v>
-      </c>
-      <c r="BA32" s="23">
-        <f t="shared" si="152"/>
+      <c r="BB32" s="23">
+        <f t="shared" si="165"/>
         <v>0.2</v>
       </c>
-      <c r="BB32" s="23">
-        <f t="shared" si="152"/>
-        <v>0.19999999999999998</v>
-      </c>
       <c r="BC32" s="23">
-        <f t="shared" si="152"/>
+        <f t="shared" si="165"/>
+        <v>0.2</v>
+      </c>
+      <c r="BD32" s="23">
+        <f t="shared" si="165"/>
+        <v>0.2</v>
+      </c>
+      <c r="BE32" s="23">
+        <f t="shared" si="165"/>
         <v>0.20000000000000004</v>
       </c>
-      <c r="BD32" s="23">
-        <f t="shared" si="152"/>
+      <c r="BF32" s="23">
+        <f t="shared" si="165"/>
         <v>0.2</v>
       </c>
-      <c r="BE32" s="23">
-        <f t="shared" si="152"/>
-        <v>0.20000000000000004</v>
-      </c>
-      <c r="BF32" s="23">
-        <f t="shared" si="152"/>
+      <c r="BG32" s="23">
+        <f t="shared" si="165"/>
         <v>0.2</v>
       </c>
-      <c r="BG32" s="23">
-        <f t="shared" si="152"/>
+      <c r="BH32" s="23">
+        <f t="shared" ref="BH32:BL32" si="166">+BH24/BH23</f>
         <v>0.2</v>
       </c>
-      <c r="BH32" s="23">
-        <f t="shared" ref="BH32:BL32" si="153">+BH24/BH23</f>
+      <c r="BI32" s="23">
+        <f t="shared" si="166"/>
         <v>0.2</v>
       </c>
-      <c r="BI32" s="23">
-        <f t="shared" si="153"/>
+      <c r="BJ32" s="23">
+        <f t="shared" si="166"/>
         <v>0.2</v>
       </c>
-      <c r="BJ32" s="23">
-        <f t="shared" si="153"/>
+      <c r="BK32" s="23">
+        <f t="shared" si="166"/>
         <v>0.2</v>
       </c>
-      <c r="BK32" s="23">
-        <f t="shared" si="153"/>
-        <v>0.2</v>
-      </c>
       <c r="BL32" s="23">
-        <f t="shared" si="153"/>
+        <f t="shared" si="166"/>
         <v>0.2</v>
       </c>
       <c r="BN32" t="s">
@@ -9140,7 +9499,7 @@
       </c>
       <c r="BO33" s="2">
         <f>NPV(BO31,AW25:CT25)+Main!M5-Main!M6</f>
-        <v>140032.21312109416</v>
+        <v>148874.8734287566</v>
       </c>
     </row>
     <row r="34" spans="2:67" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9238,79 +9597,79 @@
         <v>13716.100000000002</v>
       </c>
       <c r="AV34" s="2">
-        <f t="shared" ref="AV34:BG34" si="154">+AU34+AV25</f>
-        <v>21362.632799999999</v>
+        <f t="shared" ref="AV34:BG34" si="167">+AU34+AV25</f>
+        <v>18455.100000000002</v>
       </c>
       <c r="AW34" s="2">
-        <f t="shared" si="154"/>
-        <v>29671.359987199998</v>
+        <f t="shared" si="167"/>
+        <v>22977</v>
       </c>
       <c r="AX34" s="2">
-        <f t="shared" si="154"/>
-        <v>38329.957034892795</v>
+        <f t="shared" si="167"/>
+        <v>31748.502399999998</v>
       </c>
       <c r="AY34" s="2">
-        <f t="shared" si="154"/>
-        <v>47517.544761410223</v>
+        <f t="shared" si="167"/>
+        <v>41012.200281599995</v>
       </c>
       <c r="AZ34" s="2">
-        <f t="shared" si="154"/>
-        <v>56941.153059340868</v>
+        <f t="shared" si="167"/>
+        <v>50725.803722598394</v>
       </c>
       <c r="BA34" s="2">
-        <f t="shared" si="154"/>
-        <v>66538.825168258423</v>
+        <f t="shared" si="167"/>
+        <v>60811.101496523159</v>
       </c>
       <c r="BB34" s="2">
-        <f t="shared" si="154"/>
-        <v>75977.51550562492</v>
+        <f t="shared" si="167"/>
+        <v>70997.476618667934</v>
       </c>
       <c r="BC34" s="2">
-        <f t="shared" si="154"/>
-        <v>85850.343940605497</v>
+        <f t="shared" si="167"/>
+        <v>81796.758561646464</v>
       </c>
       <c r="BD34" s="2">
-        <f t="shared" si="154"/>
-        <v>95790.284288912866</v>
+        <f t="shared" si="167"/>
+        <v>92726.652338225787</v>
       </c>
       <c r="BE34" s="2">
-        <f t="shared" si="154"/>
-        <v>106052.83759599282</v>
+        <f t="shared" si="167"/>
+        <v>104071.35887635905</v>
       </c>
       <c r="BF34" s="2">
-        <f t="shared" si="154"/>
-        <v>116511.26070261998</v>
+        <f t="shared" si="167"/>
+        <v>115680.3961207738</v>
       </c>
       <c r="BG34" s="2">
-        <f t="shared" si="154"/>
-        <v>127078.81854066545</v>
+        <f t="shared" si="167"/>
+        <v>127605.79608533884</v>
       </c>
       <c r="BH34" s="2">
-        <f t="shared" ref="BH34" si="155">+BG34+BH25</f>
-        <v>137862.21342761247</v>
+        <f t="shared" ref="BH34" si="168">+BG34+BH25</f>
+        <v>139892.92114860611</v>
       </c>
       <c r="BI34" s="2">
-        <f t="shared" ref="BI34" si="156">+BH34+BI25</f>
-        <v>148930.75941993232</v>
+        <f t="shared" ref="BI34" si="169">+BH34+BI25</f>
+        <v>152581.92320187442</v>
       </c>
       <c r="BJ34" s="2">
-        <f t="shared" ref="BJ34" si="157">+BI34+BJ25</f>
-        <v>160333.55113264496</v>
+        <f t="shared" ref="BJ34" si="170">+BI34+BJ25</f>
+        <v>165708.915028724</v>
       </c>
       <c r="BK34" s="2">
-        <f t="shared" ref="BK34" si="158">+BJ34+BK25</f>
-        <v>172108.40801162791</v>
+        <f t="shared" ref="BK34" si="171">+BJ34+BK25</f>
+        <v>179306.91159876372</v>
       </c>
       <c r="BL34" s="2">
-        <f t="shared" ref="BL34" si="159">+BK34+BL25</f>
-        <v>180915.08492314772</v>
+        <f t="shared" ref="BL34" si="172">+BK34+BL25</f>
+        <v>189157.31010478953</v>
       </c>
       <c r="BN34" s="2" t="s">
         <v>286</v>
       </c>
       <c r="BO34" s="1">
         <f>BO33/Main!M3</f>
-        <v>542.76051597323317</v>
+        <v>586.57186985582075</v>
       </c>
     </row>
     <row r="35" spans="2:67" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9821,76 +10180,76 @@
       <c r="K43" s="12"/>
       <c r="L43" s="12"/>
       <c r="M43" s="12">
-        <f t="shared" ref="M43:R43" si="160">SUM(M34:M42)</f>
+        <f t="shared" ref="M43:R43" si="173">SUM(M34:M42)</f>
         <v>12115.058999999997</v>
       </c>
       <c r="N43" s="12">
-        <f t="shared" si="160"/>
+        <f t="shared" si="173"/>
         <v>12221.686</v>
       </c>
       <c r="O43" s="12">
-        <f t="shared" si="160"/>
+        <f t="shared" si="173"/>
         <v>12618.744999999999</v>
       </c>
       <c r="P43" s="12">
-        <f t="shared" si="160"/>
+        <f t="shared" si="173"/>
         <v>13432.499999999998</v>
       </c>
       <c r="Q43" s="12">
-        <f t="shared" si="160"/>
+        <f t="shared" si="173"/>
         <v>14256.1</v>
       </c>
       <c r="R43" s="12">
-        <f t="shared" si="160"/>
+        <f t="shared" si="173"/>
         <v>15582.2</v>
       </c>
       <c r="S43" s="12">
-        <f t="shared" ref="S43:AC43" si="161">SUM(S34:S42)</f>
+        <f t="shared" ref="S43:AC43" si="174">SUM(S34:S42)</f>
         <v>16706.400000000005</v>
       </c>
       <c r="T43" s="12">
-        <f t="shared" si="161"/>
+        <f t="shared" si="174"/>
         <v>18150.900000000001</v>
       </c>
       <c r="U43" s="12">
-        <f t="shared" si="161"/>
+        <f t="shared" si="174"/>
         <v>18974.2</v>
       </c>
       <c r="V43" s="12">
-        <f t="shared" si="161"/>
+        <f t="shared" si="174"/>
         <v>20349.2</v>
       </c>
       <c r="W43" s="12">
-        <f t="shared" si="161"/>
+        <f t="shared" si="174"/>
         <v>21726.2</v>
       </c>
       <c r="X43" s="12">
-        <f t="shared" si="161"/>
+        <f t="shared" si="174"/>
         <v>22730.199999999997</v>
       </c>
       <c r="Y43" s="12">
-        <f t="shared" si="161"/>
+        <f t="shared" si="174"/>
         <v>23917.4</v>
       </c>
       <c r="Z43" s="12">
-        <f t="shared" si="161"/>
+        <f t="shared" si="174"/>
         <v>15691.3</v>
       </c>
       <c r="AA43" s="12">
-        <f t="shared" si="161"/>
+        <f t="shared" si="174"/>
         <v>16849.3</v>
       </c>
       <c r="AB43" s="12">
-        <f t="shared" si="161"/>
+        <f t="shared" si="174"/>
         <v>17973.099999999999</v>
       </c>
       <c r="AC43" s="12">
-        <f t="shared" si="161"/>
+        <f t="shared" si="174"/>
         <v>22880.5</v>
       </c>
       <c r="AD43" s="12"/>
       <c r="AE43" s="12">
-        <f t="shared" ref="AE43" si="162">SUM(AE34:AE42)</f>
+        <f t="shared" ref="AE43" si="175">SUM(AE34:AE42)</f>
         <v>24862.299999999996</v>
       </c>
       <c r="AF43" s="12"/>
@@ -10349,51 +10708,51 @@
       <c r="K52" s="12"/>
       <c r="L52" s="12"/>
       <c r="M52" s="12">
-        <f t="shared" ref="M52:R52" si="163">SUM(M45:M51)</f>
+        <f t="shared" ref="M52:R52" si="176">SUM(M45:M51)</f>
         <v>12115.059000000001</v>
       </c>
       <c r="N52" s="12">
-        <f t="shared" si="163"/>
+        <f t="shared" si="176"/>
         <v>12221.686000000002</v>
       </c>
       <c r="O52" s="12">
-        <f t="shared" si="163"/>
+        <f t="shared" si="176"/>
         <v>12618.745000000001</v>
       </c>
       <c r="P52" s="12">
-        <f t="shared" si="163"/>
+        <f t="shared" si="176"/>
         <v>13432.5</v>
       </c>
       <c r="Q52" s="12">
-        <f t="shared" si="163"/>
+        <f t="shared" si="176"/>
         <v>14256.1</v>
       </c>
       <c r="R52" s="12">
-        <f t="shared" si="163"/>
+        <f t="shared" si="176"/>
         <v>15582.2</v>
       </c>
       <c r="S52" s="12">
-        <f t="shared" ref="S52:X52" si="164">SUM(S45:S51)</f>
+        <f t="shared" ref="S52:X52" si="177">SUM(S45:S51)</f>
         <v>16706.400000000001</v>
       </c>
       <c r="T52" s="12">
-        <f t="shared" si="164"/>
+        <f t="shared" si="177"/>
         <v>18150.900000000001</v>
       </c>
       <c r="U52" s="12">
-        <f t="shared" si="164"/>
+        <f t="shared" si="177"/>
         <v>18974.199999999997</v>
       </c>
       <c r="V52" s="12">
-        <f t="shared" si="164"/>
+        <f t="shared" si="177"/>
         <v>20349.2</v>
       </c>
       <c r="W52" s="12">
-        <f t="shared" si="164"/>
+        <f t="shared" si="177"/>
         <v>21726.2</v>
       </c>
       <c r="X52" s="12">
-        <f t="shared" si="164"/>
+        <f t="shared" si="177"/>
         <v>22730.2</v>
       </c>
       <c r="Y52" s="12">
@@ -10401,24 +10760,24 @@
         <v>23917.399999999998</v>
       </c>
       <c r="Z52" s="12">
-        <f t="shared" ref="Z52:AC52" si="165">SUM(Z45:Z51)</f>
+        <f t="shared" ref="Z52:AC52" si="178">SUM(Z45:Z51)</f>
         <v>0</v>
       </c>
       <c r="AA52" s="12">
-        <f t="shared" si="165"/>
+        <f t="shared" si="178"/>
         <v>0</v>
       </c>
       <c r="AB52" s="12">
-        <f t="shared" si="165"/>
+        <f t="shared" si="178"/>
         <v>0</v>
       </c>
       <c r="AC52" s="12">
-        <f t="shared" si="165"/>
+        <f t="shared" si="178"/>
         <v>22880.5</v>
       </c>
       <c r="AD52" s="12"/>
       <c r="AE52" s="12">
-        <f t="shared" ref="AE52" si="166">SUM(AE45:AE51)</f>
+        <f t="shared" ref="AE52" si="179">SUM(AE45:AE51)</f>
         <v>24862.3</v>
       </c>
       <c r="AF52" s="12"/>
@@ -10443,79 +10802,79 @@
       <c r="K54" s="12"/>
       <c r="L54" s="12"/>
       <c r="M54" s="12">
-        <f t="shared" ref="M54:P54" si="167">+M25</f>
+        <f t="shared" ref="M54:P54" si="180">+M25</f>
         <v>779.8</v>
       </c>
       <c r="N54" s="12">
-        <f t="shared" si="167"/>
+        <f t="shared" si="180"/>
         <v>897.40000000000009</v>
       </c>
       <c r="O54" s="12">
-        <f t="shared" si="167"/>
+        <f t="shared" si="180"/>
         <v>810.59600000000034</v>
       </c>
       <c r="P54" s="12">
-        <f t="shared" si="167"/>
+        <f t="shared" si="180"/>
         <v>868.69999999999982</v>
       </c>
       <c r="Q54" s="12">
-        <f t="shared" ref="Q54:AE54" si="168">+Q25</f>
+        <f t="shared" ref="Q54:AE54" si="181">+Q25</f>
         <v>1002.4000000000001</v>
       </c>
       <c r="R54" s="12">
-        <f t="shared" si="168"/>
+        <f t="shared" si="181"/>
         <v>984.70000000000016</v>
       </c>
       <c r="S54" s="12">
-        <f t="shared" si="168"/>
+        <f t="shared" si="181"/>
         <v>1104.7999999999995</v>
       </c>
       <c r="T54" s="12">
-        <f t="shared" si="168"/>
+        <f t="shared" si="181"/>
         <v>989.79999999999984</v>
       </c>
       <c r="U54" s="12">
-        <f t="shared" si="168"/>
+        <f t="shared" si="181"/>
         <v>1141.0999999999995</v>
       </c>
       <c r="V54" s="12">
-        <f t="shared" si="168"/>
+        <f t="shared" si="181"/>
         <v>1124.5</v>
       </c>
       <c r="W54" s="12">
-        <f t="shared" si="168"/>
+        <f t="shared" si="181"/>
         <v>1115.4000000000003</v>
       </c>
       <c r="X54" s="12">
-        <f t="shared" si="168"/>
+        <f t="shared" si="181"/>
         <v>1149.4000000000003</v>
       </c>
       <c r="Y54" s="2">
-        <f t="shared" si="168"/>
+        <f t="shared" si="181"/>
         <v>1318.5999999999995</v>
       </c>
       <c r="Z54" s="2">
-        <f t="shared" si="168"/>
+        <f t="shared" si="181"/>
         <v>1138.5999999999999</v>
       </c>
       <c r="AA54" s="2">
-        <f t="shared" si="168"/>
+        <f t="shared" si="181"/>
         <v>1158.0000000000002</v>
       </c>
       <c r="AB54" s="2">
-        <f t="shared" si="168"/>
+        <f t="shared" si="181"/>
         <v>1123.7999999999997</v>
       </c>
       <c r="AC54" s="2">
-        <f t="shared" si="168"/>
+        <f t="shared" si="181"/>
         <v>1188.4499999999998</v>
       </c>
       <c r="AD54" s="2">
-        <f t="shared" si="168"/>
+        <f t="shared" si="181"/>
         <v>1052.8999999999996</v>
       </c>
       <c r="AE54" s="2">
-        <f t="shared" si="168"/>
+        <f t="shared" si="181"/>
         <v>1298.0000000000002</v>
       </c>
     </row>
@@ -11091,55 +11450,55 @@
       <c r="K64" s="12"/>
       <c r="L64" s="12"/>
       <c r="M64" s="12">
-        <f t="shared" ref="M64:Y64" si="169">SUM(M55:M63)</f>
+        <f t="shared" ref="M64:Y64" si="182">SUM(M55:M63)</f>
         <v>921.05499999999995</v>
       </c>
       <c r="N64" s="12">
-        <f t="shared" si="169"/>
+        <f t="shared" si="182"/>
         <v>-199.76700000000002</v>
       </c>
       <c r="O64" s="12">
-        <f t="shared" si="169"/>
+        <f t="shared" si="182"/>
         <v>927.21900000000028</v>
       </c>
       <c r="P64" s="12">
-        <f t="shared" si="169"/>
+        <f t="shared" si="182"/>
         <v>994.99299999999994</v>
       </c>
       <c r="Q64" s="12">
-        <f t="shared" si="169"/>
+        <f t="shared" si="182"/>
         <v>956.20000000000016</v>
       </c>
       <c r="R64" s="12">
-        <f t="shared" si="169"/>
+        <f t="shared" si="182"/>
         <v>1139.7999999999997</v>
       </c>
       <c r="S64" s="12">
-        <f t="shared" si="169"/>
+        <f t="shared" si="182"/>
         <v>955.49999999999989</v>
       </c>
       <c r="T64" s="12">
-        <f t="shared" si="169"/>
+        <f t="shared" si="182"/>
         <v>1078.3999999999996</v>
       </c>
       <c r="U64" s="12">
-        <f t="shared" si="169"/>
+        <f t="shared" si="182"/>
         <v>899.9</v>
       </c>
       <c r="V64" s="12">
-        <f t="shared" si="169"/>
+        <f t="shared" si="182"/>
         <v>1134.4000000000001</v>
       </c>
       <c r="W64" s="12">
-        <f t="shared" si="169"/>
+        <f t="shared" si="182"/>
         <v>1268.4000000000003</v>
       </c>
       <c r="X64" s="12">
-        <f t="shared" si="169"/>
+        <f t="shared" si="182"/>
         <v>234.59999999999968</v>
       </c>
       <c r="Y64" s="2">
-        <f t="shared" si="169"/>
+        <f t="shared" si="182"/>
         <v>1306.6000000000001</v>
       </c>
       <c r="AC64" s="2">
@@ -11356,27 +11715,27 @@
       <c r="K69" s="12"/>
       <c r="L69" s="12"/>
       <c r="M69" s="12">
-        <f t="shared" ref="M69:R69" si="170">M66+M68</f>
+        <f t="shared" ref="M69:R69" si="183">M66+M68</f>
         <v>-74.308999999999997</v>
       </c>
       <c r="N69" s="12">
-        <f t="shared" si="170"/>
+        <f t="shared" si="183"/>
         <v>-79.64100000000002</v>
       </c>
       <c r="O69" s="12">
-        <f t="shared" si="170"/>
+        <f t="shared" si="183"/>
         <v>-52.952000000000012</v>
       </c>
       <c r="P69" s="12">
-        <f t="shared" si="170"/>
+        <f t="shared" si="183"/>
         <v>-133.99800000000002</v>
       </c>
       <c r="Q69" s="12">
-        <f t="shared" si="170"/>
+        <f t="shared" si="183"/>
         <v>-51.000000000000007</v>
       </c>
       <c r="R69" s="12">
-        <f t="shared" si="170"/>
+        <f t="shared" si="183"/>
         <v>-61.499999999999993</v>
       </c>
       <c r="S69" s="12">
@@ -11756,59 +12115,59 @@
       <c r="K76" s="12"/>
       <c r="L76" s="12"/>
       <c r="M76" s="12">
-        <f t="shared" ref="M76:P76" si="171">SUM(M71:M75)</f>
+        <f t="shared" ref="M76:P76" si="184">SUM(M71:M75)</f>
         <v>-518.654</v>
       </c>
       <c r="N76" s="12">
-        <f t="shared" si="171"/>
+        <f t="shared" si="184"/>
         <v>33.550000000000004</v>
       </c>
       <c r="O76" s="12">
-        <f t="shared" si="171"/>
+        <f t="shared" si="184"/>
         <v>-656.66099999999994</v>
       </c>
       <c r="P76" s="12">
-        <f t="shared" si="171"/>
+        <f t="shared" si="184"/>
         <v>-336.23500000000018</v>
       </c>
       <c r="Q76" s="12">
-        <f t="shared" ref="Q76:Y76" si="172">SUM(Q71:Q75)</f>
+        <f t="shared" ref="Q76:Y76" si="185">SUM(Q71:Q75)</f>
         <v>-95.4</v>
       </c>
       <c r="R76" s="12">
-        <f t="shared" si="172"/>
+        <f t="shared" si="185"/>
         <v>47.699999999999982</v>
       </c>
       <c r="S76" s="12">
-        <f t="shared" si="172"/>
+        <f t="shared" si="185"/>
         <v>-60.199999999999996</v>
       </c>
       <c r="T76" s="12">
-        <f t="shared" si="172"/>
+        <f t="shared" si="185"/>
         <v>40.200000000000024</v>
       </c>
       <c r="U76" s="2">
-        <f t="shared" si="172"/>
+        <f t="shared" si="185"/>
         <v>-294.70000000000005</v>
       </c>
       <c r="V76" s="2">
-        <f t="shared" si="172"/>
+        <f t="shared" si="185"/>
         <v>17.300000000000018</v>
       </c>
       <c r="W76" s="2">
-        <f t="shared" si="172"/>
+        <f t="shared" si="185"/>
         <v>-165.00000000000006</v>
       </c>
       <c r="X76" s="2">
-        <f t="shared" si="172"/>
+        <f t="shared" si="185"/>
         <v>-119.80000000000005</v>
       </c>
       <c r="Y76" s="2">
-        <f t="shared" si="172"/>
+        <f t="shared" si="185"/>
         <v>-357.5</v>
       </c>
       <c r="AC76" s="2">
-        <f t="shared" ref="AC76" si="173">SUM(AC71:AC75)</f>
+        <f t="shared" ref="AC76" si="186">SUM(AC71:AC75)</f>
         <v>-680.40000000000009</v>
       </c>
     </row>
@@ -11893,19 +12252,19 @@
       <c r="K78" s="12"/>
       <c r="L78" s="12"/>
       <c r="M78" s="12">
-        <f t="shared" ref="M78:P78" si="174">+M76+M77+M69+M64</f>
+        <f t="shared" ref="M78:P78" si="187">+M76+M77+M69+M64</f>
         <v>324.06200000000001</v>
       </c>
       <c r="N78" s="12">
-        <f t="shared" si="174"/>
+        <f t="shared" si="187"/>
         <v>-241.83900000000006</v>
       </c>
       <c r="O78" s="12">
-        <f t="shared" si="174"/>
+        <f t="shared" si="187"/>
         <v>209.14500000000032</v>
       </c>
       <c r="P78" s="12">
-        <f t="shared" si="174"/>
+        <f t="shared" si="187"/>
         <v>519.83199999999977</v>
       </c>
       <c r="Q78" s="12">
@@ -11994,7 +12353,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CD65BEA-589C-4679-9414-3940926A76D9}">
   <dimension ref="A1:H15"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
@@ -12120,7 +12479,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B06E6387-11D8-4B2C-A093-43065AD20DB4}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
@@ -12166,7 +12525,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8057770F-9056-4627-9D3F-7EDFE9146A1F}">
   <dimension ref="A1:H7"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
@@ -12237,7 +12596,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89D4BF29-0A94-4770-AA68-CFDB5D68D6D1}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
@@ -12296,7 +12655,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95E64667-B707-436E-8242-61F1E098F287}">
   <dimension ref="A1:I28"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
@@ -12355,7 +12714,7 @@
         <v>129</v>
       </c>
       <c r="C7" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -12461,7 +12820,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{680057B1-62FF-469A-BFF1-F8D2D83B9698}">
   <dimension ref="A1:C17"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
@@ -12488,7 +12847,7 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -12562,7 +12921,7 @@
     </row>
     <row r="17" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C17" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
   </sheetData>
@@ -12571,95 +12930,4 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8C3D72A-F23C-49FA-B015-8CB9FAFD237F}">
-  <dimension ref="A1:D16"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="13" x14ac:dyDescent="0.3">
-      <c r="C6" s="18" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C7" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C8" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="13" x14ac:dyDescent="0.3">
-      <c r="C10" s="18" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C11" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="D12" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C13" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="13" x14ac:dyDescent="0.3">
-      <c r="C16" s="18" t="s">
-        <v>410</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{22B1C448-9C83-4D95-99CC-9F72F9CD7C85}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>